--- a/shift-journal-93-template.xlsx
+++ b/shift-journal-93-template.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\admin\Desktop\Обход оператора\93\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{05CC5D4E-D943-4773-905F-2148D288CD2A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CA014FCD-7DAE-4EED-8197-CDE3BEB4EA1A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{189D04FD-74BB-4673-9126-C5E9C84BF947}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="1" xr2:uid="{189D04FD-74BB-4673-9126-C5E9C84BF947}"/>
   </bookViews>
   <sheets>
     <sheet name="93" sheetId="1" r:id="rId1"/>
@@ -58,7 +58,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="275" uniqueCount="185">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="902" uniqueCount="341">
   <si>
     <t>Кезекшілік журналы/тәуліктік ақпарат</t>
   </si>
@@ -450,9 +450,6 @@
     <t>мәтін</t>
   </si>
   <si>
-    <t>Ақпарат</t>
-  </si>
-  <si>
     <t>ЖАЖ / КЖАЖ</t>
   </si>
   <si>
@@ -570,12 +567,6 @@
     <t>22</t>
   </si>
   <si>
-    <t>Сорпа атауы / нөмірі</t>
-  </si>
-  <si>
-    <t>Сорпалар</t>
-  </si>
-  <si>
     <t>21</t>
   </si>
   <si>
@@ -757,13 +748,490 @@
   </si>
   <si>
     <t>ТҚ-93 — Excel экспорт картасы</t>
+  </si>
+  <si>
+    <t>1ші қатар</t>
+  </si>
+  <si>
+    <t>2ші қатар</t>
+  </si>
+  <si>
+    <t>Сорап атауы / нөмірі</t>
+  </si>
+  <si>
+    <t>3ші қатар</t>
+  </si>
+  <si>
+    <t>Тығырық / сальник</t>
+  </si>
+  <si>
+    <t>Белдік / ремень</t>
+  </si>
+  <si>
+    <t>Скважиналарды өңдеу-сауықтыру жұмыстары</t>
+  </si>
+  <si>
+    <t>Көлемі, м³</t>
+  </si>
+  <si>
+    <t>37</t>
+  </si>
+  <si>
+    <t>38</t>
+  </si>
+  <si>
+    <t>39</t>
+  </si>
+  <si>
+    <t>40</t>
+  </si>
+  <si>
+    <t>41</t>
+  </si>
+  <si>
+    <t>42</t>
+  </si>
+  <si>
+    <t>43</t>
+  </si>
+  <si>
+    <t>44</t>
+  </si>
+  <si>
+    <t>45</t>
+  </si>
+  <si>
+    <t>46</t>
+  </si>
+  <si>
+    <t>47</t>
+  </si>
+  <si>
+    <t>48</t>
+  </si>
+  <si>
+    <t>49</t>
+  </si>
+  <si>
+    <t>50</t>
+  </si>
+  <si>
+    <t>51</t>
+  </si>
+  <si>
+    <t>52</t>
+  </si>
+  <si>
+    <t>53</t>
+  </si>
+  <si>
+    <t>54</t>
+  </si>
+  <si>
+    <t>55</t>
+  </si>
+  <si>
+    <t>56</t>
+  </si>
+  <si>
+    <t>57</t>
+  </si>
+  <si>
+    <t>58</t>
+  </si>
+  <si>
+    <t>59</t>
+  </si>
+  <si>
+    <t>60</t>
+  </si>
+  <si>
+    <t>61</t>
+  </si>
+  <si>
+    <t>62</t>
+  </si>
+  <si>
+    <t>63</t>
+  </si>
+  <si>
+    <t>64</t>
+  </si>
+  <si>
+    <t>65</t>
+  </si>
+  <si>
+    <t>66</t>
+  </si>
+  <si>
+    <t>67</t>
+  </si>
+  <si>
+    <t>68</t>
+  </si>
+  <si>
+    <t>69</t>
+  </si>
+  <si>
+    <t>70</t>
+  </si>
+  <si>
+    <t>71</t>
+  </si>
+  <si>
+    <t>72</t>
+  </si>
+  <si>
+    <t>73</t>
+  </si>
+  <si>
+    <t>74</t>
+  </si>
+  <si>
+    <t>75</t>
+  </si>
+  <si>
+    <t>76</t>
+  </si>
+  <si>
+    <t>77</t>
+  </si>
+  <si>
+    <t>78</t>
+  </si>
+  <si>
+    <t>79</t>
+  </si>
+  <si>
+    <t>80</t>
+  </si>
+  <si>
+    <t>81</t>
+  </si>
+  <si>
+    <t>82</t>
+  </si>
+  <si>
+    <t>83</t>
+  </si>
+  <si>
+    <t>84</t>
+  </si>
+  <si>
+    <t>85</t>
+  </si>
+  <si>
+    <t>86</t>
+  </si>
+  <si>
+    <t>87</t>
+  </si>
+  <si>
+    <t>88</t>
+  </si>
+  <si>
+    <t>89</t>
+  </si>
+  <si>
+    <t>90</t>
+  </si>
+  <si>
+    <t>91</t>
+  </si>
+  <si>
+    <t>92</t>
+  </si>
+  <si>
+    <t>93</t>
+  </si>
+  <si>
+    <t>94</t>
+  </si>
+  <si>
+    <t>95</t>
+  </si>
+  <si>
+    <t>96</t>
+  </si>
+  <si>
+    <t>97</t>
+  </si>
+  <si>
+    <t>98</t>
+  </si>
+  <si>
+    <t>99</t>
+  </si>
+  <si>
+    <t>100</t>
+  </si>
+  <si>
+    <t>101</t>
+  </si>
+  <si>
+    <t>102</t>
+  </si>
+  <si>
+    <t>103</t>
+  </si>
+  <si>
+    <t>104</t>
+  </si>
+  <si>
+    <t>105</t>
+  </si>
+  <si>
+    <t>106</t>
+  </si>
+  <si>
+    <t>107</t>
+  </si>
+  <si>
+    <t>108</t>
+  </si>
+  <si>
+    <t>109</t>
+  </si>
+  <si>
+    <t>110</t>
+  </si>
+  <si>
+    <t>111</t>
+  </si>
+  <si>
+    <t>112</t>
+  </si>
+  <si>
+    <t>113</t>
+  </si>
+  <si>
+    <t>114</t>
+  </si>
+  <si>
+    <t>115</t>
+  </si>
+  <si>
+    <t>116</t>
+  </si>
+  <si>
+    <t>117</t>
+  </si>
+  <si>
+    <t>118</t>
+  </si>
+  <si>
+    <t>119</t>
+  </si>
+  <si>
+    <t>120</t>
+  </si>
+  <si>
+    <t>121</t>
+  </si>
+  <si>
+    <t>122</t>
+  </si>
+  <si>
+    <t>123</t>
+  </si>
+  <si>
+    <t>124</t>
+  </si>
+  <si>
+    <t>125</t>
+  </si>
+  <si>
+    <t>126</t>
+  </si>
+  <si>
+    <t>127</t>
+  </si>
+  <si>
+    <t>128</t>
+  </si>
+  <si>
+    <t>129</t>
+  </si>
+  <si>
+    <t>130</t>
+  </si>
+  <si>
+    <t>131</t>
+  </si>
+  <si>
+    <t>132</t>
+  </si>
+  <si>
+    <t>133</t>
+  </si>
+  <si>
+    <t>134</t>
+  </si>
+  <si>
+    <t>135</t>
+  </si>
+  <si>
+    <t>136</t>
+  </si>
+  <si>
+    <t>137</t>
+  </si>
+  <si>
+    <t>138</t>
+  </si>
+  <si>
+    <t>139</t>
+  </si>
+  <si>
+    <t>140</t>
+  </si>
+  <si>
+    <t>141</t>
+  </si>
+  <si>
+    <t>142</t>
+  </si>
+  <si>
+    <t>143</t>
+  </si>
+  <si>
+    <t>144</t>
+  </si>
+  <si>
+    <t>145</t>
+  </si>
+  <si>
+    <t>146</t>
+  </si>
+  <si>
+    <t>147</t>
+  </si>
+  <si>
+    <t>148</t>
+  </si>
+  <si>
+    <t>149</t>
+  </si>
+  <si>
+    <t>150</t>
+  </si>
+  <si>
+    <t>151</t>
+  </si>
+  <si>
+    <t>152</t>
+  </si>
+  <si>
+    <t>153</t>
+  </si>
+  <si>
+    <t>154</t>
+  </si>
+  <si>
+    <t>155</t>
+  </si>
+  <si>
+    <t>156</t>
+  </si>
+  <si>
+    <t>157</t>
+  </si>
+  <si>
+    <t>158</t>
+  </si>
+  <si>
+    <t>159</t>
+  </si>
+  <si>
+    <t>160</t>
+  </si>
+  <si>
+    <t>161</t>
+  </si>
+  <si>
+    <t>162</t>
+  </si>
+  <si>
+    <t>163</t>
+  </si>
+  <si>
+    <t>164</t>
+  </si>
+  <si>
+    <t>165</t>
+  </si>
+  <si>
+    <t>166</t>
+  </si>
+  <si>
+    <t>167</t>
+  </si>
+  <si>
+    <t>168</t>
+  </si>
+  <si>
+    <t>169</t>
+  </si>
+  <si>
+    <t>170</t>
+  </si>
+  <si>
+    <t>171</t>
+  </si>
+  <si>
+    <t>172</t>
+  </si>
+  <si>
+    <t>173</t>
+  </si>
+  <si>
+    <t>174</t>
+  </si>
+  <si>
+    <t>175</t>
+  </si>
+  <si>
+    <t>176</t>
+  </si>
+  <si>
+    <t>177</t>
+  </si>
+  <si>
+    <t>178</t>
+  </si>
+  <si>
+    <t>179</t>
+  </si>
+  <si>
+    <t>180</t>
+  </si>
+  <si>
+    <t>181</t>
+  </si>
+  <si>
+    <t>182</t>
+  </si>
+  <si>
+    <t>183</t>
+  </si>
+  <si>
+    <t>184</t>
+  </si>
+  <si>
+    <t>185</t>
+  </si>
+  <si>
+    <t>186</t>
+  </si>
+  <si>
+    <t>187</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="18">
+  <fonts count="20">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -875,6 +1343,17 @@
       <sz val="16"/>
       <color rgb="FFFFFFFF"/>
       <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF182433"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <charset val="204"/>
     </font>
   </fonts>
   <fills count="18">
@@ -1518,7 +1997,7 @@
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="194">
+  <cellXfs count="195">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1600,9 +2079,6 @@
     </xf>
     <xf numFmtId="0" fontId="8" fillId="4" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="4" borderId="20" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -1908,103 +2384,46 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="16" borderId="8" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="16" borderId="9" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="16" borderId="10" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="16" borderId="37" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="16" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="16" borderId="38" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="16" borderId="39" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="16" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="16" borderId="40" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="17" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="2" fillId="17" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="41" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="17" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="18" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="7" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="24" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="30" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="9" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="31" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="21" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="22" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="23" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="16" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="17" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="18" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="16" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="33" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="34" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="35" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="3" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2040,6 +2459,12 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="24" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="7" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="5" borderId="24" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
     </xf>
@@ -2052,11 +2477,95 @@
     <xf numFmtId="0" fontId="3" fillId="4" borderId="26" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="16" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="17" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="18" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="30" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="9" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="31" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="21" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="22" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="23" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="16" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="17" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="18" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="33" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="34" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="35" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="41" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="24" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="15" borderId="0" xfId="5" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2064,38 +2573,11 @@
     <xf numFmtId="0" fontId="16" fillId="14" borderId="0" xfId="5" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="16" borderId="8" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="20" fontId="14" fillId="0" borderId="42" xfId="5" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="16" borderId="9" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="16" borderId="10" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="16" borderId="37" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="16" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="16" borderId="38" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="16" borderId="39" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="16" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="16" borderId="40" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="17" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="17" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="42" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="6">
@@ -23183,14 +23665,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:19">
-      <c r="G1" s="179" t="s">
+      <c r="G1" s="141" t="s">
         <v>0</v>
       </c>
-      <c r="H1" s="179"/>
-      <c r="I1" s="179"/>
-      <c r="J1" s="179"/>
-      <c r="K1" s="179"/>
-      <c r="L1" s="179"/>
+      <c r="H1" s="141"/>
+      <c r="I1" s="141"/>
+      <c r="J1" s="141"/>
+      <c r="K1" s="141"/>
+      <c r="L1" s="141"/>
     </row>
     <row r="2" spans="1:19">
       <c r="A2" s="3"/>
@@ -23219,9 +23701,9 @@
       <c r="P2" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="Q2" s="121"/>
-      <c r="R2" s="121"/>
-      <c r="S2" s="121"/>
+      <c r="Q2" s="120"/>
+      <c r="R2" s="120"/>
+      <c r="S2" s="120"/>
     </row>
     <row r="3" spans="1:19">
       <c r="A3" s="3"/>
@@ -23245,55 +23727,55 @@
       <c r="S3" s="7"/>
     </row>
     <row r="4" spans="1:19" ht="21.75" customHeight="1">
-      <c r="A4" s="180" t="s">
+      <c r="A4" s="142" t="s">
         <v>5</v>
       </c>
-      <c r="B4" s="180" t="s">
+      <c r="B4" s="142" t="s">
         <v>6</v>
       </c>
-      <c r="C4" s="180" t="s">
+      <c r="C4" s="142" t="s">
         <v>7</v>
       </c>
-      <c r="D4" s="148" t="s">
+      <c r="D4" s="143" t="s">
         <v>8</v>
       </c>
-      <c r="E4" s="148" t="s">
+      <c r="E4" s="143" t="s">
         <v>9</v>
       </c>
-      <c r="F4" s="148" t="s">
+      <c r="F4" s="143" t="s">
         <v>10</v>
       </c>
-      <c r="G4" s="148" t="s">
+      <c r="G4" s="143" t="s">
         <v>11</v>
       </c>
-      <c r="H4" s="148"/>
-      <c r="I4" s="148"/>
-      <c r="J4" s="180" t="s">
+      <c r="H4" s="143"/>
+      <c r="I4" s="143"/>
+      <c r="J4" s="142" t="s">
         <v>12</v>
       </c>
-      <c r="K4" s="180" t="s">
+      <c r="K4" s="142" t="s">
         <v>13</v>
       </c>
-      <c r="L4" s="148" t="s">
+      <c r="L4" s="143" t="s">
         <v>14</v>
       </c>
-      <c r="M4" s="148" t="s">
+      <c r="M4" s="143" t="s">
         <v>15</v>
       </c>
-      <c r="N4" s="148"/>
-      <c r="O4" s="148"/>
-      <c r="P4" s="148"/>
-      <c r="Q4" s="148"/>
-      <c r="R4" s="148"/>
-      <c r="S4" s="148"/>
+      <c r="N4" s="143"/>
+      <c r="O4" s="143"/>
+      <c r="P4" s="143"/>
+      <c r="Q4" s="143"/>
+      <c r="R4" s="143"/>
+      <c r="S4" s="143"/>
     </row>
     <row r="5" spans="1:19" ht="27.75" customHeight="1">
-      <c r="A5" s="180"/>
-      <c r="B5" s="180"/>
-      <c r="C5" s="180"/>
-      <c r="D5" s="148"/>
-      <c r="E5" s="148"/>
-      <c r="F5" s="148"/>
+      <c r="A5" s="142"/>
+      <c r="B5" s="142"/>
+      <c r="C5" s="142"/>
+      <c r="D5" s="143"/>
+      <c r="E5" s="143"/>
+      <c r="F5" s="143"/>
       <c r="G5" s="8" t="s">
         <v>16</v>
       </c>
@@ -23303,25 +23785,25 @@
       <c r="I5" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="J5" s="180"/>
-      <c r="K5" s="180"/>
-      <c r="L5" s="148"/>
-      <c r="M5" s="148"/>
-      <c r="N5" s="148"/>
-      <c r="O5" s="148"/>
-      <c r="P5" s="148"/>
-      <c r="Q5" s="148"/>
-      <c r="R5" s="148"/>
-      <c r="S5" s="148"/>
+      <c r="J5" s="142"/>
+      <c r="K5" s="142"/>
+      <c r="L5" s="143"/>
+      <c r="M5" s="143"/>
+      <c r="N5" s="143"/>
+      <c r="O5" s="143"/>
+      <c r="P5" s="143"/>
+      <c r="Q5" s="143"/>
+      <c r="R5" s="143"/>
+      <c r="S5" s="143"/>
     </row>
     <row r="6" spans="1:19" s="16" customFormat="1" ht="21" customHeight="1">
       <c r="A6" s="9">
         <v>1</v>
       </c>
-      <c r="B6" s="164" t="s">
+      <c r="B6" s="144" t="s">
         <v>19</v>
       </c>
-      <c r="C6" s="166" t="s">
+      <c r="C6" s="146" t="s">
         <v>20</v>
       </c>
       <c r="D6" s="10">
@@ -23367,8 +23849,8 @@
       <c r="A7" s="9">
         <v>2</v>
       </c>
-      <c r="B7" s="165"/>
-      <c r="C7" s="167"/>
+      <c r="B7" s="145"/>
+      <c r="C7" s="147"/>
       <c r="D7" s="10">
         <v>2</v>
       </c>
@@ -23412,8 +23894,8 @@
       <c r="A8" s="9">
         <v>3</v>
       </c>
-      <c r="B8" s="165"/>
-      <c r="C8" s="167"/>
+      <c r="B8" s="145"/>
+      <c r="C8" s="147"/>
       <c r="D8" s="10">
         <v>3</v>
       </c>
@@ -23439,22 +23921,22 @@
       <c r="J8" s="9"/>
       <c r="K8" s="9"/>
       <c r="L8" s="20"/>
-      <c r="M8" s="168" t="s">
+      <c r="M8" s="148" t="s">
         <v>24</v>
       </c>
-      <c r="N8" s="169"/>
-      <c r="O8" s="169"/>
-      <c r="P8" s="169"/>
-      <c r="Q8" s="169"/>
-      <c r="R8" s="169"/>
-      <c r="S8" s="170"/>
+      <c r="N8" s="149"/>
+      <c r="O8" s="149"/>
+      <c r="P8" s="149"/>
+      <c r="Q8" s="149"/>
+      <c r="R8" s="149"/>
+      <c r="S8" s="150"/>
     </row>
     <row r="9" spans="1:19" s="16" customFormat="1" ht="21" customHeight="1">
       <c r="A9" s="9">
         <v>4</v>
       </c>
-      <c r="B9" s="165"/>
-      <c r="C9" s="167"/>
+      <c r="B9" s="145"/>
+      <c r="C9" s="147"/>
       <c r="D9" s="10">
         <v>5</v>
       </c>
@@ -23480,28 +23962,28 @@
       <c r="J9" s="9"/>
       <c r="K9" s="9"/>
       <c r="L9" s="20"/>
-      <c r="M9" s="112" t="s">
+      <c r="M9" s="111" t="s">
         <v>72</v>
       </c>
-      <c r="N9" s="113" t="s">
+      <c r="N9" s="112" t="s">
         <v>73</v>
       </c>
-      <c r="O9" s="114"/>
-      <c r="P9" s="112" t="s">
+      <c r="O9" s="113"/>
+      <c r="P9" s="111" t="s">
         <v>72</v>
       </c>
-      <c r="Q9" s="113" t="s">
+      <c r="Q9" s="112" t="s">
         <v>73</v>
       </c>
-      <c r="R9" s="113"/>
-      <c r="S9" s="115"/>
+      <c r="R9" s="112"/>
+      <c r="S9" s="114"/>
     </row>
     <row r="10" spans="1:19" s="16" customFormat="1" ht="21" customHeight="1">
       <c r="A10" s="9">
         <v>5</v>
       </c>
-      <c r="B10" s="165"/>
-      <c r="C10" s="167"/>
+      <c r="B10" s="145"/>
+      <c r="C10" s="147"/>
       <c r="D10" s="10">
         <v>6</v>
       </c>
@@ -23539,8 +24021,8 @@
       <c r="A11" s="9">
         <v>6</v>
       </c>
-      <c r="B11" s="165"/>
-      <c r="C11" s="167"/>
+      <c r="B11" s="145"/>
+      <c r="C11" s="147"/>
       <c r="D11" s="10">
         <v>7</v>
       </c>
@@ -23578,8 +24060,8 @@
       <c r="A12" s="9">
         <v>7</v>
       </c>
-      <c r="B12" s="165"/>
-      <c r="C12" s="167"/>
+      <c r="B12" s="145"/>
+      <c r="C12" s="147"/>
       <c r="D12" s="10">
         <v>8</v>
       </c>
@@ -23617,8 +24099,8 @@
       <c r="A13" s="9">
         <v>8</v>
       </c>
-      <c r="B13" s="165"/>
-      <c r="C13" s="167"/>
+      <c r="B13" s="145"/>
+      <c r="C13" s="147"/>
       <c r="D13" s="10">
         <v>9</v>
       </c>
@@ -23656,8 +24138,8 @@
       <c r="A14" s="9">
         <v>9</v>
       </c>
-      <c r="B14" s="165"/>
-      <c r="C14" s="167"/>
+      <c r="B14" s="145"/>
+      <c r="C14" s="147"/>
       <c r="D14" s="10">
         <v>10</v>
       </c>
@@ -23695,8 +24177,8 @@
       <c r="A15" s="9">
         <v>10</v>
       </c>
-      <c r="B15" s="165"/>
-      <c r="C15" s="167"/>
+      <c r="B15" s="145"/>
+      <c r="C15" s="147"/>
       <c r="D15" s="10">
         <v>11</v>
       </c>
@@ -23730,8 +24212,8 @@
       <c r="A16" s="9">
         <v>11</v>
       </c>
-      <c r="B16" s="165"/>
-      <c r="C16" s="167"/>
+      <c r="B16" s="145"/>
+      <c r="C16" s="147"/>
       <c r="D16" s="10">
         <v>12</v>
       </c>
@@ -23757,7 +24239,7 @@
       <c r="J16" s="9"/>
       <c r="K16" s="9"/>
       <c r="L16" s="20"/>
-      <c r="M16" s="111"/>
+      <c r="M16" s="110"/>
       <c r="N16" s="22"/>
       <c r="O16" s="23"/>
       <c r="P16" s="22"/>
@@ -23769,8 +24251,8 @@
       <c r="A17" s="9">
         <v>12</v>
       </c>
-      <c r="B17" s="165"/>
-      <c r="C17" s="167"/>
+      <c r="B17" s="145"/>
+      <c r="C17" s="147"/>
       <c r="D17" s="10">
         <v>13</v>
       </c>
@@ -23796,22 +24278,22 @@
       <c r="J17" s="9"/>
       <c r="K17" s="9"/>
       <c r="L17" s="20"/>
-      <c r="M17" s="171" t="s">
+      <c r="M17" s="151" t="s">
         <v>25</v>
       </c>
-      <c r="N17" s="172"/>
-      <c r="O17" s="172"/>
-      <c r="P17" s="172"/>
-      <c r="Q17" s="172"/>
-      <c r="R17" s="172"/>
-      <c r="S17" s="173"/>
+      <c r="N17" s="152"/>
+      <c r="O17" s="152"/>
+      <c r="P17" s="152"/>
+      <c r="Q17" s="152"/>
+      <c r="R17" s="152"/>
+      <c r="S17" s="153"/>
     </row>
     <row r="18" spans="1:19" s="16" customFormat="1" ht="21" customHeight="1">
       <c r="A18" s="9">
         <v>13</v>
       </c>
-      <c r="B18" s="165"/>
-      <c r="C18" s="167"/>
+      <c r="B18" s="145"/>
+      <c r="C18" s="147"/>
       <c r="D18" s="10">
         <v>14</v>
       </c>
@@ -23846,23 +24328,23 @@
       <c r="O18" s="27" t="s">
         <v>27</v>
       </c>
-      <c r="P18" s="116" t="s">
+      <c r="P18" s="115" t="s">
         <v>72</v>
       </c>
-      <c r="Q18" s="28"/>
-      <c r="R18" s="26" t="s">
+      <c r="Q18" s="26" t="s">
         <v>26</v>
       </c>
-      <c r="S18" s="29" t="s">
+      <c r="R18" s="28" t="s">
         <v>27</v>
       </c>
+      <c r="S18" s="28"/>
     </row>
     <row r="19" spans="1:19" s="16" customFormat="1" ht="26.25" customHeight="1">
       <c r="A19" s="9">
         <v>14</v>
       </c>
-      <c r="B19" s="165"/>
-      <c r="C19" s="166" t="s">
+      <c r="B19" s="145"/>
+      <c r="C19" s="146" t="s">
         <v>28</v>
       </c>
       <c r="D19" s="10">
@@ -23890,19 +24372,19 @@
       <c r="J19" s="9"/>
       <c r="K19" s="9"/>
       <c r="L19" s="20"/>
-      <c r="M19" s="30"/>
-      <c r="O19" s="31"/>
-      <c r="P19" s="32"/>
-      <c r="Q19" s="31"/>
-      <c r="R19" s="31"/>
-      <c r="S19" s="33"/>
+      <c r="M19" s="29"/>
+      <c r="O19" s="30"/>
+      <c r="P19" s="31"/>
+      <c r="Q19" s="30"/>
+      <c r="R19" s="30"/>
+      <c r="S19" s="32"/>
     </row>
     <row r="20" spans="1:19" s="16" customFormat="1" ht="21" customHeight="1">
       <c r="A20" s="9">
         <v>15</v>
       </c>
-      <c r="B20" s="165"/>
-      <c r="C20" s="167"/>
+      <c r="B20" s="145"/>
+      <c r="C20" s="147"/>
       <c r="D20" s="10">
         <v>2</v>
       </c>
@@ -23928,20 +24410,20 @@
       <c r="J20" s="9"/>
       <c r="K20" s="9"/>
       <c r="L20" s="20"/>
-      <c r="M20" s="30"/>
-      <c r="N20" s="31"/>
-      <c r="O20" s="31"/>
-      <c r="P20" s="32"/>
-      <c r="Q20" s="31"/>
-      <c r="R20" s="31"/>
-      <c r="S20" s="33"/>
+      <c r="M20" s="29"/>
+      <c r="N20" s="30"/>
+      <c r="O20" s="30"/>
+      <c r="P20" s="31"/>
+      <c r="Q20" s="30"/>
+      <c r="R20" s="30"/>
+      <c r="S20" s="32"/>
     </row>
     <row r="21" spans="1:19" s="16" customFormat="1" ht="21" customHeight="1">
       <c r="A21" s="9">
         <v>16</v>
       </c>
-      <c r="B21" s="165"/>
-      <c r="C21" s="167"/>
+      <c r="B21" s="145"/>
+      <c r="C21" s="147"/>
       <c r="D21" s="10">
         <v>3</v>
       </c>
@@ -23966,20 +24448,20 @@
       <c r="J21" s="9"/>
       <c r="K21" s="9"/>
       <c r="L21" s="20"/>
-      <c r="M21" s="30"/>
-      <c r="N21" s="31"/>
-      <c r="O21" s="31"/>
-      <c r="P21" s="32"/>
-      <c r="Q21" s="31"/>
-      <c r="R21" s="31"/>
-      <c r="S21" s="33"/>
+      <c r="M21" s="29"/>
+      <c r="N21" s="30"/>
+      <c r="O21" s="30"/>
+      <c r="P21" s="31"/>
+      <c r="Q21" s="30"/>
+      <c r="R21" s="30"/>
+      <c r="S21" s="32"/>
     </row>
     <row r="22" spans="1:19" s="16" customFormat="1" ht="21" customHeight="1">
       <c r="A22" s="9">
         <v>17</v>
       </c>
-      <c r="B22" s="165"/>
-      <c r="C22" s="167"/>
+      <c r="B22" s="145"/>
+      <c r="C22" s="147"/>
       <c r="D22" s="10">
         <v>4</v>
       </c>
@@ -24005,20 +24487,20 @@
       <c r="J22" s="9"/>
       <c r="K22" s="9"/>
       <c r="L22" s="20"/>
-      <c r="M22" s="30"/>
-      <c r="N22" s="31"/>
-      <c r="O22" s="31"/>
-      <c r="P22" s="32"/>
-      <c r="Q22" s="31"/>
-      <c r="R22" s="31"/>
-      <c r="S22" s="33"/>
+      <c r="M22" s="29"/>
+      <c r="N22" s="30"/>
+      <c r="O22" s="30"/>
+      <c r="P22" s="31"/>
+      <c r="Q22" s="30"/>
+      <c r="R22" s="30"/>
+      <c r="S22" s="32"/>
     </row>
     <row r="23" spans="1:19" s="16" customFormat="1" ht="21" customHeight="1">
       <c r="A23" s="9">
         <v>18</v>
       </c>
-      <c r="B23" s="165"/>
-      <c r="C23" s="167"/>
+      <c r="B23" s="145"/>
+      <c r="C23" s="147"/>
       <c r="D23" s="10">
         <v>5</v>
       </c>
@@ -24044,20 +24526,20 @@
       <c r="J23" s="9"/>
       <c r="K23" s="9"/>
       <c r="L23" s="20"/>
-      <c r="M23" s="30"/>
-      <c r="N23" s="31"/>
-      <c r="O23" s="31"/>
-      <c r="P23" s="32"/>
-      <c r="Q23" s="31"/>
-      <c r="R23" s="31"/>
-      <c r="S23" s="33"/>
+      <c r="M23" s="29"/>
+      <c r="N23" s="30"/>
+      <c r="O23" s="30"/>
+      <c r="P23" s="31"/>
+      <c r="Q23" s="30"/>
+      <c r="R23" s="30"/>
+      <c r="S23" s="32"/>
     </row>
     <row r="24" spans="1:19" s="16" customFormat="1" ht="21" customHeight="1">
       <c r="A24" s="9">
         <v>19</v>
       </c>
-      <c r="B24" s="165"/>
-      <c r="C24" s="167"/>
+      <c r="B24" s="145"/>
+      <c r="C24" s="147"/>
       <c r="D24" s="10">
         <v>6</v>
       </c>
@@ -24083,20 +24565,20 @@
       <c r="J24" s="9"/>
       <c r="K24" s="9"/>
       <c r="L24" s="20"/>
-      <c r="M24" s="30"/>
-      <c r="N24" s="32"/>
-      <c r="O24" s="32"/>
-      <c r="P24" s="32"/>
-      <c r="Q24" s="32"/>
-      <c r="R24" s="32"/>
-      <c r="S24" s="34"/>
+      <c r="M24" s="29"/>
+      <c r="N24" s="31"/>
+      <c r="O24" s="31"/>
+      <c r="P24" s="31"/>
+      <c r="Q24" s="31"/>
+      <c r="R24" s="31"/>
+      <c r="S24" s="33"/>
     </row>
     <row r="25" spans="1:19" s="16" customFormat="1" ht="21" customHeight="1">
       <c r="A25" s="9">
         <v>20</v>
       </c>
-      <c r="B25" s="165"/>
-      <c r="C25" s="167"/>
+      <c r="B25" s="145"/>
+      <c r="C25" s="147"/>
       <c r="D25" s="10">
         <v>8</v>
       </c>
@@ -24122,21 +24604,21 @@
       <c r="J25" s="9"/>
       <c r="K25" s="9"/>
       <c r="L25" s="20"/>
-      <c r="M25" s="30"/>
-      <c r="N25" s="32"/>
-      <c r="O25" s="32"/>
-      <c r="P25" s="32"/>
-      <c r="Q25" s="32"/>
-      <c r="R25" s="32"/>
-      <c r="S25" s="34"/>
+      <c r="M25" s="29"/>
+      <c r="N25" s="31"/>
+      <c r="O25" s="31"/>
+      <c r="P25" s="31"/>
+      <c r="Q25" s="31"/>
+      <c r="R25" s="31"/>
+      <c r="S25" s="33"/>
     </row>
     <row r="26" spans="1:19" s="16" customFormat="1" ht="21" customHeight="1">
       <c r="A26" s="9">
         <v>21</v>
       </c>
-      <c r="B26" s="165"/>
-      <c r="C26" s="167"/>
-      <c r="D26" s="35">
+      <c r="B26" s="145"/>
+      <c r="C26" s="147"/>
+      <c r="D26" s="34">
         <v>9</v>
       </c>
       <c r="E26" s="11">
@@ -24161,21 +24643,21 @@
       <c r="J26" s="9"/>
       <c r="K26" s="9"/>
       <c r="L26" s="20"/>
-      <c r="M26" s="30"/>
-      <c r="N26" s="32"/>
-      <c r="O26" s="32"/>
-      <c r="P26" s="32"/>
-      <c r="Q26" s="32"/>
-      <c r="R26" s="32"/>
-      <c r="S26" s="34"/>
+      <c r="M26" s="29"/>
+      <c r="N26" s="31"/>
+      <c r="O26" s="31"/>
+      <c r="P26" s="31"/>
+      <c r="Q26" s="31"/>
+      <c r="R26" s="31"/>
+      <c r="S26" s="33"/>
     </row>
     <row r="27" spans="1:19" s="16" customFormat="1" ht="21" customHeight="1">
       <c r="A27" s="9">
         <v>22</v>
       </c>
-      <c r="B27" s="165"/>
-      <c r="C27" s="167"/>
-      <c r="D27" s="35">
+      <c r="B27" s="145"/>
+      <c r="C27" s="147"/>
+      <c r="D27" s="34">
         <v>10</v>
       </c>
       <c r="E27" s="11">
@@ -24200,20 +24682,20 @@
       <c r="J27" s="9"/>
       <c r="K27" s="9"/>
       <c r="L27" s="20"/>
-      <c r="M27" s="30"/>
-      <c r="N27" s="32"/>
-      <c r="O27" s="32"/>
-      <c r="P27" s="32"/>
-      <c r="Q27" s="32"/>
-      <c r="R27" s="32"/>
-      <c r="S27" s="34"/>
+      <c r="M27" s="29"/>
+      <c r="N27" s="31"/>
+      <c r="O27" s="31"/>
+      <c r="P27" s="31"/>
+      <c r="Q27" s="31"/>
+      <c r="R27" s="31"/>
+      <c r="S27" s="33"/>
     </row>
     <row r="28" spans="1:19" s="16" customFormat="1" ht="21" customHeight="1">
       <c r="A28" s="9">
         <v>23</v>
       </c>
-      <c r="B28" s="165"/>
-      <c r="C28" s="167"/>
+      <c r="B28" s="145"/>
+      <c r="C28" s="147"/>
       <c r="D28" s="10">
         <v>11</v>
       </c>
@@ -24239,21 +24721,21 @@
       <c r="J28" s="9"/>
       <c r="K28" s="9"/>
       <c r="L28" s="20"/>
-      <c r="M28" s="30"/>
-      <c r="N28" s="32"/>
-      <c r="O28" s="32"/>
-      <c r="P28" s="32"/>
-      <c r="Q28" s="32"/>
-      <c r="R28" s="32"/>
-      <c r="S28" s="34"/>
+      <c r="M28" s="29"/>
+      <c r="N28" s="31"/>
+      <c r="O28" s="31"/>
+      <c r="P28" s="31"/>
+      <c r="Q28" s="31"/>
+      <c r="R28" s="31"/>
+      <c r="S28" s="33"/>
     </row>
     <row r="29" spans="1:19" s="16" customFormat="1" ht="21.75" customHeight="1">
       <c r="A29" s="9">
         <v>24</v>
       </c>
-      <c r="B29" s="165"/>
-      <c r="C29" s="167"/>
-      <c r="D29" s="35">
+      <c r="B29" s="145"/>
+      <c r="C29" s="147"/>
+      <c r="D29" s="34">
         <v>12</v>
       </c>
       <c r="E29" s="11">
@@ -24278,20 +24760,20 @@
       <c r="J29" s="9"/>
       <c r="K29" s="9"/>
       <c r="L29" s="20"/>
-      <c r="M29" s="30"/>
-      <c r="N29" s="36"/>
-      <c r="O29" s="36"/>
-      <c r="P29" s="32"/>
-      <c r="Q29" s="36"/>
-      <c r="R29" s="36"/>
-      <c r="S29" s="37"/>
+      <c r="M29" s="29"/>
+      <c r="N29" s="35"/>
+      <c r="O29" s="35"/>
+      <c r="P29" s="31"/>
+      <c r="Q29" s="35"/>
+      <c r="R29" s="35"/>
+      <c r="S29" s="36"/>
     </row>
     <row r="30" spans="1:19" s="16" customFormat="1" ht="21.75" customHeight="1" thickBot="1">
       <c r="A30" s="9">
         <v>25</v>
       </c>
-      <c r="B30" s="165"/>
-      <c r="C30" s="167"/>
+      <c r="B30" s="145"/>
+      <c r="C30" s="147"/>
       <c r="D30" s="10">
         <v>13</v>
       </c>
@@ -24317,21 +24799,21 @@
       <c r="J30" s="9"/>
       <c r="K30" s="9"/>
       <c r="L30" s="20"/>
-      <c r="M30" s="38"/>
-      <c r="N30" s="39"/>
-      <c r="O30" s="39"/>
-      <c r="P30" s="39"/>
-      <c r="Q30" s="39"/>
-      <c r="R30" s="39"/>
-      <c r="S30" s="40"/>
+      <c r="M30" s="37"/>
+      <c r="N30" s="38"/>
+      <c r="O30" s="38"/>
+      <c r="P30" s="38"/>
+      <c r="Q30" s="38"/>
+      <c r="R30" s="38"/>
+      <c r="S30" s="39"/>
     </row>
     <row r="31" spans="1:19" s="16" customFormat="1" ht="21" customHeight="1">
       <c r="A31" s="9">
         <v>26</v>
       </c>
-      <c r="B31" s="165"/>
-      <c r="C31" s="167"/>
-      <c r="D31" s="35">
+      <c r="B31" s="145"/>
+      <c r="C31" s="147"/>
+      <c r="D31" s="34">
         <v>14</v>
       </c>
       <c r="E31" s="11">
@@ -24344,25 +24826,25 @@
       <c r="J31" s="9"/>
       <c r="K31" s="9"/>
       <c r="L31" s="20"/>
-      <c r="M31" s="171" t="s">
+      <c r="M31" s="151" t="s">
         <v>29</v>
       </c>
-      <c r="N31" s="172"/>
-      <c r="O31" s="172"/>
-      <c r="P31" s="172"/>
-      <c r="Q31" s="172"/>
-      <c r="R31" s="172"/>
-      <c r="S31" s="173"/>
+      <c r="N31" s="152"/>
+      <c r="O31" s="152"/>
+      <c r="P31" s="152"/>
+      <c r="Q31" s="152"/>
+      <c r="R31" s="152"/>
+      <c r="S31" s="153"/>
     </row>
     <row r="32" spans="1:19" s="16" customFormat="1" ht="21" customHeight="1">
       <c r="A32" s="9">
         <v>27</v>
       </c>
-      <c r="B32" s="165"/>
-      <c r="C32" s="166" t="s">
+      <c r="B32" s="145"/>
+      <c r="C32" s="146" t="s">
         <v>30</v>
       </c>
-      <c r="D32" s="41">
+      <c r="D32" s="40">
         <v>1</v>
       </c>
       <c r="E32" s="11">
@@ -24387,25 +24869,25 @@
       <c r="J32" s="9"/>
       <c r="K32" s="9"/>
       <c r="L32" s="20"/>
-      <c r="M32" s="30">
+      <c r="M32" s="29">
         <v>1</v>
       </c>
-      <c r="N32" s="32"/>
-      <c r="O32" s="32"/>
-      <c r="P32" s="32">
+      <c r="N32" s="31"/>
+      <c r="O32" s="31"/>
+      <c r="P32" s="31">
         <v>4</v>
       </c>
-      <c r="Q32" s="32"/>
-      <c r="R32" s="32"/>
-      <c r="S32" s="34"/>
+      <c r="Q32" s="31"/>
+      <c r="R32" s="31"/>
+      <c r="S32" s="33"/>
     </row>
     <row r="33" spans="1:19" s="16" customFormat="1" ht="21" customHeight="1">
       <c r="A33" s="9">
         <v>28</v>
       </c>
-      <c r="B33" s="165"/>
-      <c r="C33" s="167"/>
-      <c r="D33" s="42">
+      <c r="B33" s="145"/>
+      <c r="C33" s="147"/>
+      <c r="D33" s="41">
         <v>2</v>
       </c>
       <c r="E33" s="11">
@@ -24430,24 +24912,24 @@
       <c r="J33" s="9"/>
       <c r="K33" s="9"/>
       <c r="L33" s="20"/>
-      <c r="M33" s="30">
+      <c r="M33" s="29">
         <v>2</v>
       </c>
-      <c r="N33" s="32"/>
-      <c r="O33" s="32"/>
-      <c r="P33" s="32">
+      <c r="N33" s="31"/>
+      <c r="O33" s="31"/>
+      <c r="P33" s="31">
         <v>5</v>
       </c>
-      <c r="Q33" s="32"/>
-      <c r="R33" s="32"/>
-      <c r="S33" s="34"/>
+      <c r="Q33" s="31"/>
+      <c r="R33" s="31"/>
+      <c r="S33" s="33"/>
     </row>
     <row r="34" spans="1:19" s="16" customFormat="1" ht="21" customHeight="1" thickBot="1">
       <c r="A34" s="9">
         <v>29</v>
       </c>
-      <c r="B34" s="165"/>
-      <c r="C34" s="167"/>
+      <c r="B34" s="145"/>
+      <c r="C34" s="147"/>
       <c r="D34" s="10">
         <v>3</v>
       </c>
@@ -24473,24 +24955,24 @@
       <c r="J34" s="9"/>
       <c r="K34" s="9"/>
       <c r="L34" s="20"/>
-      <c r="M34" s="38">
+      <c r="M34" s="37">
         <v>3</v>
       </c>
-      <c r="N34" s="39"/>
-      <c r="O34" s="39"/>
-      <c r="P34" s="39">
+      <c r="N34" s="38"/>
+      <c r="O34" s="38"/>
+      <c r="P34" s="38">
         <v>6</v>
       </c>
-      <c r="Q34" s="39"/>
-      <c r="R34" s="39"/>
-      <c r="S34" s="40"/>
+      <c r="Q34" s="38"/>
+      <c r="R34" s="38"/>
+      <c r="S34" s="39"/>
     </row>
     <row r="35" spans="1:19" s="16" customFormat="1" ht="21" customHeight="1">
       <c r="A35" s="9">
         <v>30</v>
       </c>
-      <c r="B35" s="165"/>
-      <c r="C35" s="167"/>
+      <c r="B35" s="145"/>
+      <c r="C35" s="147"/>
       <c r="D35" s="10">
         <v>4</v>
       </c>
@@ -24516,22 +24998,22 @@
       <c r="J35" s="9"/>
       <c r="K35" s="9"/>
       <c r="L35" s="20"/>
-      <c r="M35" s="171" t="s">
+      <c r="M35" s="151" t="s">
         <v>31</v>
       </c>
-      <c r="N35" s="172"/>
-      <c r="O35" s="172"/>
-      <c r="P35" s="172"/>
-      <c r="Q35" s="172"/>
-      <c r="R35" s="172"/>
-      <c r="S35" s="173"/>
+      <c r="N35" s="152"/>
+      <c r="O35" s="152"/>
+      <c r="P35" s="152"/>
+      <c r="Q35" s="152"/>
+      <c r="R35" s="152"/>
+      <c r="S35" s="153"/>
     </row>
     <row r="36" spans="1:19" s="16" customFormat="1" ht="30" customHeight="1">
       <c r="A36" s="9">
         <v>31</v>
       </c>
-      <c r="B36" s="165"/>
-      <c r="C36" s="167"/>
+      <c r="B36" s="145"/>
+      <c r="C36" s="147"/>
       <c r="D36" s="10">
         <v>5</v>
       </c>
@@ -24557,24 +25039,24 @@
       <c r="J36" s="9"/>
       <c r="K36" s="9"/>
       <c r="L36" s="20"/>
-      <c r="M36" s="43"/>
-      <c r="N36" s="132" t="s">
+      <c r="M36" s="42"/>
+      <c r="N36" s="178" t="s">
         <v>74</v>
       </c>
-      <c r="O36" s="132"/>
-      <c r="P36" s="132"/>
-      <c r="Q36" s="132"/>
-      <c r="R36" s="132" t="s">
+      <c r="O36" s="178"/>
+      <c r="P36" s="178"/>
+      <c r="Q36" s="178"/>
+      <c r="R36" s="178" t="s">
         <v>75</v>
       </c>
-      <c r="S36" s="133"/>
+      <c r="S36" s="179"/>
     </row>
     <row r="37" spans="1:19" s="16" customFormat="1" ht="30" customHeight="1">
       <c r="A37" s="9">
         <v>32</v>
       </c>
-      <c r="B37" s="165"/>
-      <c r="C37" s="167"/>
+      <c r="B37" s="145"/>
+      <c r="C37" s="147"/>
       <c r="D37" s="10">
         <v>6</v>
       </c>
@@ -24600,7 +25082,7 @@
       <c r="J37" s="9"/>
       <c r="K37" s="9"/>
       <c r="L37" s="20"/>
-      <c r="M37" s="43">
+      <c r="M37" s="42">
         <v>1</v>
       </c>
       <c r="N37" s="14"/>
@@ -24608,14 +25090,14 @@
       <c r="P37" s="14"/>
       <c r="Q37" s="14"/>
       <c r="R37" s="14"/>
-      <c r="S37" s="122"/>
+      <c r="S37" s="121"/>
     </row>
     <row r="38" spans="1:19" s="16" customFormat="1" ht="30" customHeight="1">
       <c r="A38" s="9">
         <v>33</v>
       </c>
-      <c r="B38" s="165"/>
-      <c r="C38" s="167"/>
+      <c r="B38" s="145"/>
+      <c r="C38" s="147"/>
       <c r="D38" s="10">
         <v>7</v>
       </c>
@@ -24641,7 +25123,7 @@
       <c r="J38" s="9"/>
       <c r="K38" s="9"/>
       <c r="L38" s="20"/>
-      <c r="M38" s="43">
+      <c r="M38" s="42">
         <v>2</v>
       </c>
       <c r="N38" s="14"/>
@@ -24649,15 +25131,15 @@
       <c r="P38" s="14"/>
       <c r="Q38" s="14"/>
       <c r="R38" s="14"/>
-      <c r="S38" s="122"/>
+      <c r="S38" s="121"/>
     </row>
     <row r="39" spans="1:19" s="16" customFormat="1" ht="30" customHeight="1">
       <c r="A39" s="9">
         <v>34</v>
       </c>
-      <c r="B39" s="165"/>
-      <c r="C39" s="167"/>
-      <c r="D39" s="46">
+      <c r="B39" s="145"/>
+      <c r="C39" s="147"/>
+      <c r="D39" s="45">
         <v>13</v>
       </c>
       <c r="E39" s="11">
@@ -24682,7 +25164,7 @@
       <c r="J39" s="9"/>
       <c r="K39" s="9"/>
       <c r="L39" s="20"/>
-      <c r="M39" s="43">
+      <c r="M39" s="42">
         <v>3</v>
       </c>
       <c r="N39" s="14"/>
@@ -24690,14 +25172,14 @@
       <c r="P39" s="14"/>
       <c r="Q39" s="14"/>
       <c r="R39" s="14"/>
-      <c r="S39" s="122"/>
+      <c r="S39" s="121"/>
     </row>
     <row r="40" spans="1:19" s="16" customFormat="1" ht="30" customHeight="1">
       <c r="A40" s="9">
         <v>35</v>
       </c>
-      <c r="B40" s="165"/>
-      <c r="C40" s="174"/>
+      <c r="B40" s="145"/>
+      <c r="C40" s="154"/>
       <c r="D40" s="16">
         <v>14</v>
       </c>
@@ -24723,7 +25205,7 @@
       <c r="J40" s="9"/>
       <c r="K40" s="9"/>
       <c r="L40" s="20"/>
-      <c r="M40" s="43">
+      <c r="M40" s="42">
         <v>4</v>
       </c>
       <c r="N40" s="14"/>
@@ -24731,14 +25213,14 @@
       <c r="P40" s="14"/>
       <c r="Q40" s="14"/>
       <c r="R40" s="14"/>
-      <c r="S40" s="122"/>
+      <c r="S40" s="121"/>
     </row>
     <row r="41" spans="1:19" s="16" customFormat="1" ht="30" customHeight="1">
       <c r="A41" s="9">
         <v>36</v>
       </c>
-      <c r="B41" s="165"/>
-      <c r="C41" s="142" t="s">
+      <c r="B41" s="145"/>
+      <c r="C41" s="155" t="s">
         <v>32</v>
       </c>
       <c r="D41" s="10">
@@ -24766,7 +25248,7 @@
       <c r="J41" s="9"/>
       <c r="K41" s="9"/>
       <c r="L41" s="20"/>
-      <c r="M41" s="43">
+      <c r="M41" s="42">
         <v>5</v>
       </c>
       <c r="N41" s="14"/>
@@ -24774,14 +25256,14 @@
       <c r="P41" s="14"/>
       <c r="Q41" s="14"/>
       <c r="R41" s="14"/>
-      <c r="S41" s="122"/>
+      <c r="S41" s="121"/>
     </row>
     <row r="42" spans="1:19" s="16" customFormat="1" ht="30" customHeight="1">
       <c r="A42" s="9">
         <v>37</v>
       </c>
-      <c r="B42" s="165"/>
-      <c r="C42" s="143"/>
+      <c r="B42" s="145"/>
+      <c r="C42" s="156"/>
       <c r="D42" s="10">
         <v>2</v>
       </c>
@@ -24807,7 +25289,7 @@
       <c r="J42" s="9"/>
       <c r="K42" s="9"/>
       <c r="L42" s="20"/>
-      <c r="M42" s="43">
+      <c r="M42" s="42">
         <v>6</v>
       </c>
       <c r="N42" s="14"/>
@@ -24815,18 +25297,18 @@
       <c r="P42" s="14"/>
       <c r="Q42" s="14"/>
       <c r="R42" s="14"/>
-      <c r="S42" s="122"/>
+      <c r="S42" s="121"/>
     </row>
     <row r="43" spans="1:19" s="16" customFormat="1" ht="30" customHeight="1">
       <c r="A43" s="9">
         <v>38</v>
       </c>
-      <c r="B43" s="165"/>
-      <c r="C43" s="143"/>
+      <c r="B43" s="145"/>
+      <c r="C43" s="156"/>
       <c r="D43" s="10">
         <v>3</v>
       </c>
-      <c r="E43" s="47">
+      <c r="E43" s="46">
         <v>1193</v>
       </c>
       <c r="F43" s="12">
@@ -24845,10 +25327,10 @@
         <f t="shared" si="3"/>
         <v>4.0271999999999997</v>
       </c>
-      <c r="J43" s="48"/>
-      <c r="K43" s="48"/>
-      <c r="L43" s="49"/>
-      <c r="M43" s="43">
+      <c r="J43" s="47"/>
+      <c r="K43" s="47"/>
+      <c r="L43" s="48"/>
+      <c r="M43" s="42">
         <v>7</v>
       </c>
       <c r="N43" s="14"/>
@@ -24856,18 +25338,18 @@
       <c r="P43" s="14"/>
       <c r="Q43" s="14"/>
       <c r="R43" s="14"/>
-      <c r="S43" s="122"/>
+      <c r="S43" s="121"/>
     </row>
     <row r="44" spans="1:19" s="16" customFormat="1" ht="30" customHeight="1">
       <c r="A44" s="9">
         <v>39</v>
       </c>
-      <c r="B44" s="165"/>
-      <c r="C44" s="143"/>
+      <c r="B44" s="145"/>
+      <c r="C44" s="156"/>
       <c r="D44" s="10">
         <v>5</v>
       </c>
-      <c r="E44" s="47">
+      <c r="E44" s="46">
         <v>9437</v>
       </c>
       <c r="F44" s="12">
@@ -24886,10 +25368,10 @@
         <f t="shared" ref="I44:I68" si="9">VLOOKUP(E44,ддд,5,FALSE)</f>
         <v>3.3559999999999999</v>
       </c>
-      <c r="J44" s="50"/>
-      <c r="K44" s="50"/>
-      <c r="L44" s="51"/>
-      <c r="M44" s="43">
+      <c r="J44" s="49"/>
+      <c r="K44" s="49"/>
+      <c r="L44" s="50"/>
+      <c r="M44" s="42">
         <v>8</v>
       </c>
       <c r="N44" s="14"/>
@@ -24897,18 +25379,18 @@
       <c r="P44" s="14"/>
       <c r="Q44" s="14"/>
       <c r="R44" s="14"/>
-      <c r="S44" s="122"/>
+      <c r="S44" s="121"/>
     </row>
     <row r="45" spans="1:19" s="16" customFormat="1" ht="21" customHeight="1">
       <c r="A45" s="9">
         <v>40</v>
       </c>
-      <c r="B45" s="165"/>
-      <c r="C45" s="143"/>
+      <c r="B45" s="145"/>
+      <c r="C45" s="156"/>
       <c r="D45" s="10">
         <v>6</v>
       </c>
-      <c r="E45" s="47">
+      <c r="E45" s="46">
         <v>9684</v>
       </c>
       <c r="F45" s="12">
@@ -24927,29 +25409,29 @@
         <f t="shared" si="9"/>
         <v>8.39</v>
       </c>
-      <c r="J45" s="50"/>
-      <c r="K45" s="50"/>
-      <c r="L45" s="51"/>
-      <c r="M45" s="43">
+      <c r="J45" s="49"/>
+      <c r="K45" s="49"/>
+      <c r="L45" s="50"/>
+      <c r="M45" s="42">
         <v>9</v>
       </c>
-      <c r="N45" s="44"/>
-      <c r="O45" s="44"/>
-      <c r="P45" s="44"/>
-      <c r="Q45" s="44"/>
-      <c r="R45" s="44"/>
-      <c r="S45" s="45"/>
+      <c r="N45" s="43"/>
+      <c r="O45" s="43"/>
+      <c r="P45" s="43"/>
+      <c r="Q45" s="43"/>
+      <c r="R45" s="43"/>
+      <c r="S45" s="44"/>
     </row>
     <row r="46" spans="1:19" s="16" customFormat="1" ht="21" customHeight="1" thickBot="1">
       <c r="A46" s="9">
         <v>41</v>
       </c>
-      <c r="B46" s="165"/>
-      <c r="C46" s="143"/>
+      <c r="B46" s="145"/>
+      <c r="C46" s="156"/>
       <c r="D46" s="10">
         <v>7</v>
       </c>
-      <c r="E46" s="52">
+      <c r="E46" s="51">
         <v>9810</v>
       </c>
       <c r="F46" s="12">
@@ -24968,27 +25450,27 @@
         <f t="shared" si="9"/>
         <v>13.423999999999999</v>
       </c>
-      <c r="J46" s="50"/>
-      <c r="K46" s="50"/>
-      <c r="L46" s="51"/>
-      <c r="M46" s="43"/>
-      <c r="N46" s="44"/>
-      <c r="O46" s="44"/>
-      <c r="P46" s="44"/>
-      <c r="Q46" s="44"/>
-      <c r="R46" s="44"/>
-      <c r="S46" s="45"/>
+      <c r="J46" s="49"/>
+      <c r="K46" s="49"/>
+      <c r="L46" s="50"/>
+      <c r="M46" s="42"/>
+      <c r="N46" s="43"/>
+      <c r="O46" s="43"/>
+      <c r="P46" s="43"/>
+      <c r="Q46" s="43"/>
+      <c r="R46" s="43"/>
+      <c r="S46" s="44"/>
     </row>
     <row r="47" spans="1:19" s="16" customFormat="1" ht="21" customHeight="1">
       <c r="A47" s="9">
         <v>42</v>
       </c>
-      <c r="B47" s="165"/>
-      <c r="C47" s="143"/>
+      <c r="B47" s="145"/>
+      <c r="C47" s="156"/>
       <c r="D47" s="10">
         <v>9</v>
       </c>
-      <c r="E47" s="52">
+      <c r="E47" s="51">
         <v>6084</v>
       </c>
       <c r="F47" s="12">
@@ -25007,29 +25489,29 @@
         <f t="shared" si="9"/>
         <v>1.6779999999999999</v>
       </c>
-      <c r="J47" s="50"/>
-      <c r="K47" s="50"/>
-      <c r="L47" s="51"/>
-      <c r="M47" s="171" t="s">
+      <c r="J47" s="49"/>
+      <c r="K47" s="49"/>
+      <c r="L47" s="50"/>
+      <c r="M47" s="151" t="s">
         <v>33</v>
       </c>
-      <c r="N47" s="172"/>
-      <c r="O47" s="172"/>
-      <c r="P47" s="172"/>
-      <c r="Q47" s="172"/>
-      <c r="R47" s="172"/>
-      <c r="S47" s="173"/>
+      <c r="N47" s="152"/>
+      <c r="O47" s="152"/>
+      <c r="P47" s="152"/>
+      <c r="Q47" s="152"/>
+      <c r="R47" s="152"/>
+      <c r="S47" s="153"/>
     </row>
     <row r="48" spans="1:19" s="16" customFormat="1" ht="21" customHeight="1">
       <c r="A48" s="9">
         <v>43</v>
       </c>
-      <c r="B48" s="165"/>
-      <c r="C48" s="143"/>
+      <c r="B48" s="145"/>
+      <c r="C48" s="156"/>
       <c r="D48" s="10">
         <v>10</v>
       </c>
-      <c r="E48" s="52">
+      <c r="E48" s="51">
         <v>5602</v>
       </c>
       <c r="F48" s="12">
@@ -25048,28 +25530,28 @@
         <f t="shared" si="9"/>
         <v>25.17</v>
       </c>
-      <c r="J48" s="50"/>
-      <c r="K48" s="50"/>
-      <c r="L48" s="51"/>
-      <c r="M48" s="109" t="s">
+      <c r="J48" s="49"/>
+      <c r="K48" s="49"/>
+      <c r="L48" s="50"/>
+      <c r="M48" s="108" t="s">
         <v>70</v>
       </c>
-      <c r="N48" s="109" t="s">
+      <c r="N48" s="108" t="s">
         <v>71</v>
       </c>
-      <c r="O48" s="109" t="s">
+      <c r="O48" s="108" t="s">
         <v>70</v>
       </c>
-      <c r="P48" s="109" t="s">
+      <c r="P48" s="108" t="s">
         <v>71</v>
       </c>
-      <c r="Q48" s="109" t="s">
+      <c r="Q48" s="108" t="s">
         <v>70</v>
       </c>
-      <c r="R48" s="109" t="s">
+      <c r="R48" s="108" t="s">
         <v>71</v>
       </c>
-      <c r="S48" s="110" t="s">
+      <c r="S48" s="109" t="s">
         <v>14</v>
       </c>
     </row>
@@ -25077,12 +25559,12 @@
       <c r="A49" s="9">
         <v>44</v>
       </c>
-      <c r="B49" s="165"/>
-      <c r="C49" s="143"/>
-      <c r="D49" s="56">
+      <c r="B49" s="145"/>
+      <c r="C49" s="156"/>
+      <c r="D49" s="55">
         <v>11</v>
       </c>
-      <c r="E49" s="47">
+      <c r="E49" s="46">
         <v>6443</v>
       </c>
       <c r="F49" s="12">
@@ -25101,27 +25583,27 @@
         <f t="shared" si="9"/>
         <v>6.2925000000000004</v>
       </c>
-      <c r="J49" s="50"/>
-      <c r="K49" s="50"/>
-      <c r="L49" s="51"/>
-      <c r="M49" s="30"/>
-      <c r="N49" s="32"/>
-      <c r="O49" s="32"/>
-      <c r="P49" s="32"/>
-      <c r="Q49" s="32"/>
-      <c r="R49" s="32"/>
-      <c r="S49" s="34"/>
+      <c r="J49" s="49"/>
+      <c r="K49" s="49"/>
+      <c r="L49" s="50"/>
+      <c r="M49" s="29"/>
+      <c r="N49" s="31"/>
+      <c r="O49" s="31"/>
+      <c r="P49" s="31"/>
+      <c r="Q49" s="31"/>
+      <c r="R49" s="31"/>
+      <c r="S49" s="33"/>
     </row>
     <row r="50" spans="1:19" ht="21" customHeight="1">
       <c r="A50" s="9">
         <v>45</v>
       </c>
-      <c r="B50" s="165"/>
-      <c r="C50" s="143"/>
+      <c r="B50" s="145"/>
+      <c r="C50" s="156"/>
       <c r="D50" s="10">
         <v>13</v>
       </c>
-      <c r="E50" s="47">
+      <c r="E50" s="46">
         <v>5671</v>
       </c>
       <c r="F50" s="12">
@@ -25140,29 +25622,29 @@
         <f t="shared" si="9"/>
         <v>3.6915999999999998</v>
       </c>
-      <c r="J50" s="50"/>
-      <c r="K50" s="50"/>
-      <c r="L50" s="51"/>
-      <c r="M50" s="30"/>
-      <c r="N50" s="32"/>
-      <c r="O50" s="32"/>
-      <c r="P50" s="32"/>
-      <c r="Q50" s="32"/>
-      <c r="R50" s="32"/>
-      <c r="S50" s="34"/>
+      <c r="J50" s="49"/>
+      <c r="K50" s="49"/>
+      <c r="L50" s="50"/>
+      <c r="M50" s="29"/>
+      <c r="N50" s="31"/>
+      <c r="O50" s="31"/>
+      <c r="P50" s="31"/>
+      <c r="Q50" s="31"/>
+      <c r="R50" s="31"/>
+      <c r="S50" s="33"/>
     </row>
     <row r="51" spans="1:19" ht="21" customHeight="1">
       <c r="A51" s="9">
         <v>46</v>
       </c>
-      <c r="B51" s="165"/>
-      <c r="C51" s="142" t="s">
+      <c r="B51" s="145"/>
+      <c r="C51" s="155" t="s">
         <v>34</v>
       </c>
       <c r="D51" s="10">
         <v>1</v>
       </c>
-      <c r="E51" s="47">
+      <c r="E51" s="46">
         <v>8250</v>
       </c>
       <c r="F51" s="12">
@@ -25181,27 +25663,27 @@
         <f t="shared" si="9"/>
         <v>7.5510000000000002</v>
       </c>
-      <c r="J51" s="50"/>
-      <c r="K51" s="50"/>
-      <c r="L51" s="51"/>
-      <c r="M51" s="57"/>
-      <c r="N51" s="46"/>
-      <c r="O51" s="46"/>
-      <c r="P51" s="46"/>
-      <c r="Q51" s="46"/>
-      <c r="R51" s="46"/>
-      <c r="S51" s="58"/>
+      <c r="J51" s="49"/>
+      <c r="K51" s="49"/>
+      <c r="L51" s="50"/>
+      <c r="M51" s="56"/>
+      <c r="N51" s="45"/>
+      <c r="O51" s="45"/>
+      <c r="P51" s="45"/>
+      <c r="Q51" s="45"/>
+      <c r="R51" s="45"/>
+      <c r="S51" s="57"/>
     </row>
     <row r="52" spans="1:19" ht="21" customHeight="1" thickBot="1">
       <c r="A52" s="9">
         <v>47</v>
       </c>
-      <c r="B52" s="165"/>
-      <c r="C52" s="143"/>
-      <c r="D52" s="59">
+      <c r="B52" s="145"/>
+      <c r="C52" s="156"/>
+      <c r="D52" s="58">
         <v>2</v>
       </c>
-      <c r="E52" s="47">
+      <c r="E52" s="46">
         <v>7504</v>
       </c>
       <c r="F52" s="12">
@@ -25220,27 +25702,27 @@
         <f t="shared" si="9"/>
         <v>1.88775</v>
       </c>
-      <c r="J52" s="50"/>
-      <c r="K52" s="50"/>
-      <c r="L52" s="51"/>
-      <c r="M52" s="60"/>
-      <c r="N52" s="61"/>
-      <c r="O52" s="61"/>
-      <c r="P52" s="61"/>
-      <c r="Q52" s="61"/>
-      <c r="R52" s="61"/>
-      <c r="S52" s="62"/>
+      <c r="J52" s="49"/>
+      <c r="K52" s="49"/>
+      <c r="L52" s="50"/>
+      <c r="M52" s="59"/>
+      <c r="N52" s="60"/>
+      <c r="O52" s="60"/>
+      <c r="P52" s="60"/>
+      <c r="Q52" s="60"/>
+      <c r="R52" s="60"/>
+      <c r="S52" s="61"/>
     </row>
     <row r="53" spans="1:19" ht="21" customHeight="1">
       <c r="A53" s="9">
         <v>48</v>
       </c>
-      <c r="B53" s="165"/>
-      <c r="C53" s="143"/>
-      <c r="D53" s="59">
+      <c r="B53" s="145"/>
+      <c r="C53" s="156"/>
+      <c r="D53" s="58">
         <v>3</v>
       </c>
-      <c r="E53" s="47">
+      <c r="E53" s="46">
         <v>3834</v>
       </c>
       <c r="F53" s="12">
@@ -25259,29 +25741,29 @@
         <f t="shared" si="9"/>
         <v>7.3412499999999996</v>
       </c>
-      <c r="J53" s="50"/>
-      <c r="K53" s="50"/>
-      <c r="L53" s="51"/>
-      <c r="M53" s="176" t="s">
+      <c r="J53" s="49"/>
+      <c r="K53" s="49"/>
+      <c r="L53" s="50"/>
+      <c r="M53" s="158" t="s">
         <v>35</v>
       </c>
-      <c r="N53" s="177"/>
-      <c r="O53" s="177"/>
-      <c r="P53" s="177"/>
-      <c r="Q53" s="177"/>
-      <c r="R53" s="177"/>
-      <c r="S53" s="178"/>
+      <c r="N53" s="159"/>
+      <c r="O53" s="159"/>
+      <c r="P53" s="159"/>
+      <c r="Q53" s="159"/>
+      <c r="R53" s="159"/>
+      <c r="S53" s="160"/>
     </row>
     <row r="54" spans="1:19" ht="21" customHeight="1">
       <c r="A54" s="9">
         <v>49</v>
       </c>
-      <c r="B54" s="165"/>
-      <c r="C54" s="143"/>
-      <c r="D54" s="59">
+      <c r="B54" s="145"/>
+      <c r="C54" s="156"/>
+      <c r="D54" s="58">
         <v>4</v>
       </c>
-      <c r="E54" s="47">
+      <c r="E54" s="46">
         <v>9811</v>
       </c>
       <c r="F54" s="12">
@@ -25300,27 +25782,27 @@
         <f t="shared" si="9"/>
         <v>5.8729999999999993</v>
       </c>
-      <c r="J54" s="50"/>
-      <c r="K54" s="50"/>
-      <c r="L54" s="51"/>
-      <c r="M54" s="63"/>
-      <c r="N54" s="64"/>
-      <c r="O54" s="64"/>
-      <c r="P54" s="64"/>
-      <c r="Q54" s="64"/>
-      <c r="R54" s="64"/>
-      <c r="S54" s="65"/>
+      <c r="J54" s="49"/>
+      <c r="K54" s="49"/>
+      <c r="L54" s="50"/>
+      <c r="M54" s="62"/>
+      <c r="N54" s="63"/>
+      <c r="O54" s="63"/>
+      <c r="P54" s="63"/>
+      <c r="Q54" s="63"/>
+      <c r="R54" s="63"/>
+      <c r="S54" s="64"/>
     </row>
     <row r="55" spans="1:19" ht="21" customHeight="1">
       <c r="A55" s="9">
         <v>50</v>
       </c>
-      <c r="B55" s="165"/>
-      <c r="C55" s="143"/>
-      <c r="D55" s="59">
+      <c r="B55" s="145"/>
+      <c r="C55" s="156"/>
+      <c r="D55" s="58">
         <v>5</v>
       </c>
-      <c r="E55" s="47">
+      <c r="E55" s="46">
         <v>9686</v>
       </c>
       <c r="F55" s="12">
@@ -25339,27 +25821,27 @@
         <f t="shared" si="9"/>
         <v>7.5510000000000002</v>
       </c>
-      <c r="J55" s="50"/>
-      <c r="K55" s="50"/>
-      <c r="L55" s="51"/>
-      <c r="M55" s="63"/>
-      <c r="N55" s="64"/>
-      <c r="O55" s="64"/>
-      <c r="P55" s="64"/>
-      <c r="Q55" s="64"/>
-      <c r="R55" s="64"/>
-      <c r="S55" s="65"/>
+      <c r="J55" s="49"/>
+      <c r="K55" s="49"/>
+      <c r="L55" s="50"/>
+      <c r="M55" s="62"/>
+      <c r="N55" s="63"/>
+      <c r="O55" s="63"/>
+      <c r="P55" s="63"/>
+      <c r="Q55" s="63"/>
+      <c r="R55" s="63"/>
+      <c r="S55" s="64"/>
     </row>
     <row r="56" spans="1:19" ht="21" customHeight="1">
       <c r="A56" s="9">
         <v>51</v>
       </c>
-      <c r="B56" s="165"/>
-      <c r="C56" s="143"/>
-      <c r="D56" s="59">
+      <c r="B56" s="145"/>
+      <c r="C56" s="156"/>
+      <c r="D56" s="58">
         <v>6</v>
       </c>
-      <c r="E56" s="47">
+      <c r="E56" s="46">
         <v>8346</v>
       </c>
       <c r="F56" s="12">
@@ -25378,27 +25860,27 @@
         <f t="shared" si="9"/>
         <v>11.745999999999999</v>
       </c>
-      <c r="J56" s="50"/>
-      <c r="K56" s="50"/>
-      <c r="L56" s="51"/>
-      <c r="M56" s="63"/>
-      <c r="N56" s="64"/>
-      <c r="O56" s="64"/>
-      <c r="P56" s="64"/>
-      <c r="Q56" s="64"/>
-      <c r="R56" s="64"/>
-      <c r="S56" s="65"/>
+      <c r="J56" s="49"/>
+      <c r="K56" s="49"/>
+      <c r="L56" s="50"/>
+      <c r="M56" s="62"/>
+      <c r="N56" s="63"/>
+      <c r="O56" s="63"/>
+      <c r="P56" s="63"/>
+      <c r="Q56" s="63"/>
+      <c r="R56" s="63"/>
+      <c r="S56" s="64"/>
     </row>
     <row r="57" spans="1:19" ht="21" customHeight="1" thickBot="1">
       <c r="A57" s="9">
         <v>52</v>
       </c>
-      <c r="B57" s="165"/>
-      <c r="C57" s="143"/>
-      <c r="D57" s="59">
+      <c r="B57" s="145"/>
+      <c r="C57" s="156"/>
+      <c r="D57" s="58">
         <v>7</v>
       </c>
-      <c r="E57" s="47">
+      <c r="E57" s="46">
         <v>9796</v>
       </c>
       <c r="F57" s="12">
@@ -25417,27 +25899,27 @@
         <f t="shared" si="9"/>
         <v>5.2437500000000004</v>
       </c>
-      <c r="J57" s="50"/>
-      <c r="K57" s="50"/>
-      <c r="L57" s="51"/>
-      <c r="M57" s="63"/>
-      <c r="N57" s="64"/>
-      <c r="O57" s="64"/>
-      <c r="P57" s="64"/>
-      <c r="Q57" s="64"/>
-      <c r="R57" s="64"/>
-      <c r="S57" s="65"/>
+      <c r="J57" s="49"/>
+      <c r="K57" s="49"/>
+      <c r="L57" s="50"/>
+      <c r="M57" s="62"/>
+      <c r="N57" s="63"/>
+      <c r="O57" s="63"/>
+      <c r="P57" s="63"/>
+      <c r="Q57" s="63"/>
+      <c r="R57" s="63"/>
+      <c r="S57" s="64"/>
     </row>
     <row r="58" spans="1:19" ht="21" customHeight="1">
       <c r="A58" s="9">
         <v>53</v>
       </c>
-      <c r="B58" s="165"/>
-      <c r="C58" s="143"/>
-      <c r="D58" s="59">
+      <c r="B58" s="145"/>
+      <c r="C58" s="156"/>
+      <c r="D58" s="58">
         <v>8</v>
       </c>
-      <c r="E58" s="47">
+      <c r="E58" s="46">
         <v>6604</v>
       </c>
       <c r="F58" s="12">
@@ -25456,31 +25938,31 @@
         <f t="shared" si="9"/>
         <v>3.7755000000000001</v>
       </c>
-      <c r="J58" s="50"/>
-      <c r="K58" s="50"/>
-      <c r="L58" s="51"/>
-      <c r="M58" s="66" t="s">
+      <c r="J58" s="49"/>
+      <c r="K58" s="49"/>
+      <c r="L58" s="50"/>
+      <c r="M58" s="65" t="s">
         <v>36</v>
       </c>
-      <c r="N58" s="67"/>
-      <c r="O58" s="67"/>
-      <c r="P58" s="134" t="s">
+      <c r="N58" s="66"/>
+      <c r="O58" s="66"/>
+      <c r="P58" s="180" t="s">
         <v>78</v>
       </c>
-      <c r="Q58" s="135"/>
-      <c r="R58" s="135"/>
-      <c r="S58" s="136"/>
+      <c r="Q58" s="162"/>
+      <c r="R58" s="162"/>
+      <c r="S58" s="163"/>
     </row>
     <row r="59" spans="1:19" ht="21" customHeight="1">
       <c r="A59" s="9">
         <v>54</v>
       </c>
-      <c r="B59" s="165"/>
-      <c r="C59" s="143"/>
-      <c r="D59" s="59">
+      <c r="B59" s="145"/>
+      <c r="C59" s="156"/>
+      <c r="D59" s="58">
         <v>9</v>
       </c>
-      <c r="E59" s="47">
+      <c r="E59" s="46">
         <v>9685</v>
       </c>
       <c r="F59" s="12">
@@ -25499,33 +25981,33 @@
         <f t="shared" si="9"/>
         <v>6.3764000000000003</v>
       </c>
-      <c r="J59" s="50"/>
-      <c r="K59" s="50"/>
-      <c r="L59" s="51"/>
-      <c r="M59" s="53">
+      <c r="J59" s="49"/>
+      <c r="K59" s="49"/>
+      <c r="L59" s="50"/>
+      <c r="M59" s="52">
         <v>1</v>
       </c>
-      <c r="N59" s="54"/>
-      <c r="O59" s="54"/>
-      <c r="P59" s="54">
+      <c r="N59" s="53"/>
+      <c r="O59" s="53"/>
+      <c r="P59" s="53">
         <v>1</v>
       </c>
-      <c r="Q59" s="54"/>
-      <c r="R59" s="54">
+      <c r="Q59" s="53"/>
+      <c r="R59" s="53">
         <v>4</v>
       </c>
-      <c r="S59" s="55"/>
+      <c r="S59" s="54"/>
     </row>
     <row r="60" spans="1:19" ht="21" customHeight="1">
       <c r="A60" s="9">
         <v>55</v>
       </c>
-      <c r="B60" s="165"/>
-      <c r="C60" s="143"/>
-      <c r="D60" s="59">
+      <c r="B60" s="145"/>
+      <c r="C60" s="156"/>
+      <c r="D60" s="58">
         <v>10</v>
       </c>
-      <c r="E60" s="47">
+      <c r="E60" s="46">
         <v>6865</v>
       </c>
       <c r="F60" s="12">
@@ -25544,33 +26026,33 @@
         <f t="shared" si="9"/>
         <v>3.2301500000000001</v>
       </c>
-      <c r="J60" s="50"/>
-      <c r="K60" s="50"/>
-      <c r="L60" s="51"/>
-      <c r="M60" s="53">
+      <c r="J60" s="49"/>
+      <c r="K60" s="49"/>
+      <c r="L60" s="50"/>
+      <c r="M60" s="52">
         <v>2</v>
       </c>
-      <c r="N60" s="54"/>
-      <c r="O60" s="54"/>
-      <c r="P60" s="54">
+      <c r="N60" s="53"/>
+      <c r="O60" s="53"/>
+      <c r="P60" s="53">
         <v>2</v>
       </c>
-      <c r="Q60" s="54"/>
-      <c r="R60" s="54">
+      <c r="Q60" s="53"/>
+      <c r="R60" s="53">
         <v>5</v>
       </c>
-      <c r="S60" s="55"/>
+      <c r="S60" s="54"/>
     </row>
     <row r="61" spans="1:19" ht="21" customHeight="1" thickBot="1">
       <c r="A61" s="9">
         <v>56</v>
       </c>
-      <c r="B61" s="165"/>
-      <c r="C61" s="143"/>
-      <c r="D61" s="59">
+      <c r="B61" s="145"/>
+      <c r="C61" s="156"/>
+      <c r="D61" s="58">
         <v>11</v>
       </c>
-      <c r="E61" s="47">
+      <c r="E61" s="46">
         <v>7968</v>
       </c>
       <c r="F61" s="12">
@@ -25589,33 +26071,33 @@
         <f t="shared" si="9"/>
         <v>6.2925000000000004</v>
       </c>
-      <c r="J61" s="50"/>
-      <c r="K61" s="50"/>
-      <c r="L61" s="51"/>
-      <c r="M61" s="68">
+      <c r="J61" s="49"/>
+      <c r="K61" s="49"/>
+      <c r="L61" s="50"/>
+      <c r="M61" s="67">
         <v>3</v>
       </c>
-      <c r="N61" s="69"/>
-      <c r="O61" s="69"/>
-      <c r="P61" s="69">
+      <c r="N61" s="68"/>
+      <c r="O61" s="68"/>
+      <c r="P61" s="68">
         <v>3</v>
       </c>
-      <c r="Q61" s="69"/>
-      <c r="R61" s="69">
+      <c r="Q61" s="68"/>
+      <c r="R61" s="68">
         <v>6</v>
       </c>
-      <c r="S61" s="70"/>
+      <c r="S61" s="69"/>
     </row>
     <row r="62" spans="1:19" ht="21" customHeight="1">
       <c r="A62" s="9">
         <v>57</v>
       </c>
-      <c r="B62" s="165"/>
-      <c r="C62" s="143"/>
-      <c r="D62" s="71">
+      <c r="B62" s="145"/>
+      <c r="C62" s="156"/>
+      <c r="D62" s="70">
         <v>12</v>
       </c>
-      <c r="E62" s="47">
+      <c r="E62" s="46">
         <v>3833</v>
       </c>
       <c r="F62" s="12">
@@ -25634,29 +26116,29 @@
         <f t="shared" si="9"/>
         <v>4.1950000000000003</v>
       </c>
-      <c r="J62" s="50"/>
-      <c r="K62" s="50"/>
-      <c r="L62" s="51"/>
-      <c r="M62" s="160" t="s">
+      <c r="J62" s="49"/>
+      <c r="K62" s="49"/>
+      <c r="L62" s="50"/>
+      <c r="M62" s="161" t="s">
         <v>77</v>
       </c>
-      <c r="N62" s="135"/>
-      <c r="O62" s="135"/>
-      <c r="P62" s="135"/>
-      <c r="Q62" s="135"/>
-      <c r="R62" s="135"/>
-      <c r="S62" s="136"/>
+      <c r="N62" s="162"/>
+      <c r="O62" s="162"/>
+      <c r="P62" s="162"/>
+      <c r="Q62" s="162"/>
+      <c r="R62" s="162"/>
+      <c r="S62" s="163"/>
     </row>
     <row r="63" spans="1:19" ht="26.25" customHeight="1" thickBot="1">
       <c r="A63" s="9">
         <v>58</v>
       </c>
-      <c r="B63" s="165"/>
-      <c r="C63" s="143"/>
-      <c r="D63" s="59">
+      <c r="B63" s="145"/>
+      <c r="C63" s="156"/>
+      <c r="D63" s="58">
         <v>13</v>
       </c>
-      <c r="E63" s="47">
+      <c r="E63" s="46">
         <v>6315</v>
       </c>
       <c r="F63" s="12">
@@ -25675,27 +26157,27 @@
         <f t="shared" si="9"/>
         <v>6.2925000000000004</v>
       </c>
-      <c r="J63" s="50"/>
-      <c r="K63" s="50"/>
-      <c r="L63" s="51"/>
-      <c r="M63" s="123"/>
-      <c r="N63" s="124"/>
-      <c r="O63" s="124"/>
-      <c r="P63" s="124"/>
-      <c r="Q63" s="124"/>
-      <c r="R63" s="124"/>
-      <c r="S63" s="125"/>
+      <c r="J63" s="49"/>
+      <c r="K63" s="49"/>
+      <c r="L63" s="50"/>
+      <c r="M63" s="122"/>
+      <c r="N63" s="123"/>
+      <c r="O63" s="123"/>
+      <c r="P63" s="123"/>
+      <c r="Q63" s="123"/>
+      <c r="R63" s="123"/>
+      <c r="S63" s="124"/>
     </row>
     <row r="64" spans="1:19">
       <c r="A64" s="9">
         <v>59</v>
       </c>
-      <c r="B64" s="72"/>
-      <c r="C64" s="175"/>
-      <c r="D64" s="59">
+      <c r="B64" s="71"/>
+      <c r="C64" s="157"/>
+      <c r="D64" s="58">
         <v>14</v>
       </c>
-      <c r="E64" s="47">
+      <c r="E64" s="46">
         <v>2590</v>
       </c>
       <c r="F64" s="12">
@@ -25714,31 +26196,31 @@
         <f t="shared" si="9"/>
         <v>7.5510000000000002</v>
       </c>
-      <c r="J64" s="50"/>
-      <c r="K64" s="50"/>
-      <c r="L64" s="51"/>
-      <c r="M64" s="160" t="s">
+      <c r="J64" s="49"/>
+      <c r="K64" s="49"/>
+      <c r="L64" s="50"/>
+      <c r="M64" s="161" t="s">
         <v>37</v>
       </c>
-      <c r="N64" s="135"/>
-      <c r="O64" s="135"/>
-      <c r="P64" s="135"/>
-      <c r="Q64" s="135"/>
-      <c r="R64" s="135"/>
-      <c r="S64" s="136"/>
+      <c r="N64" s="162"/>
+      <c r="O64" s="162"/>
+      <c r="P64" s="162"/>
+      <c r="Q64" s="162"/>
+      <c r="R64" s="162"/>
+      <c r="S64" s="163"/>
     </row>
     <row r="65" spans="1:19" ht="21" customHeight="1">
       <c r="A65" s="9">
         <v>60</v>
       </c>
-      <c r="B65" s="72"/>
-      <c r="C65" s="142" t="s">
+      <c r="B65" s="71"/>
+      <c r="C65" s="155" t="s">
         <v>38</v>
       </c>
       <c r="D65" s="10">
         <v>1</v>
       </c>
-      <c r="E65" s="47">
+      <c r="E65" s="46">
         <v>7510</v>
       </c>
       <c r="F65" s="12">
@@ -25757,27 +26239,27 @@
         <f t="shared" si="9"/>
         <v>8.39</v>
       </c>
-      <c r="J65" s="50"/>
-      <c r="K65" s="50"/>
-      <c r="L65" s="51"/>
-      <c r="M65" s="73"/>
-      <c r="N65" s="74"/>
-      <c r="O65" s="74"/>
-      <c r="P65" s="74"/>
-      <c r="Q65" s="74"/>
-      <c r="R65" s="74"/>
-      <c r="S65" s="75"/>
+      <c r="J65" s="49"/>
+      <c r="K65" s="49"/>
+      <c r="L65" s="50"/>
+      <c r="M65" s="72"/>
+      <c r="N65" s="73"/>
+      <c r="O65" s="73"/>
+      <c r="P65" s="73"/>
+      <c r="Q65" s="73"/>
+      <c r="R65" s="73"/>
+      <c r="S65" s="74"/>
     </row>
     <row r="66" spans="1:19" ht="21" customHeight="1">
       <c r="A66" s="9">
         <v>61</v>
       </c>
-      <c r="B66" s="72"/>
-      <c r="C66" s="143"/>
-      <c r="D66" s="144">
+      <c r="B66" s="71"/>
+      <c r="C66" s="156"/>
+      <c r="D66" s="186">
         <v>2</v>
       </c>
-      <c r="E66" s="47">
+      <c r="E66" s="46">
         <v>8237</v>
       </c>
       <c r="F66" s="12">
@@ -25796,25 +26278,25 @@
         <f t="shared" si="9"/>
         <v>5.6632499999999997</v>
       </c>
-      <c r="J66" s="50"/>
-      <c r="K66" s="50"/>
-      <c r="L66" s="51"/>
-      <c r="M66" s="151"/>
-      <c r="N66" s="152"/>
-      <c r="O66" s="152"/>
-      <c r="P66" s="152"/>
-      <c r="Q66" s="152"/>
-      <c r="R66" s="152"/>
-      <c r="S66" s="153"/>
+      <c r="J66" s="49"/>
+      <c r="K66" s="49"/>
+      <c r="L66" s="50"/>
+      <c r="M66" s="166"/>
+      <c r="N66" s="167"/>
+      <c r="O66" s="167"/>
+      <c r="P66" s="167"/>
+      <c r="Q66" s="167"/>
+      <c r="R66" s="167"/>
+      <c r="S66" s="168"/>
     </row>
     <row r="67" spans="1:19" ht="21" customHeight="1">
       <c r="A67" s="9">
         <v>62</v>
       </c>
-      <c r="B67" s="72"/>
-      <c r="C67" s="143"/>
-      <c r="D67" s="145"/>
-      <c r="E67" s="47">
+      <c r="B67" s="71"/>
+      <c r="C67" s="156"/>
+      <c r="D67" s="187"/>
+      <c r="E67" s="46">
         <v>9456</v>
       </c>
       <c r="F67" s="12">
@@ -25833,27 +26315,27 @@
         <f>VLOOKUP(E67,ддд,5,FALSE)</f>
         <v>5.6632499999999997</v>
       </c>
-      <c r="J67" s="50"/>
-      <c r="K67" s="50"/>
-      <c r="L67" s="51"/>
-      <c r="M67" s="76"/>
-      <c r="N67" s="77"/>
-      <c r="O67" s="77"/>
-      <c r="P67" s="77"/>
-      <c r="Q67" s="77"/>
-      <c r="R67" s="77"/>
-      <c r="S67" s="78"/>
+      <c r="J67" s="49"/>
+      <c r="K67" s="49"/>
+      <c r="L67" s="50"/>
+      <c r="M67" s="75"/>
+      <c r="N67" s="76"/>
+      <c r="O67" s="76"/>
+      <c r="P67" s="76"/>
+      <c r="Q67" s="76"/>
+      <c r="R67" s="76"/>
+      <c r="S67" s="77"/>
     </row>
     <row r="68" spans="1:19" ht="21" customHeight="1" thickBot="1">
       <c r="A68" s="9">
         <v>63</v>
       </c>
-      <c r="B68" s="72"/>
-      <c r="C68" s="143"/>
-      <c r="D68" s="59">
+      <c r="B68" s="71"/>
+      <c r="C68" s="156"/>
+      <c r="D68" s="58">
         <v>3</v>
       </c>
-      <c r="E68" s="47">
+      <c r="E68" s="46">
         <v>7709</v>
       </c>
       <c r="F68" s="12">
@@ -25872,27 +26354,27 @@
         <f t="shared" si="9"/>
         <v>2.3491999999999997</v>
       </c>
-      <c r="J68" s="50"/>
-      <c r="K68" s="50"/>
-      <c r="L68" s="51"/>
-      <c r="M68" s="154"/>
-      <c r="N68" s="155"/>
-      <c r="O68" s="155"/>
-      <c r="P68" s="155"/>
-      <c r="Q68" s="155"/>
-      <c r="R68" s="155"/>
-      <c r="S68" s="156"/>
+      <c r="J68" s="49"/>
+      <c r="K68" s="49"/>
+      <c r="L68" s="50"/>
+      <c r="M68" s="169"/>
+      <c r="N68" s="170"/>
+      <c r="O68" s="170"/>
+      <c r="P68" s="170"/>
+      <c r="Q68" s="170"/>
+      <c r="R68" s="170"/>
+      <c r="S68" s="171"/>
     </row>
     <row r="69" spans="1:19" ht="21" customHeight="1">
       <c r="A69" s="9">
         <v>64</v>
       </c>
-      <c r="B69" s="72"/>
-      <c r="C69" s="143"/>
-      <c r="D69" s="59">
+      <c r="B69" s="71"/>
+      <c r="C69" s="156"/>
+      <c r="D69" s="58">
         <v>6</v>
       </c>
-      <c r="E69" s="47">
+      <c r="E69" s="46">
         <v>8238</v>
       </c>
       <c r="F69" s="12">
@@ -25911,29 +26393,29 @@
         <f t="shared" ref="I69:I75" si="13">VLOOKUP(E69,ддд,5,FALSE)</f>
         <v>6.2925000000000004</v>
       </c>
-      <c r="J69" s="50"/>
-      <c r="K69" s="50"/>
-      <c r="L69" s="51"/>
-      <c r="M69" s="157" t="s">
+      <c r="J69" s="49"/>
+      <c r="K69" s="49"/>
+      <c r="L69" s="50"/>
+      <c r="M69" s="172" t="s">
         <v>39</v>
       </c>
-      <c r="N69" s="158"/>
-      <c r="O69" s="158"/>
-      <c r="P69" s="158"/>
-      <c r="Q69" s="158"/>
-      <c r="R69" s="158"/>
-      <c r="S69" s="159"/>
+      <c r="N69" s="173"/>
+      <c r="O69" s="173"/>
+      <c r="P69" s="173"/>
+      <c r="Q69" s="173"/>
+      <c r="R69" s="173"/>
+      <c r="S69" s="174"/>
     </row>
     <row r="70" spans="1:19" ht="21" customHeight="1">
       <c r="A70" s="9">
         <v>65</v>
       </c>
-      <c r="B70" s="72"/>
-      <c r="C70" s="143"/>
-      <c r="D70" s="59">
+      <c r="B70" s="71"/>
+      <c r="C70" s="156"/>
+      <c r="D70" s="58">
         <v>7</v>
       </c>
-      <c r="E70" s="47">
+      <c r="E70" s="46">
         <v>8239</v>
       </c>
       <c r="F70" s="12">
@@ -25952,28 +26434,28 @@
         <f t="shared" si="13"/>
         <v>5.2437500000000004</v>
       </c>
-      <c r="J70" s="50"/>
-      <c r="K70" s="50"/>
-      <c r="L70" s="51"/>
-      <c r="M70" s="79" t="s">
+      <c r="J70" s="49"/>
+      <c r="K70" s="49"/>
+      <c r="L70" s="50"/>
+      <c r="M70" s="78" t="s">
         <v>40</v>
       </c>
-      <c r="N70" s="80" t="s">
+      <c r="N70" s="79" t="s">
         <v>41</v>
       </c>
-      <c r="O70" s="81" t="s">
+      <c r="O70" s="80" t="s">
         <v>42</v>
       </c>
-      <c r="P70" s="82" t="s">
+      <c r="P70" s="81" t="s">
         <v>43</v>
       </c>
-      <c r="Q70" s="83" t="s">
+      <c r="Q70" s="82" t="s">
         <v>44</v>
       </c>
-      <c r="R70" s="82" t="s">
+      <c r="R70" s="81" t="s">
         <v>45</v>
       </c>
-      <c r="S70" s="84" t="s">
+      <c r="S70" s="83" t="s">
         <v>14</v>
       </c>
     </row>
@@ -25981,12 +26463,12 @@
       <c r="A71" s="9">
         <v>66</v>
       </c>
-      <c r="B71" s="72"/>
-      <c r="C71" s="143"/>
-      <c r="D71" s="59">
+      <c r="B71" s="71"/>
+      <c r="C71" s="156"/>
+      <c r="D71" s="58">
         <v>8</v>
       </c>
-      <c r="E71" s="47">
+      <c r="E71" s="46">
         <v>7509</v>
       </c>
       <c r="F71" s="12">
@@ -26005,29 +26487,29 @@
         <f t="shared" si="13"/>
         <v>2.72675</v>
       </c>
-      <c r="J71" s="50"/>
-      <c r="K71" s="50"/>
-      <c r="L71" s="51"/>
-      <c r="M71" s="85">
+      <c r="J71" s="49"/>
+      <c r="K71" s="49"/>
+      <c r="L71" s="50"/>
+      <c r="M71" s="84">
         <v>1</v>
       </c>
-      <c r="N71" s="86"/>
-      <c r="O71" s="86"/>
-      <c r="P71" s="82"/>
-      <c r="Q71" s="83"/>
-      <c r="R71" s="82"/>
-      <c r="S71" s="87"/>
+      <c r="N71" s="85"/>
+      <c r="O71" s="85"/>
+      <c r="P71" s="81"/>
+      <c r="Q71" s="82"/>
+      <c r="R71" s="81"/>
+      <c r="S71" s="86"/>
     </row>
     <row r="72" spans="1:19" ht="21" customHeight="1">
       <c r="A72" s="9">
         <v>67</v>
       </c>
-      <c r="B72" s="72"/>
-      <c r="C72" s="143"/>
-      <c r="D72" s="59">
+      <c r="B72" s="71"/>
+      <c r="C72" s="156"/>
+      <c r="D72" s="58">
         <v>9</v>
       </c>
-      <c r="E72" s="47">
+      <c r="E72" s="46">
         <v>8245</v>
       </c>
       <c r="F72" s="12">
@@ -26046,29 +26528,29 @@
         <f t="shared" si="13"/>
         <v>1.4682499999999998</v>
       </c>
-      <c r="J72" s="50"/>
-      <c r="K72" s="50"/>
-      <c r="L72" s="51"/>
-      <c r="M72" s="85">
+      <c r="J72" s="49"/>
+      <c r="K72" s="49"/>
+      <c r="L72" s="50"/>
+      <c r="M72" s="84">
         <v>2</v>
       </c>
-      <c r="N72" s="86"/>
-      <c r="O72" s="86"/>
-      <c r="P72" s="82"/>
-      <c r="Q72" s="83"/>
-      <c r="R72" s="82"/>
-      <c r="S72" s="88"/>
+      <c r="N72" s="85"/>
+      <c r="O72" s="85"/>
+      <c r="P72" s="81"/>
+      <c r="Q72" s="82"/>
+      <c r="R72" s="81"/>
+      <c r="S72" s="87"/>
     </row>
     <row r="73" spans="1:19" ht="21" customHeight="1">
       <c r="A73" s="9">
         <v>68</v>
       </c>
-      <c r="B73" s="72"/>
-      <c r="C73" s="143"/>
-      <c r="D73" s="59">
+      <c r="B73" s="71"/>
+      <c r="C73" s="156"/>
+      <c r="D73" s="58">
         <v>10</v>
       </c>
-      <c r="E73" s="47">
+      <c r="E73" s="46">
         <v>6862</v>
       </c>
       <c r="F73" s="12">
@@ -26087,29 +26569,29 @@
         <f t="shared" si="13"/>
         <v>4.6144999999999996</v>
       </c>
-      <c r="J73" s="50"/>
-      <c r="K73" s="50"/>
-      <c r="L73" s="51"/>
-      <c r="M73" s="85">
+      <c r="J73" s="49"/>
+      <c r="K73" s="49"/>
+      <c r="L73" s="50"/>
+      <c r="M73" s="84">
         <v>3</v>
       </c>
-      <c r="N73" s="86"/>
-      <c r="O73" s="86"/>
-      <c r="P73" s="82"/>
-      <c r="Q73" s="83"/>
-      <c r="R73" s="82"/>
-      <c r="S73" s="88"/>
+      <c r="N73" s="85"/>
+      <c r="O73" s="85"/>
+      <c r="P73" s="81"/>
+      <c r="Q73" s="82"/>
+      <c r="R73" s="81"/>
+      <c r="S73" s="87"/>
     </row>
     <row r="74" spans="1:19" ht="21" customHeight="1" thickBot="1">
       <c r="A74" s="9">
         <v>69</v>
       </c>
-      <c r="B74" s="72"/>
-      <c r="C74" s="143"/>
-      <c r="D74" s="59">
+      <c r="B74" s="71"/>
+      <c r="C74" s="156"/>
+      <c r="D74" s="58">
         <v>11</v>
       </c>
-      <c r="E74" s="47">
+      <c r="E74" s="46">
         <v>7155</v>
       </c>
       <c r="F74" s="12">
@@ -26128,29 +26610,29 @@
         <f t="shared" si="13"/>
         <v>4.1950000000000003</v>
       </c>
-      <c r="J74" s="50"/>
-      <c r="K74" s="50"/>
-      <c r="L74" s="51"/>
-      <c r="M74" s="89">
+      <c r="J74" s="49"/>
+      <c r="K74" s="49"/>
+      <c r="L74" s="50"/>
+      <c r="M74" s="88">
         <v>4</v>
       </c>
-      <c r="N74" s="90"/>
-      <c r="O74" s="90"/>
-      <c r="P74" s="91"/>
-      <c r="Q74" s="92"/>
-      <c r="R74" s="91"/>
-      <c r="S74" s="93"/>
+      <c r="N74" s="89"/>
+      <c r="O74" s="89"/>
+      <c r="P74" s="90"/>
+      <c r="Q74" s="91"/>
+      <c r="R74" s="90"/>
+      <c r="S74" s="92"/>
     </row>
     <row r="75" spans="1:19" ht="21" customHeight="1" thickBot="1">
       <c r="A75" s="9">
         <v>70</v>
       </c>
-      <c r="B75" s="72"/>
-      <c r="C75" s="94"/>
-      <c r="D75" s="59">
+      <c r="B75" s="71"/>
+      <c r="C75" s="93"/>
+      <c r="D75" s="58">
         <v>14</v>
       </c>
-      <c r="E75" s="47">
+      <c r="E75" s="46">
         <v>8086</v>
       </c>
       <c r="F75" s="12">
@@ -26169,459 +26651,467 @@
         <f t="shared" si="13"/>
         <v>6.2925000000000004</v>
       </c>
-      <c r="J75" s="50"/>
-      <c r="K75" s="50"/>
-      <c r="L75" s="51"/>
-      <c r="M75" s="160" t="s">
+      <c r="J75" s="49"/>
+      <c r="K75" s="49"/>
+      <c r="L75" s="50"/>
+      <c r="M75" s="161" t="s">
         <v>46</v>
       </c>
-      <c r="N75" s="135"/>
-      <c r="O75" s="135"/>
-      <c r="P75" s="161" t="s">
+      <c r="N75" s="162"/>
+      <c r="O75" s="162"/>
+      <c r="P75" s="175" t="s">
         <v>47</v>
       </c>
-      <c r="Q75" s="162"/>
-      <c r="R75" s="162"/>
-      <c r="S75" s="163"/>
+      <c r="Q75" s="176"/>
+      <c r="R75" s="176"/>
+      <c r="S75" s="177"/>
     </row>
     <row r="76" spans="1:19" ht="21" customHeight="1" thickBot="1">
-      <c r="A76" s="50"/>
-      <c r="B76" s="95"/>
-      <c r="C76" s="96"/>
-      <c r="D76" s="97">
+      <c r="A76" s="49"/>
+      <c r="B76" s="94"/>
+      <c r="C76" s="95"/>
+      <c r="D76" s="96">
         <f>COUNT(E6:E75)</f>
         <v>70</v>
       </c>
-      <c r="E76" s="98"/>
-      <c r="F76" s="99"/>
-      <c r="G76" s="100">
+      <c r="E76" s="97"/>
+      <c r="F76" s="98"/>
+      <c r="G76" s="99">
         <f>SUM(G6:G75)</f>
         <v>2750</v>
       </c>
-      <c r="H76" s="100"/>
-      <c r="I76" s="100">
+      <c r="H76" s="99"/>
+      <c r="I76" s="99">
         <f>SUM(I6:I75)</f>
         <v>353.21899999999988</v>
       </c>
-      <c r="J76" s="50"/>
-      <c r="K76" s="50"/>
-      <c r="L76" s="51"/>
-      <c r="M76" s="101"/>
-      <c r="N76" s="102"/>
-      <c r="O76" s="103"/>
-      <c r="P76" s="101"/>
-      <c r="Q76" s="102"/>
-      <c r="R76" s="102"/>
-      <c r="S76" s="104"/>
+      <c r="J76" s="49"/>
+      <c r="K76" s="49"/>
+      <c r="L76" s="50"/>
+      <c r="M76" s="100"/>
+      <c r="N76" s="101"/>
+      <c r="O76" s="102"/>
+      <c r="P76" s="100"/>
+      <c r="Q76" s="101"/>
+      <c r="R76" s="101"/>
+      <c r="S76" s="103"/>
     </row>
     <row r="77" spans="1:19" ht="21" customHeight="1">
-      <c r="A77" s="50"/>
-      <c r="B77" s="95"/>
-      <c r="C77" s="139"/>
-      <c r="D77" s="140"/>
-      <c r="E77" s="141"/>
-      <c r="F77" s="105" t="s">
+      <c r="A77" s="49"/>
+      <c r="B77" s="94"/>
+      <c r="C77" s="183"/>
+      <c r="D77" s="184"/>
+      <c r="E77" s="185"/>
+      <c r="F77" s="104" t="s">
         <v>48</v>
       </c>
-      <c r="G77" s="105" t="s">
+      <c r="G77" s="104" t="s">
         <v>49</v>
       </c>
-      <c r="H77" s="131" t="s">
+      <c r="H77" s="165" t="s">
         <v>50</v>
       </c>
-      <c r="I77" s="131"/>
-      <c r="J77" s="131" t="s">
+      <c r="I77" s="165"/>
+      <c r="J77" s="165" t="s">
         <v>51</v>
       </c>
-      <c r="K77" s="131"/>
-      <c r="L77" s="105" t="s">
+      <c r="K77" s="165"/>
+      <c r="L77" s="104" t="s">
         <v>52</v>
       </c>
-      <c r="M77" s="106" t="s">
+      <c r="M77" s="105" t="s">
         <v>53</v>
       </c>
-      <c r="N77" s="106" t="s">
+      <c r="N77" s="105" t="s">
         <v>54</v>
       </c>
-      <c r="O77" s="106" t="s">
+      <c r="O77" s="105" t="s">
         <v>55</v>
       </c>
-      <c r="P77" s="106" t="s">
+      <c r="P77" s="105" t="s">
         <v>56</v>
       </c>
-      <c r="Q77" s="106" t="s">
+      <c r="Q77" s="105" t="s">
         <v>57</v>
       </c>
-      <c r="R77" s="107" t="s">
+      <c r="R77" s="106" t="s">
         <v>58</v>
       </c>
-      <c r="S77" s="107" t="s">
+      <c r="S77" s="106" t="s">
         <v>59</v>
       </c>
     </row>
     <row r="78" spans="1:19" ht="21.75" customHeight="1">
-      <c r="A78" s="137" t="s">
+      <c r="A78" s="181" t="s">
         <v>79</v>
       </c>
-      <c r="B78" s="138"/>
-      <c r="C78" s="49"/>
-      <c r="D78" s="129"/>
-      <c r="E78" s="130"/>
-      <c r="F78" s="108"/>
-      <c r="G78" s="108"/>
-      <c r="H78" s="48"/>
-      <c r="I78" s="48"/>
-      <c r="J78" s="48"/>
-      <c r="K78" s="48"/>
-      <c r="L78" s="108"/>
-      <c r="M78" s="48"/>
-      <c r="N78" s="48"/>
-      <c r="O78" s="48"/>
-      <c r="P78" s="48"/>
-      <c r="Q78" s="48"/>
-      <c r="R78" s="48"/>
-      <c r="S78" s="48"/>
+      <c r="B78" s="182"/>
+      <c r="C78" s="48"/>
+      <c r="D78" s="128"/>
+      <c r="E78" s="129"/>
+      <c r="F78" s="107"/>
+      <c r="G78" s="107"/>
+      <c r="H78" s="47"/>
+      <c r="I78" s="47"/>
+      <c r="J78" s="47"/>
+      <c r="K78" s="47"/>
+      <c r="L78" s="107"/>
+      <c r="M78" s="47"/>
+      <c r="N78" s="47"/>
+      <c r="O78" s="47"/>
+      <c r="P78" s="47"/>
+      <c r="Q78" s="47"/>
+      <c r="R78" s="47"/>
+      <c r="S78" s="47"/>
     </row>
     <row r="79" spans="1:19" ht="21.75" customHeight="1">
-      <c r="A79" s="146" t="s">
+      <c r="A79" s="188" t="s">
         <v>60</v>
       </c>
-      <c r="B79" s="147"/>
-      <c r="C79" s="126"/>
-      <c r="D79" s="127"/>
-      <c r="E79" s="128"/>
-      <c r="F79" s="64"/>
-      <c r="G79" s="64"/>
-      <c r="H79" s="64"/>
-      <c r="I79" s="64"/>
-      <c r="J79" s="64"/>
-      <c r="K79" s="64"/>
-      <c r="L79" s="64"/>
-      <c r="M79" s="50"/>
-      <c r="N79" s="50"/>
-      <c r="O79" s="50"/>
-      <c r="P79" s="50"/>
-      <c r="Q79" s="50"/>
-      <c r="R79" s="48"/>
-      <c r="S79" s="48"/>
+      <c r="B79" s="189"/>
+      <c r="C79" s="125"/>
+      <c r="D79" s="126"/>
+      <c r="E79" s="127"/>
+      <c r="F79" s="63"/>
+      <c r="G79" s="63"/>
+      <c r="H79" s="63"/>
+      <c r="I79" s="63"/>
+      <c r="J79" s="63"/>
+      <c r="K79" s="63"/>
+      <c r="L79" s="63"/>
+      <c r="M79" s="49"/>
+      <c r="N79" s="49"/>
+      <c r="O79" s="49"/>
+      <c r="P79" s="49"/>
+      <c r="Q79" s="49"/>
+      <c r="R79" s="47"/>
+      <c r="S79" s="47"/>
     </row>
     <row r="80" spans="1:19" ht="21.75" customHeight="1">
-      <c r="A80" s="148" t="s">
+      <c r="A80" s="143" t="s">
         <v>61</v>
       </c>
-      <c r="B80" s="148"/>
-      <c r="C80" s="49"/>
-      <c r="D80" s="129"/>
-      <c r="E80" s="130"/>
-      <c r="F80" s="50"/>
-      <c r="G80" s="50"/>
-      <c r="H80" s="50"/>
-      <c r="I80" s="50"/>
-      <c r="J80" s="50"/>
-      <c r="K80" s="50"/>
-      <c r="L80" s="50"/>
-      <c r="M80" s="50"/>
-      <c r="N80" s="50"/>
-      <c r="O80" s="50"/>
-      <c r="P80" s="50"/>
-      <c r="Q80" s="50"/>
-      <c r="R80" s="48"/>
-      <c r="S80" s="48"/>
+      <c r="B80" s="143"/>
+      <c r="C80" s="48"/>
+      <c r="D80" s="128"/>
+      <c r="E80" s="129"/>
+      <c r="F80" s="49"/>
+      <c r="G80" s="49"/>
+      <c r="H80" s="49"/>
+      <c r="I80" s="49"/>
+      <c r="J80" s="49"/>
+      <c r="K80" s="49"/>
+      <c r="L80" s="49"/>
+      <c r="M80" s="49"/>
+      <c r="N80" s="49"/>
+      <c r="O80" s="49"/>
+      <c r="P80" s="49"/>
+      <c r="Q80" s="49"/>
+      <c r="R80" s="47"/>
+      <c r="S80" s="47"/>
     </row>
     <row r="81" spans="1:19" ht="18" customHeight="1">
-      <c r="A81" s="146" t="s">
+      <c r="A81" s="188" t="s">
         <v>62</v>
       </c>
-      <c r="B81" s="149"/>
-      <c r="C81" s="149"/>
-      <c r="D81" s="149"/>
-      <c r="E81" s="149"/>
-      <c r="F81" s="149"/>
-      <c r="G81" s="149"/>
-      <c r="H81" s="149"/>
-      <c r="I81" s="149"/>
-      <c r="J81" s="149"/>
-      <c r="K81" s="149"/>
-      <c r="L81" s="147"/>
-      <c r="M81" s="105" t="s">
+      <c r="B81" s="190"/>
+      <c r="C81" s="190"/>
+      <c r="D81" s="190"/>
+      <c r="E81" s="190"/>
+      <c r="F81" s="190"/>
+      <c r="G81" s="190"/>
+      <c r="H81" s="190"/>
+      <c r="I81" s="190"/>
+      <c r="J81" s="190"/>
+      <c r="K81" s="190"/>
+      <c r="L81" s="189"/>
+      <c r="M81" s="104" t="s">
         <v>63</v>
       </c>
-      <c r="N81" s="131" t="s">
+      <c r="N81" s="165" t="s">
         <v>64</v>
       </c>
-      <c r="O81" s="131"/>
-      <c r="P81" s="105" t="s">
+      <c r="O81" s="165"/>
+      <c r="P81" s="104" t="s">
         <v>65</v>
       </c>
-      <c r="Q81" s="131" t="s">
+      <c r="Q81" s="165" t="s">
         <v>66</v>
       </c>
-      <c r="R81" s="131"/>
-      <c r="S81" s="131"/>
+      <c r="R81" s="165"/>
+      <c r="S81" s="165"/>
     </row>
     <row r="82" spans="1:19">
-      <c r="A82" s="183"/>
-      <c r="B82" s="184"/>
-      <c r="C82" s="184"/>
-      <c r="D82" s="184"/>
-      <c r="E82" s="184"/>
-      <c r="F82" s="184"/>
-      <c r="G82" s="184"/>
-      <c r="H82" s="184"/>
-      <c r="I82" s="184"/>
-      <c r="J82" s="184"/>
-      <c r="K82" s="184"/>
-      <c r="L82" s="185"/>
-      <c r="M82" s="192"/>
-      <c r="N82" s="193"/>
-      <c r="O82" s="193"/>
-      <c r="P82" s="192"/>
-      <c r="Q82" s="193"/>
-      <c r="R82" s="193"/>
-      <c r="S82" s="193"/>
+      <c r="A82" s="130"/>
+      <c r="B82" s="131"/>
+      <c r="C82" s="131"/>
+      <c r="D82" s="131"/>
+      <c r="E82" s="131"/>
+      <c r="F82" s="131"/>
+      <c r="G82" s="131"/>
+      <c r="H82" s="131"/>
+      <c r="I82" s="131"/>
+      <c r="J82" s="131"/>
+      <c r="K82" s="131"/>
+      <c r="L82" s="132"/>
+      <c r="M82" s="139"/>
+      <c r="N82" s="140"/>
+      <c r="O82" s="140"/>
+      <c r="P82" s="139"/>
+      <c r="Q82" s="140"/>
+      <c r="R82" s="140"/>
+      <c r="S82" s="140"/>
     </row>
     <row r="83" spans="1:19">
-      <c r="A83" s="186"/>
-      <c r="B83" s="187"/>
-      <c r="C83" s="187"/>
-      <c r="D83" s="187"/>
-      <c r="E83" s="187"/>
-      <c r="F83" s="187"/>
-      <c r="G83" s="187"/>
-      <c r="H83" s="187"/>
-      <c r="I83" s="187"/>
-      <c r="J83" s="187"/>
-      <c r="K83" s="187"/>
-      <c r="L83" s="188"/>
-      <c r="M83" s="192"/>
-      <c r="N83" s="193"/>
-      <c r="O83" s="193"/>
-      <c r="P83" s="192"/>
-      <c r="Q83" s="193"/>
-      <c r="R83" s="193"/>
-      <c r="S83" s="193"/>
+      <c r="A83" s="133"/>
+      <c r="B83" s="134"/>
+      <c r="C83" s="134"/>
+      <c r="D83" s="134"/>
+      <c r="E83" s="134"/>
+      <c r="F83" s="134"/>
+      <c r="G83" s="134"/>
+      <c r="H83" s="134"/>
+      <c r="I83" s="134"/>
+      <c r="J83" s="134"/>
+      <c r="K83" s="134"/>
+      <c r="L83" s="135"/>
+      <c r="M83" s="139"/>
+      <c r="N83" s="140"/>
+      <c r="O83" s="140"/>
+      <c r="P83" s="139"/>
+      <c r="Q83" s="140"/>
+      <c r="R83" s="140"/>
+      <c r="S83" s="140"/>
     </row>
     <row r="84" spans="1:19">
-      <c r="A84" s="186"/>
-      <c r="B84" s="187"/>
-      <c r="C84" s="187"/>
-      <c r="D84" s="187"/>
-      <c r="E84" s="187"/>
-      <c r="F84" s="187"/>
-      <c r="G84" s="187"/>
-      <c r="H84" s="187"/>
-      <c r="I84" s="187"/>
-      <c r="J84" s="187"/>
-      <c r="K84" s="187"/>
-      <c r="L84" s="188"/>
-      <c r="M84" s="192"/>
-      <c r="N84" s="193"/>
-      <c r="O84" s="193"/>
-      <c r="P84" s="192"/>
-      <c r="Q84" s="193"/>
-      <c r="R84" s="193"/>
-      <c r="S84" s="193"/>
+      <c r="A84" s="133"/>
+      <c r="B84" s="134"/>
+      <c r="C84" s="134"/>
+      <c r="D84" s="134"/>
+      <c r="E84" s="134"/>
+      <c r="F84" s="134"/>
+      <c r="G84" s="134"/>
+      <c r="H84" s="134"/>
+      <c r="I84" s="134"/>
+      <c r="J84" s="134"/>
+      <c r="K84" s="134"/>
+      <c r="L84" s="135"/>
+      <c r="M84" s="139"/>
+      <c r="N84" s="140"/>
+      <c r="O84" s="140"/>
+      <c r="P84" s="139"/>
+      <c r="Q84" s="140"/>
+      <c r="R84" s="140"/>
+      <c r="S84" s="140"/>
     </row>
     <row r="85" spans="1:19">
-      <c r="A85" s="186"/>
-      <c r="B85" s="187"/>
-      <c r="C85" s="187"/>
-      <c r="D85" s="187"/>
-      <c r="E85" s="187"/>
-      <c r="F85" s="187"/>
-      <c r="G85" s="187"/>
-      <c r="H85" s="187"/>
-      <c r="I85" s="187"/>
-      <c r="J85" s="187"/>
-      <c r="K85" s="187"/>
-      <c r="L85" s="188"/>
-      <c r="M85" s="192"/>
-      <c r="N85" s="193"/>
-      <c r="O85" s="193"/>
-      <c r="P85" s="192"/>
-      <c r="Q85" s="193"/>
-      <c r="R85" s="193"/>
-      <c r="S85" s="193"/>
+      <c r="A85" s="133"/>
+      <c r="B85" s="134"/>
+      <c r="C85" s="134"/>
+      <c r="D85" s="134"/>
+      <c r="E85" s="134"/>
+      <c r="F85" s="134"/>
+      <c r="G85" s="134"/>
+      <c r="H85" s="134"/>
+      <c r="I85" s="134"/>
+      <c r="J85" s="134"/>
+      <c r="K85" s="134"/>
+      <c r="L85" s="135"/>
+      <c r="M85" s="139"/>
+      <c r="N85" s="140"/>
+      <c r="O85" s="140"/>
+      <c r="P85" s="139"/>
+      <c r="Q85" s="140"/>
+      <c r="R85" s="140"/>
+      <c r="S85" s="140"/>
     </row>
     <row r="86" spans="1:19">
-      <c r="A86" s="186"/>
-      <c r="B86" s="187"/>
-      <c r="C86" s="187"/>
-      <c r="D86" s="187"/>
-      <c r="E86" s="187"/>
-      <c r="F86" s="187"/>
-      <c r="G86" s="187"/>
-      <c r="H86" s="187"/>
-      <c r="I86" s="187"/>
-      <c r="J86" s="187"/>
-      <c r="K86" s="187"/>
-      <c r="L86" s="188"/>
-      <c r="M86" s="192"/>
-      <c r="N86" s="193"/>
-      <c r="O86" s="193"/>
-      <c r="P86" s="192"/>
-      <c r="Q86" s="193"/>
-      <c r="R86" s="193"/>
-      <c r="S86" s="193"/>
+      <c r="A86" s="133"/>
+      <c r="B86" s="134"/>
+      <c r="C86" s="134"/>
+      <c r="D86" s="134"/>
+      <c r="E86" s="134"/>
+      <c r="F86" s="134"/>
+      <c r="G86" s="134"/>
+      <c r="H86" s="134"/>
+      <c r="I86" s="134"/>
+      <c r="J86" s="134"/>
+      <c r="K86" s="134"/>
+      <c r="L86" s="135"/>
+      <c r="M86" s="139"/>
+      <c r="N86" s="140"/>
+      <c r="O86" s="140"/>
+      <c r="P86" s="139"/>
+      <c r="Q86" s="140"/>
+      <c r="R86" s="140"/>
+      <c r="S86" s="140"/>
     </row>
     <row r="87" spans="1:19" ht="18.75" customHeight="1">
-      <c r="A87" s="186"/>
-      <c r="B87" s="187"/>
-      <c r="C87" s="187"/>
-      <c r="D87" s="187"/>
-      <c r="E87" s="187"/>
-      <c r="F87" s="187"/>
-      <c r="G87" s="187"/>
-      <c r="H87" s="187"/>
-      <c r="I87" s="187"/>
-      <c r="J87" s="187"/>
-      <c r="K87" s="187"/>
-      <c r="L87" s="188"/>
-      <c r="M87" s="192"/>
-      <c r="N87" s="193"/>
-      <c r="O87" s="193"/>
-      <c r="P87" s="192"/>
-      <c r="Q87" s="193"/>
-      <c r="R87" s="193"/>
-      <c r="S87" s="193"/>
+      <c r="A87" s="133"/>
+      <c r="B87" s="134"/>
+      <c r="C87" s="134"/>
+      <c r="D87" s="134"/>
+      <c r="E87" s="134"/>
+      <c r="F87" s="134"/>
+      <c r="G87" s="134"/>
+      <c r="H87" s="134"/>
+      <c r="I87" s="134"/>
+      <c r="J87" s="134"/>
+      <c r="K87" s="134"/>
+      <c r="L87" s="135"/>
+      <c r="M87" s="139"/>
+      <c r="N87" s="140"/>
+      <c r="O87" s="140"/>
+      <c r="P87" s="139"/>
+      <c r="Q87" s="140"/>
+      <c r="R87" s="140"/>
+      <c r="S87" s="140"/>
     </row>
     <row r="88" spans="1:19">
-      <c r="A88" s="186"/>
-      <c r="B88" s="187"/>
-      <c r="C88" s="187"/>
-      <c r="D88" s="187"/>
-      <c r="E88" s="187"/>
-      <c r="F88" s="187"/>
-      <c r="G88" s="187"/>
-      <c r="H88" s="187"/>
-      <c r="I88" s="187"/>
-      <c r="J88" s="187"/>
-      <c r="K88" s="187"/>
-      <c r="L88" s="188"/>
-      <c r="M88" s="192"/>
-      <c r="N88" s="193"/>
-      <c r="O88" s="193"/>
-      <c r="P88" s="192"/>
-      <c r="Q88" s="193"/>
-      <c r="R88" s="193"/>
-      <c r="S88" s="193"/>
+      <c r="A88" s="133"/>
+      <c r="B88" s="134"/>
+      <c r="C88" s="134"/>
+      <c r="D88" s="134"/>
+      <c r="E88" s="134"/>
+      <c r="F88" s="134"/>
+      <c r="G88" s="134"/>
+      <c r="H88" s="134"/>
+      <c r="I88" s="134"/>
+      <c r="J88" s="134"/>
+      <c r="K88" s="134"/>
+      <c r="L88" s="135"/>
+      <c r="M88" s="139"/>
+      <c r="N88" s="140"/>
+      <c r="O88" s="140"/>
+      <c r="P88" s="139"/>
+      <c r="Q88" s="140"/>
+      <c r="R88" s="140"/>
+      <c r="S88" s="140"/>
     </row>
     <row r="89" spans="1:19">
-      <c r="A89" s="186"/>
-      <c r="B89" s="187"/>
-      <c r="C89" s="187"/>
-      <c r="D89" s="187"/>
-      <c r="E89" s="187"/>
-      <c r="F89" s="187"/>
-      <c r="G89" s="187"/>
-      <c r="H89" s="187"/>
-      <c r="I89" s="187"/>
-      <c r="J89" s="187"/>
-      <c r="K89" s="187"/>
-      <c r="L89" s="188"/>
-      <c r="M89" s="192"/>
-      <c r="N89" s="193"/>
-      <c r="O89" s="193"/>
-      <c r="P89" s="192"/>
-      <c r="Q89" s="193"/>
-      <c r="R89" s="193"/>
-      <c r="S89" s="193"/>
+      <c r="A89" s="133"/>
+      <c r="B89" s="134"/>
+      <c r="C89" s="134"/>
+      <c r="D89" s="134"/>
+      <c r="E89" s="134"/>
+      <c r="F89" s="134"/>
+      <c r="G89" s="134"/>
+      <c r="H89" s="134"/>
+      <c r="I89" s="134"/>
+      <c r="J89" s="134"/>
+      <c r="K89" s="134"/>
+      <c r="L89" s="135"/>
+      <c r="M89" s="139"/>
+      <c r="N89" s="140"/>
+      <c r="O89" s="140"/>
+      <c r="P89" s="139"/>
+      <c r="Q89" s="140"/>
+      <c r="R89" s="140"/>
+      <c r="S89" s="140"/>
     </row>
     <row r="90" spans="1:19">
-      <c r="A90" s="186"/>
-      <c r="B90" s="187"/>
-      <c r="C90" s="187"/>
-      <c r="D90" s="187"/>
-      <c r="E90" s="187"/>
-      <c r="F90" s="187"/>
-      <c r="G90" s="187"/>
-      <c r="H90" s="187"/>
-      <c r="I90" s="187"/>
-      <c r="J90" s="187"/>
-      <c r="K90" s="187"/>
-      <c r="L90" s="188"/>
-      <c r="M90" s="192"/>
-      <c r="N90" s="193"/>
-      <c r="O90" s="193"/>
-      <c r="P90" s="192"/>
-      <c r="Q90" s="193"/>
-      <c r="R90" s="193"/>
-      <c r="S90" s="193"/>
+      <c r="A90" s="133"/>
+      <c r="B90" s="134"/>
+      <c r="C90" s="134"/>
+      <c r="D90" s="134"/>
+      <c r="E90" s="134"/>
+      <c r="F90" s="134"/>
+      <c r="G90" s="134"/>
+      <c r="H90" s="134"/>
+      <c r="I90" s="134"/>
+      <c r="J90" s="134"/>
+      <c r="K90" s="134"/>
+      <c r="L90" s="135"/>
+      <c r="M90" s="139"/>
+      <c r="N90" s="140"/>
+      <c r="O90" s="140"/>
+      <c r="P90" s="139"/>
+      <c r="Q90" s="140"/>
+      <c r="R90" s="140"/>
+      <c r="S90" s="140"/>
     </row>
     <row r="91" spans="1:19">
-      <c r="A91" s="189"/>
-      <c r="B91" s="190"/>
-      <c r="C91" s="190"/>
-      <c r="D91" s="190"/>
-      <c r="E91" s="190"/>
-      <c r="F91" s="190"/>
-      <c r="G91" s="190"/>
-      <c r="H91" s="190"/>
-      <c r="I91" s="190"/>
-      <c r="J91" s="190"/>
-      <c r="K91" s="190"/>
-      <c r="L91" s="191"/>
-      <c r="M91" s="192"/>
-      <c r="N91" s="193"/>
-      <c r="O91" s="193"/>
-      <c r="P91" s="192"/>
-      <c r="Q91" s="193"/>
-      <c r="R91" s="193"/>
-      <c r="S91" s="193"/>
+      <c r="A91" s="136"/>
+      <c r="B91" s="137"/>
+      <c r="C91" s="137"/>
+      <c r="D91" s="137"/>
+      <c r="E91" s="137"/>
+      <c r="F91" s="137"/>
+      <c r="G91" s="137"/>
+      <c r="H91" s="137"/>
+      <c r="I91" s="137"/>
+      <c r="J91" s="137"/>
+      <c r="K91" s="137"/>
+      <c r="L91" s="138"/>
+      <c r="M91" s="139"/>
+      <c r="N91" s="140"/>
+      <c r="O91" s="140"/>
+      <c r="P91" s="139"/>
+      <c r="Q91" s="140"/>
+      <c r="R91" s="140"/>
+      <c r="S91" s="140"/>
     </row>
     <row r="94" spans="1:19">
-      <c r="I94" s="150"/>
-      <c r="J94" s="150"/>
+      <c r="I94" s="164"/>
+      <c r="J94" s="164"/>
     </row>
     <row r="95" spans="1:19">
-      <c r="I95" s="150"/>
-      <c r="J95" s="150"/>
+      <c r="I95" s="164"/>
+      <c r="J95" s="164"/>
     </row>
     <row r="96" spans="1:19">
-      <c r="I96" s="150"/>
-      <c r="J96" s="150"/>
+      <c r="I96" s="164"/>
+      <c r="J96" s="164"/>
     </row>
     <row r="97" spans="9:10">
-      <c r="I97" s="150"/>
-      <c r="J97" s="150"/>
+      <c r="I97" s="164"/>
+      <c r="J97" s="164"/>
     </row>
     <row r="98" spans="9:10">
-      <c r="I98" s="150"/>
-      <c r="J98" s="150"/>
+      <c r="I98" s="164"/>
+      <c r="J98" s="164"/>
     </row>
     <row r="99" spans="9:10">
-      <c r="I99" s="150"/>
-      <c r="J99" s="150"/>
+      <c r="I99" s="164"/>
+      <c r="J99" s="164"/>
     </row>
     <row r="100" spans="9:10">
-      <c r="I100" s="150"/>
-      <c r="J100" s="150"/>
+      <c r="I100" s="164"/>
+      <c r="J100" s="164"/>
     </row>
     <row r="101" spans="9:10">
-      <c r="I101" s="150"/>
-      <c r="J101" s="150"/>
+      <c r="I101" s="164"/>
+      <c r="J101" s="164"/>
     </row>
     <row r="102" spans="9:10">
-      <c r="I102" s="150"/>
-      <c r="J102" s="150"/>
+      <c r="I102" s="164"/>
+      <c r="J102" s="164"/>
     </row>
     <row r="103" spans="9:10">
-      <c r="I103" s="150"/>
-      <c r="J103" s="150"/>
+      <c r="I103" s="164"/>
+      <c r="J103" s="164"/>
     </row>
   </sheetData>
   <mergeCells count="46">
-    <mergeCell ref="G1:L1"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="B4:B5"/>
-    <mergeCell ref="C4:C5"/>
-    <mergeCell ref="D4:D5"/>
-    <mergeCell ref="E4:E5"/>
-    <mergeCell ref="F4:F5"/>
-    <mergeCell ref="G4:I4"/>
-    <mergeCell ref="J4:J5"/>
-    <mergeCell ref="K4:K5"/>
-    <mergeCell ref="L4:L5"/>
+    <mergeCell ref="A79:B79"/>
+    <mergeCell ref="A80:B80"/>
+    <mergeCell ref="A81:L81"/>
+    <mergeCell ref="N36:Q36"/>
+    <mergeCell ref="P58:S58"/>
+    <mergeCell ref="A78:B78"/>
+    <mergeCell ref="C77:E77"/>
+    <mergeCell ref="H77:I77"/>
+    <mergeCell ref="J77:K77"/>
+    <mergeCell ref="C65:C74"/>
+    <mergeCell ref="D66:D67"/>
+    <mergeCell ref="I94:J103"/>
+    <mergeCell ref="N81:O81"/>
+    <mergeCell ref="M66:S66"/>
+    <mergeCell ref="M68:S68"/>
+    <mergeCell ref="M69:S69"/>
+    <mergeCell ref="M75:O75"/>
+    <mergeCell ref="P75:S75"/>
+    <mergeCell ref="Q81:S81"/>
     <mergeCell ref="M4:S5"/>
     <mergeCell ref="B6:B63"/>
     <mergeCell ref="C6:C18"/>
@@ -26637,26 +27127,18 @@
     <mergeCell ref="M53:S53"/>
     <mergeCell ref="M62:S62"/>
     <mergeCell ref="M64:S64"/>
-    <mergeCell ref="I94:J103"/>
-    <mergeCell ref="N81:O81"/>
-    <mergeCell ref="M66:S66"/>
-    <mergeCell ref="M68:S68"/>
-    <mergeCell ref="M69:S69"/>
-    <mergeCell ref="M75:O75"/>
-    <mergeCell ref="P75:S75"/>
-    <mergeCell ref="Q81:S81"/>
     <mergeCell ref="R36:S36"/>
-    <mergeCell ref="N36:Q36"/>
-    <mergeCell ref="P58:S58"/>
-    <mergeCell ref="A78:B78"/>
-    <mergeCell ref="C77:E77"/>
-    <mergeCell ref="H77:I77"/>
-    <mergeCell ref="J77:K77"/>
-    <mergeCell ref="C65:C74"/>
-    <mergeCell ref="D66:D67"/>
-    <mergeCell ref="A79:B79"/>
-    <mergeCell ref="A80:B80"/>
-    <mergeCell ref="A81:L81"/>
+    <mergeCell ref="G1:L1"/>
+    <mergeCell ref="A4:A5"/>
+    <mergeCell ref="B4:B5"/>
+    <mergeCell ref="C4:C5"/>
+    <mergeCell ref="D4:D5"/>
+    <mergeCell ref="E4:E5"/>
+    <mergeCell ref="F4:F5"/>
+    <mergeCell ref="G4:I4"/>
+    <mergeCell ref="J4:J5"/>
+    <mergeCell ref="K4:K5"/>
+    <mergeCell ref="L4:L5"/>
   </mergeCells>
   <conditionalFormatting sqref="E1:E81 E92:E65536">
     <cfRule type="duplicateValues" dxfId="0" priority="1" stopIfTrue="1"/>
@@ -26674,961 +27156,4523 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8A067486-5E4F-4D7E-BD41-F7AF0871CD15}">
-  <dimension ref="A1:H40"/>
+  <dimension ref="A1:H193"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="8" style="117" customWidth="1"/>
-    <col min="2" max="2" width="26.28515625" style="117" customWidth="1"/>
-    <col min="3" max="3" width="38.85546875" style="117" customWidth="1"/>
-    <col min="4" max="4" width="19.42578125" style="117" customWidth="1"/>
-    <col min="5" max="5" width="22.85546875" style="117" customWidth="1"/>
-    <col min="6" max="6" width="19.42578125" style="117" customWidth="1"/>
-    <col min="7" max="7" width="18.28515625" style="117" customWidth="1"/>
-    <col min="8" max="8" width="43.42578125" style="117" customWidth="1"/>
-    <col min="9" max="16384" width="9.140625" style="117"/>
+    <col min="1" max="1" width="8" style="116" customWidth="1"/>
+    <col min="2" max="2" width="26.28515625" style="116" customWidth="1"/>
+    <col min="3" max="3" width="38.85546875" style="116" customWidth="1"/>
+    <col min="4" max="4" width="19.42578125" style="116" customWidth="1"/>
+    <col min="5" max="5" width="22.85546875" style="116" customWidth="1"/>
+    <col min="6" max="6" width="19.42578125" style="116" customWidth="1"/>
+    <col min="7" max="7" width="18.28515625" style="116" customWidth="1"/>
+    <col min="8" max="8" width="43.42578125" style="116" customWidth="1"/>
+    <col min="9" max="16384" width="9.140625" style="116"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="27.95" customHeight="1">
-      <c r="A1" s="181" t="s">
-        <v>184</v>
-      </c>
-      <c r="B1" s="181"/>
-      <c r="C1" s="181"/>
-      <c r="D1" s="181"/>
-      <c r="E1" s="181"/>
-      <c r="F1" s="181"/>
-      <c r="G1" s="181"/>
-      <c r="H1" s="181"/>
+      <c r="A1" s="191" t="s">
+        <v>181</v>
+      </c>
+      <c r="B1" s="191"/>
+      <c r="C1" s="191"/>
+      <c r="D1" s="191"/>
+      <c r="E1" s="191"/>
+      <c r="F1" s="191"/>
+      <c r="G1" s="191"/>
+      <c r="H1" s="191"/>
     </row>
     <row r="2" spans="1:8" ht="36" customHeight="1">
-      <c r="A2" s="182" t="s">
-        <v>183</v>
-      </c>
-      <c r="B2" s="182"/>
-      <c r="C2" s="182"/>
-      <c r="D2" s="182"/>
-      <c r="E2" s="182"/>
-      <c r="F2" s="182"/>
-      <c r="G2" s="182"/>
-      <c r="H2" s="182"/>
+      <c r="A2" s="192" t="s">
+        <v>180</v>
+      </c>
+      <c r="B2" s="192"/>
+      <c r="C2" s="192"/>
+      <c r="D2" s="192"/>
+      <c r="E2" s="192"/>
+      <c r="F2" s="192"/>
+      <c r="G2" s="192"/>
+      <c r="H2" s="192"/>
     </row>
     <row r="4" spans="1:8" ht="33.950000000000003" customHeight="1">
-      <c r="A4" s="120" t="s">
-        <v>182</v>
-      </c>
-      <c r="B4" s="120" t="s">
-        <v>181</v>
-      </c>
-      <c r="C4" s="120" t="s">
-        <v>180</v>
-      </c>
-      <c r="D4" s="120" t="s">
+      <c r="A4" s="119" t="s">
         <v>179</v>
       </c>
-      <c r="E4" s="120" t="s">
+      <c r="B4" s="119" t="s">
         <v>178</v>
       </c>
-      <c r="F4" s="120" t="s">
+      <c r="C4" s="119" t="s">
         <v>177</v>
       </c>
-      <c r="G4" s="120" t="s">
+      <c r="D4" s="119" t="s">
         <v>176</v>
       </c>
-      <c r="H4" s="120" t="s">
+      <c r="E4" s="119" t="s">
         <v>175</v>
+      </c>
+      <c r="F4" s="119" t="s">
+        <v>174</v>
+      </c>
+      <c r="G4" s="119" t="s">
+        <v>173</v>
+      </c>
+      <c r="H4" s="119" t="s">
+        <v>172</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="27.95" customHeight="1">
-      <c r="A5" s="118" t="s">
-        <v>174</v>
-      </c>
-      <c r="B5" s="118" t="s">
-        <v>168</v>
-      </c>
-      <c r="C5" s="118" t="s">
-        <v>173</v>
-      </c>
-      <c r="D5" s="119">
+      <c r="A5" s="117" t="s">
+        <v>171</v>
+      </c>
+      <c r="B5" s="117" t="s">
+        <v>165</v>
+      </c>
+      <c r="C5" s="117" t="s">
+        <v>170</v>
+      </c>
+      <c r="D5" s="118">
         <v>93</v>
       </c>
-      <c r="E5" s="119" t="str">
+      <c r="E5" s="118" t="str">
         <f>'93'!I2</f>
         <v>"            "</v>
       </c>
-      <c r="F5" s="118" t="s">
-        <v>172</v>
-      </c>
-      <c r="G5" s="118"/>
-      <c r="H5" s="118" t="s">
-        <v>171</v>
+      <c r="F5" s="117" t="s">
+        <v>169</v>
+      </c>
+      <c r="G5" s="117"/>
+      <c r="H5" s="117" t="s">
+        <v>168</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="27.95" customHeight="1">
-      <c r="A6" s="118" t="s">
-        <v>170</v>
-      </c>
-      <c r="B6" s="118" t="s">
-        <v>168</v>
-      </c>
-      <c r="C6" s="118" t="s">
-        <v>132</v>
-      </c>
-      <c r="D6" s="119">
+      <c r="A6" s="117" t="s">
+        <v>167</v>
+      </c>
+      <c r="B6" s="117" t="s">
+        <v>165</v>
+      </c>
+      <c r="C6" s="117" t="s">
+        <v>129</v>
+      </c>
+      <c r="D6" s="118">
         <v>93</v>
       </c>
-      <c r="E6" s="119">
+      <c r="E6" s="118">
         <f>'93'!S2</f>
         <v>0</v>
       </c>
-      <c r="F6" s="118" t="s">
+      <c r="F6" s="117" t="s">
         <v>81</v>
       </c>
-      <c r="G6" s="118"/>
-      <c r="H6" s="118"/>
+      <c r="G6" s="117"/>
+      <c r="H6" s="117"/>
     </row>
     <row r="7" spans="1:8" ht="27.95" customHeight="1">
-      <c r="A7" s="118" t="s">
-        <v>169</v>
-      </c>
-      <c r="B7" s="118" t="s">
-        <v>168</v>
-      </c>
-      <c r="C7" s="118" t="s">
-        <v>167</v>
-      </c>
-      <c r="D7" s="119">
+      <c r="A7" s="117" t="s">
+        <v>166</v>
+      </c>
+      <c r="B7" s="117" t="s">
+        <v>165</v>
+      </c>
+      <c r="C7" s="117" t="s">
+        <v>164</v>
+      </c>
+      <c r="D7" s="118">
         <v>93</v>
       </c>
-      <c r="E7" s="119">
+      <c r="E7" s="118">
         <f>'93'!Q2</f>
         <v>0</v>
       </c>
-      <c r="F7" s="118" t="s">
+      <c r="F7" s="117" t="s">
         <v>81</v>
       </c>
-      <c r="G7" s="118"/>
-      <c r="H7" s="118"/>
+      <c r="G7" s="117"/>
+      <c r="H7" s="117"/>
     </row>
     <row r="8" spans="1:8" ht="27.95" customHeight="1">
-      <c r="A8" s="118" t="s">
-        <v>166</v>
-      </c>
-      <c r="B8" s="118" t="s">
-        <v>155</v>
-      </c>
-      <c r="C8" s="118" t="s">
-        <v>165</v>
-      </c>
-      <c r="D8" s="119">
+      <c r="A8" s="117" t="s">
+        <v>163</v>
+      </c>
+      <c r="B8" s="117" t="s">
+        <v>152</v>
+      </c>
+      <c r="C8" s="117" t="s">
+        <v>162</v>
+      </c>
+      <c r="D8" s="118">
         <v>93</v>
       </c>
-      <c r="E8" s="119">
+      <c r="E8" s="118">
         <f>'93'!N6</f>
         <v>0</v>
       </c>
-      <c r="F8" s="118" t="s">
-        <v>97</v>
-      </c>
-      <c r="G8" s="118"/>
-      <c r="H8" s="118"/>
+      <c r="F8" s="117" t="s">
+        <v>96</v>
+      </c>
+      <c r="G8" s="117"/>
+      <c r="H8" s="117"/>
     </row>
     <row r="9" spans="1:8" ht="27.95" customHeight="1">
-      <c r="A9" s="118" t="s">
-        <v>164</v>
-      </c>
-      <c r="B9" s="118" t="s">
-        <v>155</v>
-      </c>
-      <c r="C9" s="118" t="s">
-        <v>163</v>
-      </c>
-      <c r="D9" s="119">
+      <c r="A9" s="117" t="s">
+        <v>161</v>
+      </c>
+      <c r="B9" s="117" t="s">
+        <v>152</v>
+      </c>
+      <c r="C9" s="117" t="s">
+        <v>160</v>
+      </c>
+      <c r="D9" s="118">
         <v>93</v>
       </c>
-      <c r="E9" s="119">
+      <c r="E9" s="118">
         <f>'93'!P6</f>
         <v>0</v>
       </c>
-      <c r="F9" s="118" t="s">
-        <v>97</v>
-      </c>
-      <c r="G9" s="118"/>
-      <c r="H9" s="118"/>
+      <c r="F9" s="117" t="s">
+        <v>96</v>
+      </c>
+      <c r="G9" s="117"/>
+      <c r="H9" s="117"/>
     </row>
     <row r="10" spans="1:8" ht="27.95" customHeight="1">
-      <c r="A10" s="118" t="s">
-        <v>162</v>
-      </c>
-      <c r="B10" s="118" t="s">
-        <v>155</v>
-      </c>
-      <c r="C10" s="118" t="s">
-        <v>161</v>
-      </c>
-      <c r="D10" s="119">
+      <c r="A10" s="117" t="s">
+        <v>159</v>
+      </c>
+      <c r="B10" s="117" t="s">
+        <v>152</v>
+      </c>
+      <c r="C10" s="117" t="s">
+        <v>158</v>
+      </c>
+      <c r="D10" s="118">
         <v>93</v>
       </c>
-      <c r="E10" s="119">
+      <c r="E10" s="118">
         <f>'93'!R6</f>
         <v>0</v>
       </c>
-      <c r="F10" s="118" t="s">
-        <v>97</v>
-      </c>
-      <c r="G10" s="118"/>
-      <c r="H10" s="118"/>
+      <c r="F10" s="117" t="s">
+        <v>96</v>
+      </c>
+      <c r="G10" s="117"/>
+      <c r="H10" s="117"/>
     </row>
     <row r="11" spans="1:8" ht="27.95" customHeight="1">
-      <c r="A11" s="118" t="s">
-        <v>160</v>
-      </c>
-      <c r="B11" s="118" t="s">
-        <v>155</v>
-      </c>
-      <c r="C11" s="118" t="s">
-        <v>159</v>
-      </c>
-      <c r="D11" s="119">
+      <c r="A11" s="117" t="s">
+        <v>157</v>
+      </c>
+      <c r="B11" s="117" t="s">
+        <v>152</v>
+      </c>
+      <c r="C11" s="117" t="s">
+        <v>156</v>
+      </c>
+      <c r="D11" s="118">
         <v>93</v>
       </c>
-      <c r="E11" s="119">
+      <c r="E11" s="118">
         <f>'93'!N7</f>
         <v>0</v>
       </c>
-      <c r="F11" s="118" t="s">
-        <v>97</v>
-      </c>
-      <c r="G11" s="118"/>
-      <c r="H11" s="118"/>
+      <c r="F11" s="117" t="s">
+        <v>96</v>
+      </c>
+      <c r="G11" s="117"/>
+      <c r="H11" s="117"/>
     </row>
     <row r="12" spans="1:8" ht="27.95" customHeight="1">
-      <c r="A12" s="118" t="s">
-        <v>158</v>
-      </c>
-      <c r="B12" s="118" t="s">
+      <c r="A12" s="117" t="s">
         <v>155</v>
       </c>
-      <c r="C12" s="118" t="s">
-        <v>157</v>
-      </c>
-      <c r="D12" s="119">
+      <c r="B12" s="117" t="s">
+        <v>152</v>
+      </c>
+      <c r="C12" s="117" t="s">
+        <v>154</v>
+      </c>
+      <c r="D12" s="118">
         <v>93</v>
       </c>
-      <c r="E12" s="119">
+      <c r="E12" s="118">
         <f>'93'!P7</f>
         <v>0</v>
       </c>
-      <c r="F12" s="118" t="s">
-        <v>97</v>
-      </c>
-      <c r="G12" s="118"/>
-      <c r="H12" s="118"/>
+      <c r="F12" s="117" t="s">
+        <v>96</v>
+      </c>
+      <c r="G12" s="117"/>
+      <c r="H12" s="117"/>
     </row>
     <row r="13" spans="1:8" ht="27.95" customHeight="1">
-      <c r="A13" s="118" t="s">
-        <v>156</v>
-      </c>
-      <c r="B13" s="118" t="s">
-        <v>155</v>
-      </c>
-      <c r="C13" s="118" t="s">
-        <v>154</v>
-      </c>
-      <c r="D13" s="119">
+      <c r="A13" s="117" t="s">
+        <v>153</v>
+      </c>
+      <c r="B13" s="117" t="s">
+        <v>152</v>
+      </c>
+      <c r="C13" s="117" t="s">
+        <v>151</v>
+      </c>
+      <c r="D13" s="118">
         <v>93</v>
       </c>
-      <c r="E13" s="119">
+      <c r="E13" s="118">
         <f>'93'!R7</f>
         <v>0</v>
       </c>
-      <c r="F13" s="118" t="s">
-        <v>97</v>
-      </c>
-      <c r="G13" s="118"/>
-      <c r="H13" s="118"/>
+      <c r="F13" s="117" t="s">
+        <v>96</v>
+      </c>
+      <c r="G13" s="117"/>
+      <c r="H13" s="117"/>
     </row>
     <row r="14" spans="1:8" ht="27.95" customHeight="1">
-      <c r="A14" s="118" t="s">
-        <v>153</v>
-      </c>
-      <c r="B14" s="118" t="s">
-        <v>148</v>
-      </c>
-      <c r="C14" s="118" t="s">
-        <v>152</v>
-      </c>
-      <c r="D14" s="119">
+      <c r="A14" s="117" t="s">
+        <v>150</v>
+      </c>
+      <c r="B14" s="117" t="s">
+        <v>145</v>
+      </c>
+      <c r="C14" s="117" t="s">
+        <v>149</v>
+      </c>
+      <c r="D14" s="118">
         <v>93</v>
       </c>
-      <c r="E14" s="119">
+      <c r="E14" s="118">
         <f>'93'!J6</f>
         <v>0</v>
       </c>
-      <c r="F14" s="118" t="s">
-        <v>140</v>
-      </c>
-      <c r="G14" s="118" t="s">
-        <v>146</v>
-      </c>
-      <c r="H14" s="118"/>
+      <c r="F14" s="117" t="s">
+        <v>137</v>
+      </c>
+      <c r="G14" s="117" t="s">
+        <v>143</v>
+      </c>
+      <c r="H14" s="117"/>
     </row>
     <row r="15" spans="1:8" ht="27.95" customHeight="1">
-      <c r="A15" s="118" t="s">
-        <v>151</v>
-      </c>
-      <c r="B15" s="118" t="s">
+      <c r="A15" s="117" t="s">
         <v>148</v>
       </c>
-      <c r="C15" s="118" t="s">
-        <v>150</v>
-      </c>
-      <c r="D15" s="119">
+      <c r="B15" s="117" t="s">
+        <v>145</v>
+      </c>
+      <c r="C15" s="117" t="s">
+        <v>147</v>
+      </c>
+      <c r="D15" s="118">
         <v>93</v>
       </c>
-      <c r="E15" s="119">
+      <c r="E15" s="118">
         <f>'93'!K6</f>
         <v>0</v>
       </c>
-      <c r="F15" s="118" t="s">
-        <v>140</v>
-      </c>
-      <c r="G15" s="118" t="s">
-        <v>146</v>
-      </c>
-      <c r="H15" s="118"/>
+      <c r="F15" s="117" t="s">
+        <v>137</v>
+      </c>
+      <c r="G15" s="117" t="s">
+        <v>143</v>
+      </c>
+      <c r="H15" s="117"/>
     </row>
     <row r="16" spans="1:8" ht="27.95" customHeight="1">
-      <c r="A16" s="118" t="s">
-        <v>149</v>
-      </c>
-      <c r="B16" s="118" t="s">
-        <v>148</v>
-      </c>
-      <c r="C16" s="118" t="s">
-        <v>147</v>
-      </c>
-      <c r="D16" s="119">
+      <c r="A16" s="117" t="s">
+        <v>146</v>
+      </c>
+      <c r="B16" s="117" t="s">
+        <v>145</v>
+      </c>
+      <c r="C16" s="117" t="s">
+        <v>144</v>
+      </c>
+      <c r="D16" s="118">
         <v>93</v>
       </c>
-      <c r="E16" s="119">
+      <c r="E16" s="118">
         <f>'93'!L6</f>
         <v>0</v>
       </c>
-      <c r="F16" s="118" t="s">
+      <c r="F16" s="117" t="s">
         <v>81</v>
       </c>
-      <c r="G16" s="118" t="s">
-        <v>146</v>
-      </c>
-      <c r="H16" s="118" t="s">
-        <v>145</v>
+      <c r="G16" s="117" t="s">
+        <v>143</v>
+      </c>
+      <c r="H16" s="117" t="s">
+        <v>142</v>
       </c>
     </row>
     <row r="17" spans="1:8" ht="27.95" customHeight="1">
-      <c r="A17" s="118" t="s">
-        <v>144</v>
-      </c>
-      <c r="B17" s="118" t="s">
+      <c r="A17" s="117" t="s">
+        <v>141</v>
+      </c>
+      <c r="B17" s="117" t="s">
         <v>24</v>
       </c>
-      <c r="C17" s="118" t="s">
-        <v>143</v>
-      </c>
-      <c r="D17" s="119">
+      <c r="C17" s="117" t="s">
+        <v>140</v>
+      </c>
+      <c r="D17" s="118">
         <v>93</v>
       </c>
-      <c r="E17" s="119">
+      <c r="E17" s="118">
         <f>'93'!M10</f>
         <v>0</v>
       </c>
-      <c r="F17" s="118" t="s">
+      <c r="F17" s="117" t="s">
         <v>81</v>
       </c>
-      <c r="G17" s="118" t="s">
-        <v>80</v>
-      </c>
-      <c r="H17" s="118"/>
+      <c r="G17" s="117"/>
+      <c r="H17" s="117" t="s">
+        <v>182</v>
+      </c>
     </row>
     <row r="18" spans="1:8" ht="27.95" customHeight="1">
-      <c r="A18" s="118" t="s">
-        <v>142</v>
-      </c>
-      <c r="B18" s="118" t="s">
+      <c r="A18" s="117" t="s">
+        <v>139</v>
+      </c>
+      <c r="B18" s="117" t="s">
         <v>24</v>
       </c>
-      <c r="C18" s="118" t="s">
-        <v>141</v>
-      </c>
-      <c r="D18" s="119">
+      <c r="C18" s="117" t="s">
+        <v>140</v>
+      </c>
+      <c r="D18" s="118">
         <v>93</v>
       </c>
-      <c r="E18" s="119">
+      <c r="E18" s="118">
+        <f>'93'!M11</f>
+        <v>0</v>
+      </c>
+      <c r="F18" s="117" t="s">
+        <v>81</v>
+      </c>
+      <c r="G18" s="117"/>
+      <c r="H18" s="117"/>
+    </row>
+    <row r="19" spans="1:8" ht="27.95" customHeight="1">
+      <c r="A19" s="117" t="s">
+        <v>136</v>
+      </c>
+      <c r="B19" s="117" t="s">
+        <v>24</v>
+      </c>
+      <c r="C19" s="117" t="s">
+        <v>140</v>
+      </c>
+      <c r="D19" s="118">
+        <v>93</v>
+      </c>
+      <c r="E19" s="118">
+        <f>'93'!M12</f>
+        <v>0</v>
+      </c>
+      <c r="F19" s="117" t="s">
+        <v>81</v>
+      </c>
+      <c r="G19" s="117"/>
+      <c r="H19" s="117"/>
+    </row>
+    <row r="20" spans="1:8" ht="27.95" customHeight="1">
+      <c r="A20" s="117" t="s">
+        <v>134</v>
+      </c>
+      <c r="B20" s="117" t="s">
+        <v>24</v>
+      </c>
+      <c r="C20" s="117" t="s">
+        <v>140</v>
+      </c>
+      <c r="D20" s="118">
+        <v>93</v>
+      </c>
+      <c r="E20" s="118">
+        <f>'93'!M13</f>
+        <v>0</v>
+      </c>
+      <c r="F20" s="117" t="s">
+        <v>81</v>
+      </c>
+      <c r="G20" s="117"/>
+      <c r="H20" s="117"/>
+    </row>
+    <row r="21" spans="1:8" ht="27.95" customHeight="1">
+      <c r="A21" s="117" t="s">
+        <v>132</v>
+      </c>
+      <c r="B21" s="117" t="s">
+        <v>24</v>
+      </c>
+      <c r="C21" s="117" t="s">
+        <v>140</v>
+      </c>
+      <c r="D21" s="118">
+        <v>93</v>
+      </c>
+      <c r="E21" s="118">
+        <f>'93'!M14</f>
+        <v>0</v>
+      </c>
+      <c r="F21" s="117" t="s">
+        <v>81</v>
+      </c>
+      <c r="G21" s="117"/>
+      <c r="H21" s="117"/>
+    </row>
+    <row r="22" spans="1:8" ht="27.95" customHeight="1">
+      <c r="A22" s="117" t="s">
+        <v>130</v>
+      </c>
+      <c r="B22" s="117" t="s">
+        <v>24</v>
+      </c>
+      <c r="C22" s="117" t="s">
+        <v>140</v>
+      </c>
+      <c r="D22" s="118">
+        <v>93</v>
+      </c>
+      <c r="E22" s="118">
+        <f>'93'!M15</f>
+        <v>0</v>
+      </c>
+      <c r="F22" s="117" t="s">
+        <v>81</v>
+      </c>
+      <c r="G22" s="117"/>
+      <c r="H22" s="117"/>
+    </row>
+    <row r="23" spans="1:8" ht="27.95" customHeight="1">
+      <c r="A23" s="117" t="s">
+        <v>127</v>
+      </c>
+      <c r="B23" s="117" t="s">
+        <v>24</v>
+      </c>
+      <c r="C23" s="117" t="s">
+        <v>140</v>
+      </c>
+      <c r="D23" s="118">
+        <v>93</v>
+      </c>
+      <c r="E23" s="118">
+        <f>'93'!M16</f>
+        <v>0</v>
+      </c>
+      <c r="F23" s="117" t="s">
+        <v>81</v>
+      </c>
+      <c r="G23" s="117"/>
+      <c r="H23" s="117"/>
+    </row>
+    <row r="24" spans="1:8" ht="27.95" customHeight="1">
+      <c r="A24" s="117" t="s">
+        <v>125</v>
+      </c>
+      <c r="B24" s="117" t="s">
+        <v>24</v>
+      </c>
+      <c r="C24" s="117" t="s">
+        <v>140</v>
+      </c>
+      <c r="D24" s="118">
+        <v>93</v>
+      </c>
+      <c r="E24" s="118">
+        <f>'93'!P10</f>
+        <v>0</v>
+      </c>
+      <c r="F24" s="117" t="s">
+        <v>81</v>
+      </c>
+      <c r="G24" s="117"/>
+      <c r="H24" s="117" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" ht="27.95" customHeight="1">
+      <c r="A25" s="117" t="s">
+        <v>121</v>
+      </c>
+      <c r="B25" s="117" t="s">
+        <v>24</v>
+      </c>
+      <c r="C25" s="117" t="s">
+        <v>140</v>
+      </c>
+      <c r="D25" s="118">
+        <v>93</v>
+      </c>
+      <c r="E25" s="118">
+        <f>'93'!P11</f>
+        <v>0</v>
+      </c>
+      <c r="F25" s="117" t="s">
+        <v>81</v>
+      </c>
+      <c r="G25" s="117"/>
+      <c r="H25" s="117"/>
+    </row>
+    <row r="26" spans="1:8" ht="27.95" customHeight="1">
+      <c r="A26" s="117" t="s">
+        <v>120</v>
+      </c>
+      <c r="B26" s="117" t="s">
+        <v>24</v>
+      </c>
+      <c r="C26" s="117" t="s">
+        <v>140</v>
+      </c>
+      <c r="D26" s="118">
+        <v>93</v>
+      </c>
+      <c r="E26" s="118">
+        <f>'93'!P12</f>
+        <v>0</v>
+      </c>
+      <c r="F26" s="117" t="s">
+        <v>81</v>
+      </c>
+      <c r="G26" s="117"/>
+      <c r="H26" s="117"/>
+    </row>
+    <row r="27" spans="1:8" ht="27.95" customHeight="1">
+      <c r="A27" s="117" t="s">
+        <v>118</v>
+      </c>
+      <c r="B27" s="117" t="s">
+        <v>24</v>
+      </c>
+      <c r="C27" s="117" t="s">
+        <v>140</v>
+      </c>
+      <c r="D27" s="118">
+        <v>93</v>
+      </c>
+      <c r="E27" s="118">
+        <f>'93'!P13</f>
+        <v>0</v>
+      </c>
+      <c r="F27" s="117" t="s">
+        <v>81</v>
+      </c>
+      <c r="G27" s="117"/>
+      <c r="H27" s="117"/>
+    </row>
+    <row r="28" spans="1:8" ht="27.95" customHeight="1">
+      <c r="A28" s="117" t="s">
+        <v>115</v>
+      </c>
+      <c r="B28" s="117" t="s">
+        <v>24</v>
+      </c>
+      <c r="C28" s="117" t="s">
+        <v>140</v>
+      </c>
+      <c r="D28" s="118">
+        <v>93</v>
+      </c>
+      <c r="E28" s="118">
+        <f>'93'!P14</f>
+        <v>0</v>
+      </c>
+      <c r="F28" s="117" t="s">
+        <v>81</v>
+      </c>
+      <c r="G28" s="117"/>
+      <c r="H28" s="117"/>
+    </row>
+    <row r="29" spans="1:8" ht="27.95" customHeight="1">
+      <c r="A29" s="117" t="s">
+        <v>113</v>
+      </c>
+      <c r="B29" s="117" t="s">
+        <v>24</v>
+      </c>
+      <c r="C29" s="117" t="s">
+        <v>140</v>
+      </c>
+      <c r="D29" s="118">
+        <v>93</v>
+      </c>
+      <c r="E29" s="118">
+        <f>'93'!P15</f>
+        <v>0</v>
+      </c>
+      <c r="F29" s="117" t="s">
+        <v>81</v>
+      </c>
+      <c r="G29" s="117"/>
+      <c r="H29" s="117"/>
+    </row>
+    <row r="30" spans="1:8" ht="27.95" customHeight="1">
+      <c r="A30" s="117" t="s">
+        <v>111</v>
+      </c>
+      <c r="B30" s="117" t="s">
+        <v>24</v>
+      </c>
+      <c r="C30" s="117" t="s">
+        <v>140</v>
+      </c>
+      <c r="D30" s="118">
+        <v>93</v>
+      </c>
+      <c r="E30" s="118">
+        <f>'93'!P16</f>
+        <v>0</v>
+      </c>
+      <c r="F30" s="117" t="s">
+        <v>81</v>
+      </c>
+      <c r="G30" s="117"/>
+      <c r="H30" s="117"/>
+    </row>
+    <row r="31" spans="1:8" ht="27.95" customHeight="1">
+      <c r="A31" s="117" t="s">
+        <v>109</v>
+      </c>
+      <c r="B31" s="117" t="s">
+        <v>24</v>
+      </c>
+      <c r="C31" s="117" t="s">
+        <v>138</v>
+      </c>
+      <c r="D31" s="118">
+        <v>93</v>
+      </c>
+      <c r="E31" s="118">
         <f>'93'!N10</f>
         <v>0</v>
       </c>
-      <c r="F18" s="118" t="s">
-        <v>140</v>
-      </c>
-      <c r="G18" s="118" t="s">
-        <v>80</v>
-      </c>
-      <c r="H18" s="118"/>
+      <c r="F31" s="117" t="s">
+        <v>137</v>
+      </c>
+      <c r="G31" s="117"/>
+      <c r="H31" s="117" t="s">
+        <v>182</v>
+      </c>
     </row>
-    <row r="19" spans="1:8" ht="27.95" customHeight="1">
-      <c r="A19" s="118" t="s">
-        <v>139</v>
-      </c>
-      <c r="B19" s="118" t="s">
+    <row r="32" spans="1:8" ht="27.95" customHeight="1">
+      <c r="A32" s="117" t="s">
+        <v>107</v>
+      </c>
+      <c r="B32" s="117" t="s">
+        <v>24</v>
+      </c>
+      <c r="C32" s="117" t="s">
+        <v>138</v>
+      </c>
+      <c r="D32" s="118">
+        <v>93</v>
+      </c>
+      <c r="E32" s="118">
+        <f>'93'!N11</f>
+        <v>0</v>
+      </c>
+      <c r="F32" s="117" t="s">
+        <v>137</v>
+      </c>
+      <c r="G32" s="117"/>
+      <c r="H32" s="117"/>
+    </row>
+    <row r="33" spans="1:8" ht="27.95" customHeight="1">
+      <c r="A33" s="117" t="s">
+        <v>103</v>
+      </c>
+      <c r="B33" s="117" t="s">
+        <v>24</v>
+      </c>
+      <c r="C33" s="117" t="s">
+        <v>138</v>
+      </c>
+      <c r="D33" s="118">
+        <v>93</v>
+      </c>
+      <c r="E33" s="118">
+        <f>'93'!N12</f>
+        <v>0</v>
+      </c>
+      <c r="F33" s="117" t="s">
+        <v>137</v>
+      </c>
+      <c r="G33" s="117"/>
+      <c r="H33" s="117"/>
+    </row>
+    <row r="34" spans="1:8" ht="27.95" customHeight="1">
+      <c r="A34" s="117" t="s">
+        <v>101</v>
+      </c>
+      <c r="B34" s="117" t="s">
+        <v>24</v>
+      </c>
+      <c r="C34" s="117" t="s">
+        <v>138</v>
+      </c>
+      <c r="D34" s="118">
+        <v>93</v>
+      </c>
+      <c r="E34" s="118">
+        <f>'93'!N13</f>
+        <v>0</v>
+      </c>
+      <c r="F34" s="117" t="s">
+        <v>137</v>
+      </c>
+      <c r="G34" s="117"/>
+      <c r="H34" s="117"/>
+    </row>
+    <row r="35" spans="1:8" ht="27.95" customHeight="1">
+      <c r="A35" s="117" t="s">
+        <v>99</v>
+      </c>
+      <c r="B35" s="117" t="s">
+        <v>24</v>
+      </c>
+      <c r="C35" s="117" t="s">
+        <v>138</v>
+      </c>
+      <c r="D35" s="118">
+        <v>93</v>
+      </c>
+      <c r="E35" s="118">
+        <f>'93'!N14</f>
+        <v>0</v>
+      </c>
+      <c r="F35" s="117" t="s">
+        <v>137</v>
+      </c>
+      <c r="G35" s="117"/>
+      <c r="H35" s="117"/>
+    </row>
+    <row r="36" spans="1:8" ht="27.95" customHeight="1">
+      <c r="A36" s="117" t="s">
+        <v>94</v>
+      </c>
+      <c r="B36" s="117" t="s">
+        <v>24</v>
+      </c>
+      <c r="C36" s="117" t="s">
+        <v>138</v>
+      </c>
+      <c r="D36" s="118">
+        <v>93</v>
+      </c>
+      <c r="E36" s="118">
+        <f>'93'!N15</f>
+        <v>0</v>
+      </c>
+      <c r="F36" s="117" t="s">
+        <v>137</v>
+      </c>
+      <c r="G36" s="117"/>
+      <c r="H36" s="117"/>
+    </row>
+    <row r="37" spans="1:8" ht="27.95" customHeight="1">
+      <c r="A37" s="117" t="s">
+        <v>90</v>
+      </c>
+      <c r="B37" s="117" t="s">
+        <v>24</v>
+      </c>
+      <c r="C37" s="117" t="s">
+        <v>138</v>
+      </c>
+      <c r="D37" s="118">
+        <v>93</v>
+      </c>
+      <c r="E37" s="118">
+        <f>'93'!N16</f>
+        <v>0</v>
+      </c>
+      <c r="F37" s="117" t="s">
+        <v>137</v>
+      </c>
+      <c r="G37" s="117"/>
+      <c r="H37" s="117"/>
+    </row>
+    <row r="38" spans="1:8" ht="27.95" customHeight="1">
+      <c r="A38" s="117" t="s">
+        <v>88</v>
+      </c>
+      <c r="B38" s="117" t="s">
+        <v>24</v>
+      </c>
+      <c r="C38" s="117" t="s">
+        <v>138</v>
+      </c>
+      <c r="D38" s="118">
+        <v>93</v>
+      </c>
+      <c r="E38" s="118">
+        <f>'93'!Q10</f>
+        <v>0</v>
+      </c>
+      <c r="F38" s="117" t="s">
+        <v>137</v>
+      </c>
+      <c r="G38" s="117"/>
+      <c r="H38" s="117" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8" ht="27.95" customHeight="1">
+      <c r="A39" s="117" t="s">
+        <v>85</v>
+      </c>
+      <c r="B39" s="117" t="s">
+        <v>24</v>
+      </c>
+      <c r="C39" s="117" t="s">
+        <v>138</v>
+      </c>
+      <c r="D39" s="118">
+        <v>93</v>
+      </c>
+      <c r="E39" s="118">
+        <f>'93'!Q11</f>
+        <v>0</v>
+      </c>
+      <c r="F39" s="117" t="s">
+        <v>137</v>
+      </c>
+      <c r="G39" s="117"/>
+      <c r="H39" s="117"/>
+    </row>
+    <row r="40" spans="1:8" ht="27.95" customHeight="1">
+      <c r="A40" s="117" t="s">
+        <v>83</v>
+      </c>
+      <c r="B40" s="117" t="s">
+        <v>24</v>
+      </c>
+      <c r="C40" s="117" t="s">
+        <v>138</v>
+      </c>
+      <c r="D40" s="118">
+        <v>93</v>
+      </c>
+      <c r="E40" s="118">
+        <f>'93'!Q12</f>
+        <v>0</v>
+      </c>
+      <c r="F40" s="117" t="s">
+        <v>137</v>
+      </c>
+      <c r="G40" s="117"/>
+      <c r="H40" s="117"/>
+    </row>
+    <row r="41" spans="1:8" ht="27.95" customHeight="1">
+      <c r="A41" s="117" t="s">
+        <v>190</v>
+      </c>
+      <c r="B41" s="117" t="s">
+        <v>24</v>
+      </c>
+      <c r="C41" s="117" t="s">
+        <v>138</v>
+      </c>
+      <c r="D41" s="118">
+        <v>93</v>
+      </c>
+      <c r="E41" s="118">
+        <f>'93'!Q13</f>
+        <v>0</v>
+      </c>
+      <c r="F41" s="117" t="s">
+        <v>137</v>
+      </c>
+      <c r="G41" s="117"/>
+      <c r="H41" s="117"/>
+    </row>
+    <row r="42" spans="1:8" ht="27.95" customHeight="1">
+      <c r="A42" s="117" t="s">
+        <v>191</v>
+      </c>
+      <c r="B42" s="117" t="s">
+        <v>24</v>
+      </c>
+      <c r="C42" s="117" t="s">
+        <v>138</v>
+      </c>
+      <c r="D42" s="118">
+        <v>93</v>
+      </c>
+      <c r="E42" s="118">
+        <f>'93'!Q14</f>
+        <v>0</v>
+      </c>
+      <c r="F42" s="117" t="s">
+        <v>137</v>
+      </c>
+      <c r="G42" s="117"/>
+      <c r="H42" s="117"/>
+    </row>
+    <row r="43" spans="1:8" ht="27.95" customHeight="1">
+      <c r="A43" s="117" t="s">
+        <v>192</v>
+      </c>
+      <c r="B43" s="117" t="s">
+        <v>24</v>
+      </c>
+      <c r="C43" s="117" t="s">
+        <v>138</v>
+      </c>
+      <c r="D43" s="118">
+        <v>93</v>
+      </c>
+      <c r="E43" s="118">
+        <f>'93'!Q15</f>
+        <v>0</v>
+      </c>
+      <c r="F43" s="117" t="s">
+        <v>137</v>
+      </c>
+      <c r="G43" s="117"/>
+      <c r="H43" s="117"/>
+    </row>
+    <row r="44" spans="1:8" ht="27.95" customHeight="1">
+      <c r="A44" s="117" t="s">
+        <v>193</v>
+      </c>
+      <c r="B44" s="117" t="s">
+        <v>24</v>
+      </c>
+      <c r="C44" s="117" t="s">
+        <v>138</v>
+      </c>
+      <c r="D44" s="118">
+        <v>93</v>
+      </c>
+      <c r="E44" s="118">
+        <f>'93'!Q16</f>
+        <v>0</v>
+      </c>
+      <c r="F44" s="117" t="s">
+        <v>137</v>
+      </c>
+      <c r="G44" s="117"/>
+      <c r="H44" s="117"/>
+    </row>
+    <row r="45" spans="1:8" ht="27.95" customHeight="1">
+      <c r="A45" s="117" t="s">
+        <v>194</v>
+      </c>
+      <c r="B45" s="117" t="s">
         <v>25</v>
       </c>
-      <c r="C19" s="118" t="s">
-        <v>138</v>
-      </c>
-      <c r="D19" s="119">
+      <c r="C45" s="117" t="s">
+        <v>135</v>
+      </c>
+      <c r="D45" s="118">
         <v>93</v>
       </c>
-      <c r="E19" s="119">
+      <c r="E45" s="118">
         <f>'93'!M19</f>
         <v>0</v>
       </c>
-      <c r="F19" s="118" t="s">
+      <c r="F45" s="117" t="s">
         <v>81</v>
       </c>
-      <c r="G19" s="118" t="s">
-        <v>80</v>
-      </c>
-      <c r="H19" s="118"/>
+      <c r="G45" s="117"/>
+      <c r="H45" s="117" t="s">
+        <v>182</v>
+      </c>
     </row>
-    <row r="20" spans="1:8" ht="27.95" customHeight="1">
-      <c r="A20" s="118" t="s">
-        <v>137</v>
-      </c>
-      <c r="B20" s="118" t="s">
+    <row r="46" spans="1:8" ht="27.95" customHeight="1">
+      <c r="A46" s="117" t="s">
+        <v>195</v>
+      </c>
+      <c r="B46" s="117" t="s">
         <v>25</v>
       </c>
-      <c r="C20" s="118" t="s">
-        <v>136</v>
-      </c>
-      <c r="D20" s="119">
+      <c r="C46" s="117" t="s">
+        <v>135</v>
+      </c>
+      <c r="D46" s="118">
         <v>93</v>
       </c>
-      <c r="E20" s="119">
+      <c r="E46" s="118">
+        <f>'93'!M20</f>
+        <v>0</v>
+      </c>
+      <c r="F46" s="117" t="s">
+        <v>81</v>
+      </c>
+      <c r="G46" s="117"/>
+      <c r="H46" s="117"/>
+    </row>
+    <row r="47" spans="1:8" ht="27.95" customHeight="1">
+      <c r="A47" s="117" t="s">
+        <v>196</v>
+      </c>
+      <c r="B47" s="117" t="s">
+        <v>25</v>
+      </c>
+      <c r="C47" s="117" t="s">
+        <v>135</v>
+      </c>
+      <c r="D47" s="118">
+        <v>93</v>
+      </c>
+      <c r="E47" s="118">
+        <f>'93'!M21</f>
+        <v>0</v>
+      </c>
+      <c r="F47" s="117" t="s">
+        <v>81</v>
+      </c>
+      <c r="G47" s="117"/>
+      <c r="H47" s="117"/>
+    </row>
+    <row r="48" spans="1:8" ht="27.95" customHeight="1">
+      <c r="A48" s="117" t="s">
+        <v>197</v>
+      </c>
+      <c r="B48" s="117" t="s">
+        <v>25</v>
+      </c>
+      <c r="C48" s="117" t="s">
+        <v>135</v>
+      </c>
+      <c r="D48" s="118">
+        <v>93</v>
+      </c>
+      <c r="E48" s="118">
+        <f>'93'!M22</f>
+        <v>0</v>
+      </c>
+      <c r="F48" s="117" t="s">
+        <v>81</v>
+      </c>
+      <c r="G48" s="117"/>
+      <c r="H48" s="117"/>
+    </row>
+    <row r="49" spans="1:8" ht="27.95" customHeight="1">
+      <c r="A49" s="117" t="s">
+        <v>198</v>
+      </c>
+      <c r="B49" s="117" t="s">
+        <v>25</v>
+      </c>
+      <c r="C49" s="117" t="s">
+        <v>135</v>
+      </c>
+      <c r="D49" s="118">
+        <v>93</v>
+      </c>
+      <c r="E49" s="118">
+        <f>'93'!M23</f>
+        <v>0</v>
+      </c>
+      <c r="F49" s="117" t="s">
+        <v>81</v>
+      </c>
+      <c r="G49" s="117"/>
+      <c r="H49" s="117"/>
+    </row>
+    <row r="50" spans="1:8" ht="27.95" customHeight="1">
+      <c r="A50" s="117" t="s">
+        <v>199</v>
+      </c>
+      <c r="B50" s="117" t="s">
+        <v>25</v>
+      </c>
+      <c r="C50" s="117" t="s">
+        <v>135</v>
+      </c>
+      <c r="D50" s="118">
+        <v>93</v>
+      </c>
+      <c r="E50" s="118">
+        <f>'93'!M24</f>
+        <v>0</v>
+      </c>
+      <c r="F50" s="117" t="s">
+        <v>81</v>
+      </c>
+      <c r="G50" s="117"/>
+      <c r="H50" s="117"/>
+    </row>
+    <row r="51" spans="1:8" ht="27.95" customHeight="1">
+      <c r="A51" s="117" t="s">
+        <v>200</v>
+      </c>
+      <c r="B51" s="117" t="s">
+        <v>25</v>
+      </c>
+      <c r="C51" s="117" t="s">
+        <v>135</v>
+      </c>
+      <c r="D51" s="118">
+        <v>93</v>
+      </c>
+      <c r="E51" s="118">
+        <f>'93'!M25</f>
+        <v>0</v>
+      </c>
+      <c r="F51" s="117" t="s">
+        <v>81</v>
+      </c>
+      <c r="G51" s="117"/>
+      <c r="H51" s="117"/>
+    </row>
+    <row r="52" spans="1:8" ht="27.95" customHeight="1">
+      <c r="A52" s="117" t="s">
+        <v>201</v>
+      </c>
+      <c r="B52" s="117" t="s">
+        <v>25</v>
+      </c>
+      <c r="C52" s="117" t="s">
+        <v>135</v>
+      </c>
+      <c r="D52" s="118">
+        <v>93</v>
+      </c>
+      <c r="E52" s="118">
+        <f>'93'!M26</f>
+        <v>0</v>
+      </c>
+      <c r="F52" s="117" t="s">
+        <v>81</v>
+      </c>
+      <c r="G52" s="117"/>
+      <c r="H52" s="117"/>
+    </row>
+    <row r="53" spans="1:8" ht="27.95" customHeight="1">
+      <c r="A53" s="117" t="s">
+        <v>202</v>
+      </c>
+      <c r="B53" s="117" t="s">
+        <v>25</v>
+      </c>
+      <c r="C53" s="117" t="s">
+        <v>135</v>
+      </c>
+      <c r="D53" s="118">
+        <v>93</v>
+      </c>
+      <c r="E53" s="118">
+        <f>'93'!M27</f>
+        <v>0</v>
+      </c>
+      <c r="F53" s="117" t="s">
+        <v>81</v>
+      </c>
+      <c r="G53" s="117"/>
+      <c r="H53" s="117"/>
+    </row>
+    <row r="54" spans="1:8" ht="27.95" customHeight="1">
+      <c r="A54" s="117" t="s">
+        <v>203</v>
+      </c>
+      <c r="B54" s="117" t="s">
+        <v>25</v>
+      </c>
+      <c r="C54" s="117" t="s">
+        <v>135</v>
+      </c>
+      <c r="D54" s="118">
+        <v>93</v>
+      </c>
+      <c r="E54" s="118">
+        <f>'93'!M28</f>
+        <v>0</v>
+      </c>
+      <c r="F54" s="117" t="s">
+        <v>81</v>
+      </c>
+      <c r="G54" s="117"/>
+      <c r="H54" s="117"/>
+    </row>
+    <row r="55" spans="1:8" ht="27.95" customHeight="1">
+      <c r="A55" s="117" t="s">
+        <v>204</v>
+      </c>
+      <c r="B55" s="117" t="s">
+        <v>25</v>
+      </c>
+      <c r="C55" s="117" t="s">
+        <v>135</v>
+      </c>
+      <c r="D55" s="118">
+        <v>93</v>
+      </c>
+      <c r="E55" s="118">
+        <f>'93'!M29</f>
+        <v>0</v>
+      </c>
+      <c r="F55" s="117" t="s">
+        <v>81</v>
+      </c>
+      <c r="G55" s="117"/>
+      <c r="H55" s="117"/>
+    </row>
+    <row r="56" spans="1:8" ht="27.95" customHeight="1">
+      <c r="A56" s="117" t="s">
+        <v>205</v>
+      </c>
+      <c r="B56" s="117" t="s">
+        <v>25</v>
+      </c>
+      <c r="C56" s="117" t="s">
+        <v>135</v>
+      </c>
+      <c r="D56" s="118">
+        <v>93</v>
+      </c>
+      <c r="E56" s="118">
+        <f>'93'!M30</f>
+        <v>0</v>
+      </c>
+      <c r="F56" s="117" t="s">
+        <v>81</v>
+      </c>
+      <c r="G56" s="117"/>
+      <c r="H56" s="117"/>
+    </row>
+    <row r="57" spans="1:8" ht="27.95" customHeight="1">
+      <c r="A57" s="117" t="s">
+        <v>206</v>
+      </c>
+      <c r="B57" s="117" t="s">
+        <v>25</v>
+      </c>
+      <c r="C57" s="117" t="s">
+        <v>135</v>
+      </c>
+      <c r="D57" s="118">
+        <v>93</v>
+      </c>
+      <c r="E57" s="118">
+        <f>'93'!P19</f>
+        <v>0</v>
+      </c>
+      <c r="F57" s="117" t="s">
+        <v>81</v>
+      </c>
+      <c r="G57" s="117"/>
+      <c r="H57" s="117" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="58" spans="1:8" ht="27.95" customHeight="1">
+      <c r="A58" s="117" t="s">
+        <v>207</v>
+      </c>
+      <c r="B58" s="117" t="s">
+        <v>25</v>
+      </c>
+      <c r="C58" s="117" t="s">
+        <v>135</v>
+      </c>
+      <c r="D58" s="118">
+        <v>93</v>
+      </c>
+      <c r="E58" s="118">
+        <f>'93'!P20</f>
+        <v>0</v>
+      </c>
+      <c r="F58" s="117" t="s">
+        <v>81</v>
+      </c>
+      <c r="G58" s="117"/>
+      <c r="H58" s="117"/>
+    </row>
+    <row r="59" spans="1:8" ht="27.95" customHeight="1">
+      <c r="A59" s="117" t="s">
+        <v>208</v>
+      </c>
+      <c r="B59" s="117" t="s">
+        <v>25</v>
+      </c>
+      <c r="C59" s="117" t="s">
+        <v>135</v>
+      </c>
+      <c r="D59" s="118">
+        <v>93</v>
+      </c>
+      <c r="E59" s="118">
+        <f>'93'!P21</f>
+        <v>0</v>
+      </c>
+      <c r="F59" s="117" t="s">
+        <v>81</v>
+      </c>
+      <c r="G59" s="117"/>
+      <c r="H59" s="117"/>
+    </row>
+    <row r="60" spans="1:8" ht="27.95" customHeight="1">
+      <c r="A60" s="117" t="s">
+        <v>209</v>
+      </c>
+      <c r="B60" s="117" t="s">
+        <v>25</v>
+      </c>
+      <c r="C60" s="117" t="s">
+        <v>135</v>
+      </c>
+      <c r="D60" s="118">
+        <v>93</v>
+      </c>
+      <c r="E60" s="118">
+        <f>'93'!P22</f>
+        <v>0</v>
+      </c>
+      <c r="F60" s="117" t="s">
+        <v>81</v>
+      </c>
+      <c r="G60" s="117"/>
+      <c r="H60" s="117"/>
+    </row>
+    <row r="61" spans="1:8" ht="27.95" customHeight="1">
+      <c r="A61" s="117" t="s">
+        <v>210</v>
+      </c>
+      <c r="B61" s="117" t="s">
+        <v>25</v>
+      </c>
+      <c r="C61" s="117" t="s">
+        <v>135</v>
+      </c>
+      <c r="D61" s="118">
+        <v>93</v>
+      </c>
+      <c r="E61" s="118">
+        <f>'93'!P23</f>
+        <v>0</v>
+      </c>
+      <c r="F61" s="117" t="s">
+        <v>81</v>
+      </c>
+      <c r="G61" s="117"/>
+      <c r="H61" s="117"/>
+    </row>
+    <row r="62" spans="1:8" ht="27.95" customHeight="1">
+      <c r="A62" s="117" t="s">
+        <v>211</v>
+      </c>
+      <c r="B62" s="117" t="s">
+        <v>25</v>
+      </c>
+      <c r="C62" s="117" t="s">
+        <v>135</v>
+      </c>
+      <c r="D62" s="118">
+        <v>93</v>
+      </c>
+      <c r="E62" s="118">
+        <f>'93'!P24</f>
+        <v>0</v>
+      </c>
+      <c r="F62" s="117" t="s">
+        <v>81</v>
+      </c>
+      <c r="G62" s="117"/>
+      <c r="H62" s="117"/>
+    </row>
+    <row r="63" spans="1:8" ht="27.95" customHeight="1">
+      <c r="A63" s="117" t="s">
+        <v>212</v>
+      </c>
+      <c r="B63" s="117" t="s">
+        <v>25</v>
+      </c>
+      <c r="C63" s="117" t="s">
+        <v>135</v>
+      </c>
+      <c r="D63" s="118">
+        <v>93</v>
+      </c>
+      <c r="E63" s="118">
+        <f>'93'!P25</f>
+        <v>0</v>
+      </c>
+      <c r="F63" s="117" t="s">
+        <v>81</v>
+      </c>
+      <c r="G63" s="117"/>
+      <c r="H63" s="117"/>
+    </row>
+    <row r="64" spans="1:8" ht="27.95" customHeight="1">
+      <c r="A64" s="117" t="s">
+        <v>213</v>
+      </c>
+      <c r="B64" s="117" t="s">
+        <v>25</v>
+      </c>
+      <c r="C64" s="117" t="s">
+        <v>135</v>
+      </c>
+      <c r="D64" s="118">
+        <v>93</v>
+      </c>
+      <c r="E64" s="118">
+        <f>'93'!P26</f>
+        <v>0</v>
+      </c>
+      <c r="F64" s="117" t="s">
+        <v>81</v>
+      </c>
+      <c r="G64" s="117"/>
+      <c r="H64" s="117"/>
+    </row>
+    <row r="65" spans="1:8" ht="27.95" customHeight="1">
+      <c r="A65" s="117" t="s">
+        <v>214</v>
+      </c>
+      <c r="B65" s="117" t="s">
+        <v>25</v>
+      </c>
+      <c r="C65" s="117" t="s">
+        <v>135</v>
+      </c>
+      <c r="D65" s="118">
+        <v>93</v>
+      </c>
+      <c r="E65" s="118">
+        <f>'93'!P27</f>
+        <v>0</v>
+      </c>
+      <c r="F65" s="117" t="s">
+        <v>81</v>
+      </c>
+      <c r="G65" s="117"/>
+      <c r="H65" s="117"/>
+    </row>
+    <row r="66" spans="1:8" ht="27.95" customHeight="1">
+      <c r="A66" s="117" t="s">
+        <v>215</v>
+      </c>
+      <c r="B66" s="117" t="s">
+        <v>25</v>
+      </c>
+      <c r="C66" s="117" t="s">
+        <v>135</v>
+      </c>
+      <c r="D66" s="118">
+        <v>93</v>
+      </c>
+      <c r="E66" s="118">
+        <f>'93'!P28</f>
+        <v>0</v>
+      </c>
+      <c r="F66" s="117" t="s">
+        <v>81</v>
+      </c>
+      <c r="G66" s="117"/>
+      <c r="H66" s="117"/>
+    </row>
+    <row r="67" spans="1:8" ht="27.95" customHeight="1">
+      <c r="A67" s="117" t="s">
+        <v>216</v>
+      </c>
+      <c r="B67" s="117" t="s">
+        <v>25</v>
+      </c>
+      <c r="C67" s="117" t="s">
+        <v>135</v>
+      </c>
+      <c r="D67" s="118">
+        <v>93</v>
+      </c>
+      <c r="E67" s="118">
+        <f>'93'!P29</f>
+        <v>0</v>
+      </c>
+      <c r="F67" s="117" t="s">
+        <v>81</v>
+      </c>
+      <c r="G67" s="117"/>
+      <c r="H67" s="117"/>
+    </row>
+    <row r="68" spans="1:8" ht="27.95" customHeight="1">
+      <c r="A68" s="117" t="s">
+        <v>217</v>
+      </c>
+      <c r="B68" s="117" t="s">
+        <v>25</v>
+      </c>
+      <c r="C68" s="117" t="s">
+        <v>135</v>
+      </c>
+      <c r="D68" s="118">
+        <v>93</v>
+      </c>
+      <c r="E68" s="118">
+        <f>'93'!P30</f>
+        <v>0</v>
+      </c>
+      <c r="F68" s="117" t="s">
+        <v>81</v>
+      </c>
+      <c r="G68" s="117"/>
+      <c r="H68" s="117"/>
+    </row>
+    <row r="69" spans="1:8" ht="27.95" customHeight="1">
+      <c r="A69" s="117" t="s">
+        <v>218</v>
+      </c>
+      <c r="B69" s="117" t="s">
+        <v>25</v>
+      </c>
+      <c r="C69" s="117" t="s">
+        <v>133</v>
+      </c>
+      <c r="D69" s="118">
+        <v>93</v>
+      </c>
+      <c r="E69" s="118">
         <f>'93'!N19</f>
         <v>0</v>
       </c>
-      <c r="F20" s="118" t="s">
-        <v>87</v>
-      </c>
-      <c r="G20" s="118" t="s">
-        <v>80</v>
-      </c>
-      <c r="H20" s="118"/>
+      <c r="F69" s="117" t="s">
+        <v>86</v>
+      </c>
+      <c r="G69" s="117"/>
+      <c r="H69" s="117" t="s">
+        <v>182</v>
+      </c>
     </row>
-    <row r="21" spans="1:8" ht="27.95" customHeight="1">
-      <c r="A21" s="118" t="s">
-        <v>135</v>
-      </c>
-      <c r="B21" s="118" t="s">
+    <row r="70" spans="1:8" ht="27.95" customHeight="1">
+      <c r="A70" s="117" t="s">
+        <v>219</v>
+      </c>
+      <c r="B70" s="117" t="s">
         <v>25</v>
       </c>
-      <c r="C21" s="118" t="s">
-        <v>134</v>
-      </c>
-      <c r="D21" s="119">
+      <c r="C70" s="117" t="s">
+        <v>133</v>
+      </c>
+      <c r="D70" s="118">
         <v>93</v>
       </c>
-      <c r="E21" s="119">
+      <c r="E70" s="118">
+        <f>'93'!N20</f>
+        <v>0</v>
+      </c>
+      <c r="F70" s="117" t="s">
+        <v>86</v>
+      </c>
+      <c r="G70" s="117"/>
+      <c r="H70" s="117"/>
+    </row>
+    <row r="71" spans="1:8" ht="27.95" customHeight="1">
+      <c r="A71" s="117" t="s">
+        <v>220</v>
+      </c>
+      <c r="B71" s="117" t="s">
+        <v>25</v>
+      </c>
+      <c r="C71" s="117" t="s">
+        <v>133</v>
+      </c>
+      <c r="D71" s="118">
+        <v>93</v>
+      </c>
+      <c r="E71" s="118">
+        <f>'93'!N21</f>
+        <v>0</v>
+      </c>
+      <c r="F71" s="117" t="s">
+        <v>86</v>
+      </c>
+      <c r="G71" s="117"/>
+      <c r="H71" s="117"/>
+    </row>
+    <row r="72" spans="1:8" ht="27.95" customHeight="1">
+      <c r="A72" s="117" t="s">
+        <v>221</v>
+      </c>
+      <c r="B72" s="117" t="s">
+        <v>25</v>
+      </c>
+      <c r="C72" s="117" t="s">
+        <v>133</v>
+      </c>
+      <c r="D72" s="118">
+        <v>93</v>
+      </c>
+      <c r="E72" s="118">
+        <f>'93'!N22</f>
+        <v>0</v>
+      </c>
+      <c r="F72" s="117" t="s">
+        <v>86</v>
+      </c>
+      <c r="G72" s="117"/>
+      <c r="H72" s="117"/>
+    </row>
+    <row r="73" spans="1:8" ht="27.95" customHeight="1">
+      <c r="A73" s="117" t="s">
+        <v>222</v>
+      </c>
+      <c r="B73" s="117" t="s">
+        <v>25</v>
+      </c>
+      <c r="C73" s="117" t="s">
+        <v>133</v>
+      </c>
+      <c r="D73" s="118">
+        <v>93</v>
+      </c>
+      <c r="E73" s="118">
+        <f>'93'!N23</f>
+        <v>0</v>
+      </c>
+      <c r="F73" s="117" t="s">
+        <v>86</v>
+      </c>
+      <c r="G73" s="117"/>
+      <c r="H73" s="117"/>
+    </row>
+    <row r="74" spans="1:8" ht="27.95" customHeight="1">
+      <c r="A74" s="117" t="s">
+        <v>223</v>
+      </c>
+      <c r="B74" s="117" t="s">
+        <v>25</v>
+      </c>
+      <c r="C74" s="117" t="s">
+        <v>133</v>
+      </c>
+      <c r="D74" s="118">
+        <v>93</v>
+      </c>
+      <c r="E74" s="118">
+        <f>'93'!N24</f>
+        <v>0</v>
+      </c>
+      <c r="F74" s="117" t="s">
+        <v>86</v>
+      </c>
+      <c r="G74" s="117"/>
+      <c r="H74" s="117"/>
+    </row>
+    <row r="75" spans="1:8" ht="27.95" customHeight="1">
+      <c r="A75" s="117" t="s">
+        <v>224</v>
+      </c>
+      <c r="B75" s="117" t="s">
+        <v>25</v>
+      </c>
+      <c r="C75" s="117" t="s">
+        <v>133</v>
+      </c>
+      <c r="D75" s="118">
+        <v>93</v>
+      </c>
+      <c r="E75" s="118">
+        <f>'93'!N25</f>
+        <v>0</v>
+      </c>
+      <c r="F75" s="117" t="s">
+        <v>86</v>
+      </c>
+      <c r="G75" s="117"/>
+      <c r="H75" s="117"/>
+    </row>
+    <row r="76" spans="1:8" ht="27.95" customHeight="1">
+      <c r="A76" s="117" t="s">
+        <v>225</v>
+      </c>
+      <c r="B76" s="117" t="s">
+        <v>25</v>
+      </c>
+      <c r="C76" s="117" t="s">
+        <v>133</v>
+      </c>
+      <c r="D76" s="118">
+        <v>93</v>
+      </c>
+      <c r="E76" s="118">
+        <f>'93'!N26</f>
+        <v>0</v>
+      </c>
+      <c r="F76" s="117" t="s">
+        <v>86</v>
+      </c>
+      <c r="G76" s="117"/>
+      <c r="H76" s="117"/>
+    </row>
+    <row r="77" spans="1:8" ht="27.95" customHeight="1">
+      <c r="A77" s="117" t="s">
+        <v>226</v>
+      </c>
+      <c r="B77" s="117" t="s">
+        <v>25</v>
+      </c>
+      <c r="C77" s="117" t="s">
+        <v>133</v>
+      </c>
+      <c r="D77" s="118">
+        <v>93</v>
+      </c>
+      <c r="E77" s="118">
+        <f>'93'!N27</f>
+        <v>0</v>
+      </c>
+      <c r="F77" s="117" t="s">
+        <v>86</v>
+      </c>
+      <c r="G77" s="117"/>
+      <c r="H77" s="117"/>
+    </row>
+    <row r="78" spans="1:8" ht="27.95" customHeight="1">
+      <c r="A78" s="117" t="s">
+        <v>227</v>
+      </c>
+      <c r="B78" s="117" t="s">
+        <v>25</v>
+      </c>
+      <c r="C78" s="117" t="s">
+        <v>133</v>
+      </c>
+      <c r="D78" s="118">
+        <v>93</v>
+      </c>
+      <c r="E78" s="118">
+        <f>'93'!N28</f>
+        <v>0</v>
+      </c>
+      <c r="F78" s="117" t="s">
+        <v>86</v>
+      </c>
+      <c r="G78" s="117"/>
+      <c r="H78" s="117"/>
+    </row>
+    <row r="79" spans="1:8" ht="27.95" customHeight="1">
+      <c r="A79" s="117" t="s">
+        <v>228</v>
+      </c>
+      <c r="B79" s="117" t="s">
+        <v>25</v>
+      </c>
+      <c r="C79" s="117" t="s">
+        <v>133</v>
+      </c>
+      <c r="D79" s="118">
+        <v>93</v>
+      </c>
+      <c r="E79" s="118">
+        <f>'93'!N29</f>
+        <v>0</v>
+      </c>
+      <c r="F79" s="117" t="s">
+        <v>86</v>
+      </c>
+      <c r="G79" s="117"/>
+      <c r="H79" s="117"/>
+    </row>
+    <row r="80" spans="1:8" ht="27.95" customHeight="1">
+      <c r="A80" s="117" t="s">
+        <v>229</v>
+      </c>
+      <c r="B80" s="117" t="s">
+        <v>25</v>
+      </c>
+      <c r="C80" s="117" t="s">
+        <v>133</v>
+      </c>
+      <c r="D80" s="118">
+        <v>93</v>
+      </c>
+      <c r="E80" s="118">
+        <f>'93'!N30</f>
+        <v>0</v>
+      </c>
+      <c r="F80" s="117" t="s">
+        <v>86</v>
+      </c>
+      <c r="G80" s="117"/>
+      <c r="H80" s="117"/>
+    </row>
+    <row r="81" spans="1:8" ht="27.95" customHeight="1">
+      <c r="A81" s="117" t="s">
+        <v>230</v>
+      </c>
+      <c r="B81" s="117" t="s">
+        <v>25</v>
+      </c>
+      <c r="C81" s="117" t="s">
+        <v>133</v>
+      </c>
+      <c r="D81" s="118">
+        <v>93</v>
+      </c>
+      <c r="E81" s="118">
+        <f>'93'!Q19</f>
+        <v>0</v>
+      </c>
+      <c r="F81" s="117" t="s">
+        <v>86</v>
+      </c>
+      <c r="G81" s="117"/>
+      <c r="H81" s="117" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="82" spans="1:8" ht="27.95" customHeight="1">
+      <c r="A82" s="117" t="s">
+        <v>231</v>
+      </c>
+      <c r="B82" s="117" t="s">
+        <v>25</v>
+      </c>
+      <c r="C82" s="117" t="s">
+        <v>133</v>
+      </c>
+      <c r="D82" s="118">
+        <v>93</v>
+      </c>
+      <c r="E82" s="118">
+        <f>'93'!Q20</f>
+        <v>0</v>
+      </c>
+      <c r="F82" s="117" t="s">
+        <v>86</v>
+      </c>
+      <c r="G82" s="117"/>
+      <c r="H82" s="117"/>
+    </row>
+    <row r="83" spans="1:8" ht="27.95" customHeight="1">
+      <c r="A83" s="117" t="s">
+        <v>232</v>
+      </c>
+      <c r="B83" s="117" t="s">
+        <v>25</v>
+      </c>
+      <c r="C83" s="117" t="s">
+        <v>133</v>
+      </c>
+      <c r="D83" s="118">
+        <v>93</v>
+      </c>
+      <c r="E83" s="118">
+        <f>'93'!Q21</f>
+        <v>0</v>
+      </c>
+      <c r="F83" s="117" t="s">
+        <v>86</v>
+      </c>
+      <c r="G83" s="117"/>
+      <c r="H83" s="117"/>
+    </row>
+    <row r="84" spans="1:8" ht="27.95" customHeight="1">
+      <c r="A84" s="117" t="s">
+        <v>233</v>
+      </c>
+      <c r="B84" s="117" t="s">
+        <v>25</v>
+      </c>
+      <c r="C84" s="117" t="s">
+        <v>133</v>
+      </c>
+      <c r="D84" s="118">
+        <v>93</v>
+      </c>
+      <c r="E84" s="118">
+        <f>'93'!Q22</f>
+        <v>0</v>
+      </c>
+      <c r="F84" s="117" t="s">
+        <v>86</v>
+      </c>
+      <c r="G84" s="117"/>
+      <c r="H84" s="117"/>
+    </row>
+    <row r="85" spans="1:8" ht="27.95" customHeight="1">
+      <c r="A85" s="117" t="s">
+        <v>234</v>
+      </c>
+      <c r="B85" s="117" t="s">
+        <v>25</v>
+      </c>
+      <c r="C85" s="117" t="s">
+        <v>133</v>
+      </c>
+      <c r="D85" s="118">
+        <v>93</v>
+      </c>
+      <c r="E85" s="118">
+        <f>'93'!Q23</f>
+        <v>0</v>
+      </c>
+      <c r="F85" s="117" t="s">
+        <v>86</v>
+      </c>
+      <c r="G85" s="117"/>
+      <c r="H85" s="117"/>
+    </row>
+    <row r="86" spans="1:8" ht="27.95" customHeight="1">
+      <c r="A86" s="117" t="s">
+        <v>235</v>
+      </c>
+      <c r="B86" s="117" t="s">
+        <v>25</v>
+      </c>
+      <c r="C86" s="117" t="s">
+        <v>133</v>
+      </c>
+      <c r="D86" s="118">
+        <v>93</v>
+      </c>
+      <c r="E86" s="118">
+        <f>'93'!Q24</f>
+        <v>0</v>
+      </c>
+      <c r="F86" s="117" t="s">
+        <v>86</v>
+      </c>
+      <c r="G86" s="117"/>
+      <c r="H86" s="117"/>
+    </row>
+    <row r="87" spans="1:8" ht="27.95" customHeight="1">
+      <c r="A87" s="117" t="s">
+        <v>236</v>
+      </c>
+      <c r="B87" s="117" t="s">
+        <v>25</v>
+      </c>
+      <c r="C87" s="117" t="s">
+        <v>133</v>
+      </c>
+      <c r="D87" s="118">
+        <v>93</v>
+      </c>
+      <c r="E87" s="118">
+        <f>'93'!Q25</f>
+        <v>0</v>
+      </c>
+      <c r="F87" s="117" t="s">
+        <v>86</v>
+      </c>
+      <c r="G87" s="117"/>
+      <c r="H87" s="117"/>
+    </row>
+    <row r="88" spans="1:8" ht="27.95" customHeight="1">
+      <c r="A88" s="117" t="s">
+        <v>237</v>
+      </c>
+      <c r="B88" s="117" t="s">
+        <v>25</v>
+      </c>
+      <c r="C88" s="117" t="s">
+        <v>133</v>
+      </c>
+      <c r="D88" s="118">
+        <v>93</v>
+      </c>
+      <c r="E88" s="118">
+        <f>'93'!Q26</f>
+        <v>0</v>
+      </c>
+      <c r="F88" s="117" t="s">
+        <v>86</v>
+      </c>
+      <c r="G88" s="117"/>
+      <c r="H88" s="117"/>
+    </row>
+    <row r="89" spans="1:8" ht="27.95" customHeight="1">
+      <c r="A89" s="117" t="s">
+        <v>238</v>
+      </c>
+      <c r="B89" s="117" t="s">
+        <v>25</v>
+      </c>
+      <c r="C89" s="117" t="s">
+        <v>133</v>
+      </c>
+      <c r="D89" s="118">
+        <v>93</v>
+      </c>
+      <c r="E89" s="118">
+        <f>'93'!Q27</f>
+        <v>0</v>
+      </c>
+      <c r="F89" s="117" t="s">
+        <v>86</v>
+      </c>
+      <c r="G89" s="117"/>
+      <c r="H89" s="117"/>
+    </row>
+    <row r="90" spans="1:8" ht="27.95" customHeight="1">
+      <c r="A90" s="117" t="s">
+        <v>239</v>
+      </c>
+      <c r="B90" s="117" t="s">
+        <v>25</v>
+      </c>
+      <c r="C90" s="117" t="s">
+        <v>133</v>
+      </c>
+      <c r="D90" s="118">
+        <v>93</v>
+      </c>
+      <c r="E90" s="118">
+        <f>'93'!Q28</f>
+        <v>0</v>
+      </c>
+      <c r="F90" s="117" t="s">
+        <v>86</v>
+      </c>
+      <c r="G90" s="117"/>
+      <c r="H90" s="117"/>
+    </row>
+    <row r="91" spans="1:8" ht="27.95" customHeight="1">
+      <c r="A91" s="117" t="s">
+        <v>240</v>
+      </c>
+      <c r="B91" s="117" t="s">
+        <v>25</v>
+      </c>
+      <c r="C91" s="117" t="s">
+        <v>133</v>
+      </c>
+      <c r="D91" s="118">
+        <v>93</v>
+      </c>
+      <c r="E91" s="118">
+        <f>'93'!Q29</f>
+        <v>0</v>
+      </c>
+      <c r="F91" s="117" t="s">
+        <v>86</v>
+      </c>
+      <c r="G91" s="117"/>
+      <c r="H91" s="117"/>
+    </row>
+    <row r="92" spans="1:8" ht="27.95" customHeight="1">
+      <c r="A92" s="117" t="s">
+        <v>241</v>
+      </c>
+      <c r="B92" s="117" t="s">
+        <v>25</v>
+      </c>
+      <c r="C92" s="117" t="s">
+        <v>133</v>
+      </c>
+      <c r="D92" s="118">
+        <v>93</v>
+      </c>
+      <c r="E92" s="118">
+        <f>'93'!Q30</f>
+        <v>0</v>
+      </c>
+      <c r="F92" s="117" t="s">
+        <v>86</v>
+      </c>
+      <c r="G92" s="117"/>
+      <c r="H92" s="117"/>
+    </row>
+    <row r="93" spans="1:8" ht="27.95" customHeight="1">
+      <c r="A93" s="117" t="s">
+        <v>242</v>
+      </c>
+      <c r="B93" s="117" t="s">
+        <v>25</v>
+      </c>
+      <c r="C93" s="117" t="s">
+        <v>131</v>
+      </c>
+      <c r="D93" s="118">
+        <v>93</v>
+      </c>
+      <c r="E93" s="118">
         <f>'93'!O19</f>
         <v>0</v>
       </c>
-      <c r="F21" s="118" t="s">
-        <v>87</v>
-      </c>
-      <c r="G21" s="118" t="s">
-        <v>80</v>
-      </c>
-      <c r="H21" s="118"/>
+      <c r="F93" s="117" t="s">
+        <v>86</v>
+      </c>
+      <c r="G93" s="117"/>
+      <c r="H93" s="117" t="s">
+        <v>182</v>
+      </c>
     </row>
-    <row r="22" spans="1:8" ht="27.95" customHeight="1">
-      <c r="A22" s="118" t="s">
-        <v>133</v>
-      </c>
-      <c r="B22" s="118" t="s">
+    <row r="94" spans="1:8" ht="27.95" customHeight="1">
+      <c r="A94" s="117" t="s">
+        <v>243</v>
+      </c>
+      <c r="B94" s="117" t="s">
+        <v>25</v>
+      </c>
+      <c r="C94" s="117" t="s">
+        <v>131</v>
+      </c>
+      <c r="D94" s="118">
+        <v>93</v>
+      </c>
+      <c r="E94" s="118">
+        <f>'93'!O20</f>
+        <v>0</v>
+      </c>
+      <c r="F94" s="117" t="s">
+        <v>86</v>
+      </c>
+      <c r="G94" s="117"/>
+      <c r="H94" s="117"/>
+    </row>
+    <row r="95" spans="1:8" ht="27.95" customHeight="1">
+      <c r="A95" s="117" t="s">
+        <v>244</v>
+      </c>
+      <c r="B95" s="117" t="s">
+        <v>25</v>
+      </c>
+      <c r="C95" s="117" t="s">
+        <v>131</v>
+      </c>
+      <c r="D95" s="118">
+        <v>93</v>
+      </c>
+      <c r="E95" s="118">
+        <f>'93'!O21</f>
+        <v>0</v>
+      </c>
+      <c r="F95" s="117" t="s">
+        <v>86</v>
+      </c>
+      <c r="G95" s="117"/>
+      <c r="H95" s="117"/>
+    </row>
+    <row r="96" spans="1:8" ht="27.95" customHeight="1">
+      <c r="A96" s="117" t="s">
+        <v>245</v>
+      </c>
+      <c r="B96" s="117" t="s">
+        <v>25</v>
+      </c>
+      <c r="C96" s="117" t="s">
+        <v>131</v>
+      </c>
+      <c r="D96" s="118">
+        <v>93</v>
+      </c>
+      <c r="E96" s="118">
+        <f>'93'!O22</f>
+        <v>0</v>
+      </c>
+      <c r="F96" s="117" t="s">
+        <v>86</v>
+      </c>
+      <c r="G96" s="117"/>
+      <c r="H96" s="117"/>
+    </row>
+    <row r="97" spans="1:8" ht="27.95" customHeight="1">
+      <c r="A97" s="117" t="s">
+        <v>246</v>
+      </c>
+      <c r="B97" s="117" t="s">
+        <v>25</v>
+      </c>
+      <c r="C97" s="117" t="s">
+        <v>131</v>
+      </c>
+      <c r="D97" s="118">
+        <v>93</v>
+      </c>
+      <c r="E97" s="118">
+        <f>'93'!O23</f>
+        <v>0</v>
+      </c>
+      <c r="F97" s="117" t="s">
+        <v>86</v>
+      </c>
+      <c r="G97" s="117"/>
+      <c r="H97" s="117"/>
+    </row>
+    <row r="98" spans="1:8" ht="27.95" customHeight="1">
+      <c r="A98" s="117" t="s">
+        <v>247</v>
+      </c>
+      <c r="B98" s="117" t="s">
+        <v>25</v>
+      </c>
+      <c r="C98" s="117" t="s">
+        <v>131</v>
+      </c>
+      <c r="D98" s="118">
+        <v>93</v>
+      </c>
+      <c r="E98" s="118">
+        <f>'93'!O24</f>
+        <v>0</v>
+      </c>
+      <c r="F98" s="117" t="s">
+        <v>86</v>
+      </c>
+      <c r="G98" s="117"/>
+      <c r="H98" s="117"/>
+    </row>
+    <row r="99" spans="1:8" ht="27.95" customHeight="1">
+      <c r="A99" s="117" t="s">
+        <v>248</v>
+      </c>
+      <c r="B99" s="117" t="s">
+        <v>25</v>
+      </c>
+      <c r="C99" s="117" t="s">
+        <v>131</v>
+      </c>
+      <c r="D99" s="118">
+        <v>93</v>
+      </c>
+      <c r="E99" s="118">
+        <f>'93'!O25</f>
+        <v>0</v>
+      </c>
+      <c r="F99" s="117" t="s">
+        <v>86</v>
+      </c>
+      <c r="G99" s="117"/>
+      <c r="H99" s="117"/>
+    </row>
+    <row r="100" spans="1:8" ht="27.95" customHeight="1">
+      <c r="A100" s="117" t="s">
+        <v>249</v>
+      </c>
+      <c r="B100" s="117" t="s">
+        <v>25</v>
+      </c>
+      <c r="C100" s="117" t="s">
+        <v>131</v>
+      </c>
+      <c r="D100" s="118">
+        <v>93</v>
+      </c>
+      <c r="E100" s="118">
+        <f>'93'!O26</f>
+        <v>0</v>
+      </c>
+      <c r="F100" s="117" t="s">
+        <v>86</v>
+      </c>
+      <c r="G100" s="117"/>
+      <c r="H100" s="117"/>
+    </row>
+    <row r="101" spans="1:8" ht="27.95" customHeight="1">
+      <c r="A101" s="117" t="s">
+        <v>250</v>
+      </c>
+      <c r="B101" s="117" t="s">
+        <v>25</v>
+      </c>
+      <c r="C101" s="117" t="s">
+        <v>131</v>
+      </c>
+      <c r="D101" s="118">
+        <v>93</v>
+      </c>
+      <c r="E101" s="118">
+        <f>'93'!O27</f>
+        <v>0</v>
+      </c>
+      <c r="F101" s="117" t="s">
+        <v>86</v>
+      </c>
+      <c r="G101" s="117"/>
+      <c r="H101" s="117"/>
+    </row>
+    <row r="102" spans="1:8" ht="27.95" customHeight="1">
+      <c r="A102" s="117" t="s">
+        <v>251</v>
+      </c>
+      <c r="B102" s="117" t="s">
+        <v>25</v>
+      </c>
+      <c r="C102" s="117" t="s">
+        <v>131</v>
+      </c>
+      <c r="D102" s="118">
+        <v>93</v>
+      </c>
+      <c r="E102" s="118">
+        <f>'93'!O28</f>
+        <v>0</v>
+      </c>
+      <c r="F102" s="117" t="s">
+        <v>86</v>
+      </c>
+      <c r="G102" s="117"/>
+      <c r="H102" s="117"/>
+    </row>
+    <row r="103" spans="1:8" ht="27.95" customHeight="1">
+      <c r="A103" s="117" t="s">
+        <v>252</v>
+      </c>
+      <c r="B103" s="117" t="s">
+        <v>25</v>
+      </c>
+      <c r="C103" s="117" t="s">
+        <v>131</v>
+      </c>
+      <c r="D103" s="118">
+        <v>93</v>
+      </c>
+      <c r="E103" s="118">
+        <f>'93'!O29</f>
+        <v>0</v>
+      </c>
+      <c r="F103" s="117" t="s">
+        <v>86</v>
+      </c>
+      <c r="G103" s="117"/>
+      <c r="H103" s="117"/>
+    </row>
+    <row r="104" spans="1:8" ht="27.95" customHeight="1">
+      <c r="A104" s="117" t="s">
+        <v>253</v>
+      </c>
+      <c r="B104" s="117" t="s">
+        <v>25</v>
+      </c>
+      <c r="C104" s="117" t="s">
+        <v>131</v>
+      </c>
+      <c r="D104" s="118">
+        <v>93</v>
+      </c>
+      <c r="E104" s="118">
+        <f>'93'!O30</f>
+        <v>0</v>
+      </c>
+      <c r="F104" s="117" t="s">
+        <v>86</v>
+      </c>
+      <c r="G104" s="117"/>
+      <c r="H104" s="117"/>
+    </row>
+    <row r="105" spans="1:8" ht="27.95" customHeight="1">
+      <c r="A105" s="117" t="s">
+        <v>254</v>
+      </c>
+      <c r="B105" s="117" t="s">
+        <v>25</v>
+      </c>
+      <c r="C105" s="117" t="s">
+        <v>131</v>
+      </c>
+      <c r="D105" s="118">
+        <v>93</v>
+      </c>
+      <c r="E105" s="118">
+        <f>'93'!R19</f>
+        <v>0</v>
+      </c>
+      <c r="F105" s="117" t="s">
+        <v>86</v>
+      </c>
+      <c r="G105" s="117"/>
+      <c r="H105" s="117" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="106" spans="1:8" ht="27.95" customHeight="1">
+      <c r="A106" s="117" t="s">
+        <v>255</v>
+      </c>
+      <c r="B106" s="117" t="s">
+        <v>25</v>
+      </c>
+      <c r="C106" s="117" t="s">
+        <v>131</v>
+      </c>
+      <c r="D106" s="118">
+        <v>93</v>
+      </c>
+      <c r="E106" s="118">
+        <f>'93'!R20</f>
+        <v>0</v>
+      </c>
+      <c r="F106" s="117" t="s">
+        <v>86</v>
+      </c>
+      <c r="G106" s="117"/>
+      <c r="H106" s="117"/>
+    </row>
+    <row r="107" spans="1:8" ht="27.95" customHeight="1">
+      <c r="A107" s="117" t="s">
+        <v>256</v>
+      </c>
+      <c r="B107" s="117" t="s">
+        <v>25</v>
+      </c>
+      <c r="C107" s="117" t="s">
+        <v>131</v>
+      </c>
+      <c r="D107" s="118">
+        <v>93</v>
+      </c>
+      <c r="E107" s="118">
+        <f>'93'!R21</f>
+        <v>0</v>
+      </c>
+      <c r="F107" s="117" t="s">
+        <v>86</v>
+      </c>
+      <c r="G107" s="117"/>
+      <c r="H107" s="117"/>
+    </row>
+    <row r="108" spans="1:8" ht="27.95" customHeight="1">
+      <c r="A108" s="117" t="s">
+        <v>257</v>
+      </c>
+      <c r="B108" s="117" t="s">
+        <v>25</v>
+      </c>
+      <c r="C108" s="117" t="s">
+        <v>131</v>
+      </c>
+      <c r="D108" s="118">
+        <v>93</v>
+      </c>
+      <c r="E108" s="118">
+        <f>'93'!R22</f>
+        <v>0</v>
+      </c>
+      <c r="F108" s="117" t="s">
+        <v>86</v>
+      </c>
+      <c r="G108" s="117"/>
+      <c r="H108" s="117"/>
+    </row>
+    <row r="109" spans="1:8" ht="27.95" customHeight="1">
+      <c r="A109" s="117" t="s">
+        <v>258</v>
+      </c>
+      <c r="B109" s="117" t="s">
+        <v>25</v>
+      </c>
+      <c r="C109" s="117" t="s">
+        <v>131</v>
+      </c>
+      <c r="D109" s="118">
+        <v>93</v>
+      </c>
+      <c r="E109" s="118">
+        <f>'93'!R23</f>
+        <v>0</v>
+      </c>
+      <c r="F109" s="117" t="s">
+        <v>86</v>
+      </c>
+      <c r="G109" s="117"/>
+      <c r="H109" s="117"/>
+    </row>
+    <row r="110" spans="1:8" ht="27.95" customHeight="1">
+      <c r="A110" s="117" t="s">
+        <v>259</v>
+      </c>
+      <c r="B110" s="117" t="s">
+        <v>25</v>
+      </c>
+      <c r="C110" s="117" t="s">
+        <v>131</v>
+      </c>
+      <c r="D110" s="118">
+        <v>93</v>
+      </c>
+      <c r="E110" s="118">
+        <f>'93'!R24</f>
+        <v>0</v>
+      </c>
+      <c r="F110" s="117" t="s">
+        <v>86</v>
+      </c>
+      <c r="G110" s="117"/>
+      <c r="H110" s="117"/>
+    </row>
+    <row r="111" spans="1:8" ht="27.95" customHeight="1">
+      <c r="A111" s="117" t="s">
+        <v>260</v>
+      </c>
+      <c r="B111" s="117" t="s">
+        <v>25</v>
+      </c>
+      <c r="C111" s="117" t="s">
+        <v>131</v>
+      </c>
+      <c r="D111" s="118">
+        <v>93</v>
+      </c>
+      <c r="E111" s="118">
+        <f>'93'!R25</f>
+        <v>0</v>
+      </c>
+      <c r="F111" s="117" t="s">
+        <v>86</v>
+      </c>
+      <c r="G111" s="117"/>
+      <c r="H111" s="117"/>
+    </row>
+    <row r="112" spans="1:8" ht="27.95" customHeight="1">
+      <c r="A112" s="117" t="s">
+        <v>261</v>
+      </c>
+      <c r="B112" s="117" t="s">
+        <v>25</v>
+      </c>
+      <c r="C112" s="117" t="s">
+        <v>131</v>
+      </c>
+      <c r="D112" s="118">
+        <v>93</v>
+      </c>
+      <c r="E112" s="118">
+        <f>'93'!R26</f>
+        <v>0</v>
+      </c>
+      <c r="F112" s="117" t="s">
+        <v>86</v>
+      </c>
+      <c r="G112" s="117"/>
+      <c r="H112" s="117"/>
+    </row>
+    <row r="113" spans="1:8" ht="27.95" customHeight="1">
+      <c r="A113" s="117" t="s">
+        <v>262</v>
+      </c>
+      <c r="B113" s="117" t="s">
+        <v>25</v>
+      </c>
+      <c r="C113" s="117" t="s">
+        <v>131</v>
+      </c>
+      <c r="D113" s="118">
+        <v>93</v>
+      </c>
+      <c r="E113" s="118">
+        <f>'93'!R27</f>
+        <v>0</v>
+      </c>
+      <c r="F113" s="117" t="s">
+        <v>86</v>
+      </c>
+      <c r="G113" s="117"/>
+      <c r="H113" s="117"/>
+    </row>
+    <row r="114" spans="1:8" ht="27.95" customHeight="1">
+      <c r="A114" s="117" t="s">
+        <v>263</v>
+      </c>
+      <c r="B114" s="117" t="s">
+        <v>25</v>
+      </c>
+      <c r="C114" s="117" t="s">
+        <v>131</v>
+      </c>
+      <c r="D114" s="118">
+        <v>93</v>
+      </c>
+      <c r="E114" s="118">
+        <f>'93'!R28</f>
+        <v>0</v>
+      </c>
+      <c r="F114" s="117" t="s">
+        <v>86</v>
+      </c>
+      <c r="G114" s="117"/>
+      <c r="H114" s="117"/>
+    </row>
+    <row r="115" spans="1:8" ht="27.95" customHeight="1">
+      <c r="A115" s="117" t="s">
+        <v>264</v>
+      </c>
+      <c r="B115" s="117" t="s">
+        <v>25</v>
+      </c>
+      <c r="C115" s="117" t="s">
+        <v>131</v>
+      </c>
+      <c r="D115" s="118">
+        <v>93</v>
+      </c>
+      <c r="E115" s="118">
+        <f>'93'!R29</f>
+        <v>0</v>
+      </c>
+      <c r="F115" s="117" t="s">
+        <v>86</v>
+      </c>
+      <c r="G115" s="117"/>
+      <c r="H115" s="117"/>
+    </row>
+    <row r="116" spans="1:8" ht="27.95" customHeight="1">
+      <c r="A116" s="117" t="s">
+        <v>265</v>
+      </c>
+      <c r="B116" s="117" t="s">
+        <v>25</v>
+      </c>
+      <c r="C116" s="117" t="s">
+        <v>131</v>
+      </c>
+      <c r="D116" s="118">
+        <v>93</v>
+      </c>
+      <c r="E116" s="118">
+        <f>'93'!R30</f>
+        <v>0</v>
+      </c>
+      <c r="F116" s="117" t="s">
+        <v>86</v>
+      </c>
+      <c r="G116" s="117"/>
+      <c r="H116" s="117"/>
+    </row>
+    <row r="117" spans="1:8" ht="27.95" customHeight="1">
+      <c r="A117" s="117" t="s">
+        <v>266</v>
+      </c>
+      <c r="B117" s="117" t="s">
         <v>31</v>
       </c>
-      <c r="C22" s="118" t="s">
-        <v>132</v>
-      </c>
-      <c r="D22" s="119">
+      <c r="C117" s="117" t="s">
+        <v>129</v>
+      </c>
+      <c r="D117" s="118">
         <v>93</v>
       </c>
-      <c r="E22" s="119">
+      <c r="E117" s="118">
         <f>'93'!M36</f>
         <v>0</v>
       </c>
-      <c r="F22" s="118" t="s">
-        <v>131</v>
-      </c>
-      <c r="G22" s="118"/>
-      <c r="H22" s="118"/>
+      <c r="F117" s="117" t="s">
+        <v>128</v>
+      </c>
+      <c r="G117" s="117"/>
+      <c r="H117" s="117"/>
     </row>
-    <row r="23" spans="1:8" ht="27.95" customHeight="1">
-      <c r="A23" s="118" t="s">
-        <v>130</v>
-      </c>
-      <c r="B23" s="118" t="s">
+    <row r="118" spans="1:8" ht="27.95" customHeight="1">
+      <c r="A118" s="117" t="s">
+        <v>267</v>
+      </c>
+      <c r="B118" s="117" t="s">
         <v>31</v>
       </c>
-      <c r="C23" s="118" t="s">
-        <v>129</v>
-      </c>
-      <c r="D23" s="119">
+      <c r="C118" s="117" t="s">
+        <v>126</v>
+      </c>
+      <c r="D118" s="118">
         <v>93</v>
       </c>
-      <c r="E23" s="119">
+      <c r="E118" s="118">
         <f>'93'!N37</f>
         <v>0</v>
       </c>
-      <c r="F23" s="118" t="s">
+      <c r="F118" s="117" t="s">
         <v>81</v>
       </c>
-      <c r="G23" s="118" t="s">
-        <v>126</v>
-      </c>
-      <c r="H23" s="118"/>
+      <c r="G118" s="117" t="s">
+        <v>123</v>
+      </c>
+      <c r="H118" s="117"/>
     </row>
-    <row r="24" spans="1:8" ht="27.95" customHeight="1">
-      <c r="A24" s="118" t="s">
-        <v>128</v>
-      </c>
-      <c r="B24" s="118" t="s">
+    <row r="119" spans="1:8" ht="27.95" customHeight="1">
+      <c r="A119" s="117" t="s">
+        <v>268</v>
+      </c>
+      <c r="B119" s="117" t="s">
         <v>31</v>
       </c>
-      <c r="C24" s="118" t="s">
-        <v>127</v>
-      </c>
-      <c r="D24" s="119">
+      <c r="C119" s="117" t="s">
+        <v>124</v>
+      </c>
+      <c r="D119" s="118">
         <v>93</v>
       </c>
-      <c r="E24" s="119">
+      <c r="E119" s="118">
         <f>'93'!R37</f>
         <v>0</v>
       </c>
-      <c r="F24" s="118" t="s">
-        <v>87</v>
-      </c>
-      <c r="G24" s="118" t="s">
-        <v>126</v>
-      </c>
-      <c r="H24" s="118" t="s">
-        <v>125</v>
+      <c r="F119" s="117" t="s">
+        <v>86</v>
+      </c>
+      <c r="G119" s="117" t="s">
+        <v>123</v>
+      </c>
+      <c r="H119" s="117" t="s">
+        <v>122</v>
       </c>
     </row>
-    <row r="25" spans="1:8" ht="27.95" customHeight="1">
-      <c r="A25" s="118" t="s">
-        <v>124</v>
-      </c>
-      <c r="B25" s="118" t="s">
-        <v>123</v>
-      </c>
-      <c r="C25" s="118" t="s">
-        <v>122</v>
-      </c>
-      <c r="D25" s="119">
+    <row r="120" spans="1:8" ht="27.95" customHeight="1">
+      <c r="A120" s="117" t="s">
+        <v>269</v>
+      </c>
+      <c r="B120" s="117" t="s">
+        <v>29</v>
+      </c>
+      <c r="C120" s="117" t="s">
+        <v>184</v>
+      </c>
+      <c r="D120" s="118">
         <v>93</v>
       </c>
-      <c r="E25" s="119">
-        <f>'93'!M32</f>
-        <v>1</v>
-      </c>
-      <c r="F25" s="118" t="s">
+      <c r="E120" s="118">
+        <f>'93'!N32</f>
+        <v>0</v>
+      </c>
+      <c r="F120" s="117" t="s">
         <v>81</v>
       </c>
-      <c r="G25" s="118" t="s">
+      <c r="G120" s="117" t="s">
         <v>80</v>
       </c>
-      <c r="H25" s="118"/>
+      <c r="H120" s="117"/>
     </row>
-    <row r="26" spans="1:8" ht="27.95" customHeight="1">
-      <c r="A26" s="118" t="s">
-        <v>121</v>
-      </c>
-      <c r="B26" s="118" t="s">
-        <v>118</v>
-      </c>
-      <c r="C26" s="118" t="s">
-        <v>120</v>
-      </c>
-      <c r="D26" s="119">
+    <row r="121" spans="1:8" ht="27.95" customHeight="1">
+      <c r="A121" s="117" t="s">
+        <v>270</v>
+      </c>
+      <c r="B121" s="117" t="s">
+        <v>29</v>
+      </c>
+      <c r="C121" s="117" t="s">
+        <v>184</v>
+      </c>
+      <c r="D121" s="118">
         <v>93</v>
       </c>
-      <c r="E26" s="119">
+      <c r="E121" s="118">
+        <f>'93'!N33</f>
+        <v>0</v>
+      </c>
+      <c r="F121" s="117" t="s">
+        <v>81</v>
+      </c>
+      <c r="G121" s="117"/>
+      <c r="H121" s="117"/>
+    </row>
+    <row r="122" spans="1:8" ht="27.95" customHeight="1">
+      <c r="A122" s="117" t="s">
+        <v>271</v>
+      </c>
+      <c r="B122" s="117" t="s">
+        <v>29</v>
+      </c>
+      <c r="C122" s="117" t="s">
+        <v>184</v>
+      </c>
+      <c r="D122" s="118">
+        <v>93</v>
+      </c>
+      <c r="E122" s="118">
+        <f>'93'!N34</f>
+        <v>0</v>
+      </c>
+      <c r="F122" s="117" t="s">
+        <v>81</v>
+      </c>
+      <c r="G122" s="117"/>
+      <c r="H122" s="117"/>
+    </row>
+    <row r="123" spans="1:8" ht="27.95" customHeight="1">
+      <c r="A123" s="117" t="s">
+        <v>272</v>
+      </c>
+      <c r="B123" s="117" t="s">
+        <v>29</v>
+      </c>
+      <c r="C123" s="117" t="s">
+        <v>184</v>
+      </c>
+      <c r="D123" s="118">
+        <v>93</v>
+      </c>
+      <c r="E123" s="118">
+        <f>'93'!Q32</f>
+        <v>0</v>
+      </c>
+      <c r="F123" s="117" t="s">
+        <v>81</v>
+      </c>
+      <c r="G123" s="117"/>
+      <c r="H123" s="117"/>
+    </row>
+    <row r="124" spans="1:8" ht="27.95" customHeight="1">
+      <c r="A124" s="117" t="s">
+        <v>273</v>
+      </c>
+      <c r="B124" s="117" t="s">
+        <v>29</v>
+      </c>
+      <c r="C124" s="117" t="s">
+        <v>184</v>
+      </c>
+      <c r="D124" s="118">
+        <v>93</v>
+      </c>
+      <c r="E124" s="118">
+        <f>'93'!Q33</f>
+        <v>0</v>
+      </c>
+      <c r="F124" s="117" t="s">
+        <v>81</v>
+      </c>
+      <c r="G124" s="117"/>
+      <c r="H124" s="117"/>
+    </row>
+    <row r="125" spans="1:8" ht="27.95" customHeight="1">
+      <c r="A125" s="117" t="s">
+        <v>274</v>
+      </c>
+      <c r="B125" s="117" t="s">
+        <v>29</v>
+      </c>
+      <c r="C125" s="117" t="s">
+        <v>184</v>
+      </c>
+      <c r="D125" s="118">
+        <v>93</v>
+      </c>
+      <c r="E125" s="118">
+        <f>'93'!Q34</f>
+        <v>0</v>
+      </c>
+      <c r="F125" s="117" t="s">
+        <v>81</v>
+      </c>
+      <c r="G125" s="117"/>
+      <c r="H125" s="117"/>
+    </row>
+    <row r="126" spans="1:8" ht="27.95" customHeight="1">
+      <c r="A126" s="117" t="s">
+        <v>275</v>
+      </c>
+      <c r="B126" s="117" t="s">
+        <v>117</v>
+      </c>
+      <c r="C126" s="117" t="s">
+        <v>119</v>
+      </c>
+      <c r="D126" s="118">
+        <v>93</v>
+      </c>
+      <c r="E126" s="118">
         <f>'93'!M49</f>
         <v>0</v>
       </c>
-      <c r="F26" s="118" t="s">
+      <c r="F126" s="117" t="s">
         <v>81</v>
       </c>
-      <c r="G26" s="118" t="s">
+      <c r="G126" s="117" t="s">
         <v>80</v>
       </c>
-      <c r="H26" s="118"/>
+      <c r="H126" s="117" t="s">
+        <v>182</v>
+      </c>
     </row>
-    <row r="27" spans="1:8" ht="27.95" customHeight="1">
-      <c r="A27" s="118" t="s">
+    <row r="127" spans="1:8" ht="27.95" customHeight="1">
+      <c r="A127" s="117" t="s">
+        <v>276</v>
+      </c>
+      <c r="B127" s="117" t="s">
+        <v>117</v>
+      </c>
+      <c r="C127" s="117" t="s">
         <v>119</v>
       </c>
-      <c r="B27" s="118" t="s">
-        <v>118</v>
-      </c>
-      <c r="C27" s="118" t="s">
+      <c r="D127" s="118">
+        <v>93</v>
+      </c>
+      <c r="E127" s="118">
+        <f>'93'!M50</f>
+        <v>0</v>
+      </c>
+      <c r="F127" s="117" t="s">
+        <v>81</v>
+      </c>
+      <c r="G127" s="117"/>
+      <c r="H127" s="117"/>
+    </row>
+    <row r="128" spans="1:8" ht="27.95" customHeight="1">
+      <c r="A128" s="117" t="s">
+        <v>277</v>
+      </c>
+      <c r="B128" s="117" t="s">
         <v>117</v>
       </c>
-      <c r="D27" s="119">
+      <c r="C128" s="117" t="s">
+        <v>119</v>
+      </c>
+      <c r="D128" s="118">
         <v>93</v>
       </c>
-      <c r="E27" s="119">
+      <c r="E128" s="118">
+        <f>'93'!M51</f>
+        <v>0</v>
+      </c>
+      <c r="F128" s="117" t="s">
+        <v>81</v>
+      </c>
+      <c r="G128" s="117"/>
+      <c r="H128" s="117"/>
+    </row>
+    <row r="129" spans="1:8" ht="27.95" customHeight="1">
+      <c r="A129" s="117" t="s">
+        <v>278</v>
+      </c>
+      <c r="B129" s="117" t="s">
+        <v>117</v>
+      </c>
+      <c r="C129" s="117" t="s">
+        <v>119</v>
+      </c>
+      <c r="D129" s="118">
+        <v>93</v>
+      </c>
+      <c r="E129" s="118">
+        <f>'93'!M52</f>
+        <v>0</v>
+      </c>
+      <c r="F129" s="117" t="s">
+        <v>81</v>
+      </c>
+      <c r="G129" s="117"/>
+      <c r="H129" s="117"/>
+    </row>
+    <row r="130" spans="1:8" ht="27.95" customHeight="1">
+      <c r="A130" s="117" t="s">
+        <v>279</v>
+      </c>
+      <c r="B130" s="117" t="s">
+        <v>117</v>
+      </c>
+      <c r="C130" s="117" t="s">
+        <v>119</v>
+      </c>
+      <c r="D130" s="118">
+        <v>93</v>
+      </c>
+      <c r="E130" s="118">
+        <f>'93'!O49</f>
+        <v>0</v>
+      </c>
+      <c r="F130" s="117" t="s">
+        <v>81</v>
+      </c>
+      <c r="G130" s="117"/>
+      <c r="H130" s="117" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="131" spans="1:8" ht="27.95" customHeight="1">
+      <c r="A131" s="117" t="s">
+        <v>280</v>
+      </c>
+      <c r="B131" s="117" t="s">
+        <v>117</v>
+      </c>
+      <c r="C131" s="117" t="s">
+        <v>119</v>
+      </c>
+      <c r="D131" s="118">
+        <v>93</v>
+      </c>
+      <c r="E131" s="118">
+        <f>'93'!O50</f>
+        <v>0</v>
+      </c>
+      <c r="F131" s="117" t="s">
+        <v>81</v>
+      </c>
+      <c r="G131" s="117"/>
+      <c r="H131" s="117"/>
+    </row>
+    <row r="132" spans="1:8" ht="27.95" customHeight="1">
+      <c r="A132" s="117" t="s">
+        <v>281</v>
+      </c>
+      <c r="B132" s="117" t="s">
+        <v>117</v>
+      </c>
+      <c r="C132" s="117" t="s">
+        <v>119</v>
+      </c>
+      <c r="D132" s="118">
+        <v>93</v>
+      </c>
+      <c r="E132" s="118">
+        <f>'93'!O51</f>
+        <v>0</v>
+      </c>
+      <c r="F132" s="117" t="s">
+        <v>81</v>
+      </c>
+      <c r="G132" s="117"/>
+      <c r="H132" s="117"/>
+    </row>
+    <row r="133" spans="1:8" ht="27.95" customHeight="1">
+      <c r="A133" s="117" t="s">
+        <v>282</v>
+      </c>
+      <c r="B133" s="117" t="s">
+        <v>117</v>
+      </c>
+      <c r="C133" s="117" t="s">
+        <v>119</v>
+      </c>
+      <c r="D133" s="118">
+        <v>93</v>
+      </c>
+      <c r="E133" s="118">
+        <f>'93'!O52</f>
+        <v>0</v>
+      </c>
+      <c r="F133" s="117" t="s">
+        <v>81</v>
+      </c>
+      <c r="G133" s="117"/>
+      <c r="H133" s="117"/>
+    </row>
+    <row r="134" spans="1:8" ht="27.95" customHeight="1">
+      <c r="A134" s="117" t="s">
+        <v>283</v>
+      </c>
+      <c r="B134" s="117" t="s">
+        <v>117</v>
+      </c>
+      <c r="C134" s="117" t="s">
+        <v>119</v>
+      </c>
+      <c r="D134" s="118">
+        <v>93</v>
+      </c>
+      <c r="E134" s="118">
+        <f>'93'!Q49</f>
+        <v>0</v>
+      </c>
+      <c r="F134" s="117" t="s">
+        <v>81</v>
+      </c>
+      <c r="G134" s="117"/>
+      <c r="H134" s="117" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="135" spans="1:8" ht="27.95" customHeight="1">
+      <c r="A135" s="117" t="s">
+        <v>284</v>
+      </c>
+      <c r="B135" s="117" t="s">
+        <v>117</v>
+      </c>
+      <c r="C135" s="117" t="s">
+        <v>119</v>
+      </c>
+      <c r="D135" s="118">
+        <v>93</v>
+      </c>
+      <c r="E135" s="118">
+        <f>'93'!Q50</f>
+        <v>0</v>
+      </c>
+      <c r="F135" s="117" t="s">
+        <v>81</v>
+      </c>
+      <c r="G135" s="117"/>
+      <c r="H135" s="117"/>
+    </row>
+    <row r="136" spans="1:8" ht="27.95" customHeight="1">
+      <c r="A136" s="117" t="s">
+        <v>285</v>
+      </c>
+      <c r="B136" s="117" t="s">
+        <v>117</v>
+      </c>
+      <c r="C136" s="117" t="s">
+        <v>119</v>
+      </c>
+      <c r="D136" s="118">
+        <v>93</v>
+      </c>
+      <c r="E136" s="118">
+        <f>'93'!Q51</f>
+        <v>0</v>
+      </c>
+      <c r="F136" s="117" t="s">
+        <v>81</v>
+      </c>
+      <c r="G136" s="117"/>
+      <c r="H136" s="117"/>
+    </row>
+    <row r="137" spans="1:8" ht="27.95" customHeight="1">
+      <c r="A137" s="117" t="s">
+        <v>286</v>
+      </c>
+      <c r="B137" s="117" t="s">
+        <v>117</v>
+      </c>
+      <c r="C137" s="117" t="s">
+        <v>119</v>
+      </c>
+      <c r="D137" s="118">
+        <v>93</v>
+      </c>
+      <c r="E137" s="118">
+        <f>'93'!Q52</f>
+        <v>0</v>
+      </c>
+      <c r="F137" s="117" t="s">
+        <v>81</v>
+      </c>
+      <c r="G137" s="117"/>
+      <c r="H137" s="117"/>
+    </row>
+    <row r="138" spans="1:8" ht="27.95" customHeight="1">
+      <c r="A138" s="117" t="s">
+        <v>287</v>
+      </c>
+      <c r="B138" s="117" t="s">
+        <v>117</v>
+      </c>
+      <c r="C138" s="117" t="s">
+        <v>116</v>
+      </c>
+      <c r="D138" s="118">
+        <v>93</v>
+      </c>
+      <c r="E138" s="118">
         <f>'93'!N49</f>
         <v>0</v>
       </c>
-      <c r="F27" s="118" t="s">
-        <v>87</v>
-      </c>
-      <c r="G27" s="118" t="s">
+      <c r="F138" s="117" t="s">
+        <v>86</v>
+      </c>
+      <c r="G138" s="117" t="s">
         <v>80</v>
       </c>
-      <c r="H27" s="118"/>
+      <c r="H138" s="117" t="s">
+        <v>182</v>
+      </c>
     </row>
-    <row r="28" spans="1:8" ht="27.95" customHeight="1">
-      <c r="A28" s="118" t="s">
+    <row r="139" spans="1:8" ht="27.95" customHeight="1">
+      <c r="A139" s="117" t="s">
+        <v>288</v>
+      </c>
+      <c r="B139" s="117" t="s">
+        <v>117</v>
+      </c>
+      <c r="C139" s="117" t="s">
         <v>116</v>
       </c>
-      <c r="B28" s="118" t="s">
+      <c r="D139" s="118">
+        <v>93</v>
+      </c>
+      <c r="E139" s="118">
+        <f>'93'!N50</f>
+        <v>0</v>
+      </c>
+      <c r="F139" s="117" t="s">
+        <v>86</v>
+      </c>
+      <c r="G139" s="117"/>
+      <c r="H139" s="117"/>
+    </row>
+    <row r="140" spans="1:8" ht="27.95" customHeight="1">
+      <c r="A140" s="117" t="s">
+        <v>289</v>
+      </c>
+      <c r="B140" s="117" t="s">
+        <v>117</v>
+      </c>
+      <c r="C140" s="117" t="s">
+        <v>116</v>
+      </c>
+      <c r="D140" s="118">
+        <v>93</v>
+      </c>
+      <c r="E140" s="118">
+        <f>'93'!N51</f>
+        <v>0</v>
+      </c>
+      <c r="F140" s="117" t="s">
+        <v>86</v>
+      </c>
+      <c r="G140" s="117"/>
+      <c r="H140" s="117"/>
+    </row>
+    <row r="141" spans="1:8" ht="27.95" customHeight="1">
+      <c r="A141" s="117" t="s">
+        <v>290</v>
+      </c>
+      <c r="B141" s="117" t="s">
+        <v>117</v>
+      </c>
+      <c r="C141" s="117" t="s">
+        <v>116</v>
+      </c>
+      <c r="D141" s="118">
+        <v>93</v>
+      </c>
+      <c r="E141" s="118">
+        <f>'93'!N52</f>
+        <v>0</v>
+      </c>
+      <c r="F141" s="117" t="s">
+        <v>86</v>
+      </c>
+      <c r="G141" s="117"/>
+      <c r="H141" s="117"/>
+    </row>
+    <row r="142" spans="1:8" ht="27.95" customHeight="1">
+      <c r="A142" s="117" t="s">
+        <v>291</v>
+      </c>
+      <c r="B142" s="117" t="s">
+        <v>117</v>
+      </c>
+      <c r="C142" s="117" t="s">
+        <v>116</v>
+      </c>
+      <c r="D142" s="118">
+        <v>93</v>
+      </c>
+      <c r="E142" s="118">
+        <f>'93'!P49</f>
+        <v>0</v>
+      </c>
+      <c r="F142" s="117" t="s">
+        <v>86</v>
+      </c>
+      <c r="G142" s="117"/>
+      <c r="H142" s="117" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="143" spans="1:8" ht="27.95" customHeight="1">
+      <c r="A143" s="117" t="s">
+        <v>292</v>
+      </c>
+      <c r="B143" s="117" t="s">
+        <v>117</v>
+      </c>
+      <c r="C143" s="117" t="s">
+        <v>116</v>
+      </c>
+      <c r="D143" s="118">
+        <v>93</v>
+      </c>
+      <c r="E143" s="118">
+        <f>'93'!P50</f>
+        <v>0</v>
+      </c>
+      <c r="F143" s="117" t="s">
+        <v>86</v>
+      </c>
+      <c r="G143" s="117"/>
+      <c r="H143" s="117"/>
+    </row>
+    <row r="144" spans="1:8" ht="27.95" customHeight="1">
+      <c r="A144" s="117" t="s">
+        <v>293</v>
+      </c>
+      <c r="B144" s="117" t="s">
+        <v>117</v>
+      </c>
+      <c r="C144" s="117" t="s">
+        <v>116</v>
+      </c>
+      <c r="D144" s="118">
+        <v>93</v>
+      </c>
+      <c r="E144" s="118">
+        <f>'93'!P51</f>
+        <v>0</v>
+      </c>
+      <c r="F144" s="117" t="s">
+        <v>86</v>
+      </c>
+      <c r="G144" s="117"/>
+      <c r="H144" s="117"/>
+    </row>
+    <row r="145" spans="1:8" ht="27.95" customHeight="1">
+      <c r="A145" s="117" t="s">
+        <v>294</v>
+      </c>
+      <c r="B145" s="117" t="s">
+        <v>117</v>
+      </c>
+      <c r="C145" s="117" t="s">
+        <v>116</v>
+      </c>
+      <c r="D145" s="118">
+        <v>93</v>
+      </c>
+      <c r="E145" s="118">
+        <f>'93'!P52</f>
+        <v>0</v>
+      </c>
+      <c r="F145" s="117" t="s">
+        <v>86</v>
+      </c>
+      <c r="G145" s="117"/>
+      <c r="H145" s="117"/>
+    </row>
+    <row r="146" spans="1:8" ht="27.95" customHeight="1">
+      <c r="A146" s="117" t="s">
+        <v>295</v>
+      </c>
+      <c r="B146" s="117" t="s">
+        <v>117</v>
+      </c>
+      <c r="C146" s="117" t="s">
+        <v>116</v>
+      </c>
+      <c r="D146" s="118">
+        <v>93</v>
+      </c>
+      <c r="E146" s="118">
+        <f>'93'!R49</f>
+        <v>0</v>
+      </c>
+      <c r="F146" s="117" t="s">
+        <v>86</v>
+      </c>
+      <c r="G146" s="117"/>
+      <c r="H146" s="117" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="147" spans="1:8" ht="27.95" customHeight="1">
+      <c r="A147" s="117" t="s">
+        <v>296</v>
+      </c>
+      <c r="B147" s="117" t="s">
+        <v>117</v>
+      </c>
+      <c r="C147" s="117" t="s">
+        <v>116</v>
+      </c>
+      <c r="D147" s="118">
+        <v>93</v>
+      </c>
+      <c r="E147" s="118">
+        <f>'93'!R50</f>
+        <v>0</v>
+      </c>
+      <c r="F147" s="117" t="s">
+        <v>86</v>
+      </c>
+      <c r="G147" s="117"/>
+      <c r="H147" s="117"/>
+    </row>
+    <row r="148" spans="1:8" ht="27.95" customHeight="1">
+      <c r="A148" s="117" t="s">
+        <v>297</v>
+      </c>
+      <c r="B148" s="117" t="s">
+        <v>117</v>
+      </c>
+      <c r="C148" s="117" t="s">
+        <v>116</v>
+      </c>
+      <c r="D148" s="118">
+        <v>93</v>
+      </c>
+      <c r="E148" s="118">
+        <f>'93'!R51</f>
+        <v>0</v>
+      </c>
+      <c r="F148" s="117" t="s">
+        <v>86</v>
+      </c>
+      <c r="G148" s="117"/>
+      <c r="H148" s="117"/>
+    </row>
+    <row r="149" spans="1:8" ht="27.95" customHeight="1">
+      <c r="A149" s="117" t="s">
+        <v>298</v>
+      </c>
+      <c r="B149" s="117" t="s">
+        <v>117</v>
+      </c>
+      <c r="C149" s="117" t="s">
+        <v>116</v>
+      </c>
+      <c r="D149" s="118">
+        <v>93</v>
+      </c>
+      <c r="E149" s="118">
+        <f>'93'!R52</f>
+        <v>0</v>
+      </c>
+      <c r="F149" s="117" t="s">
+        <v>86</v>
+      </c>
+      <c r="G149" s="117"/>
+      <c r="H149" s="117"/>
+    </row>
+    <row r="150" spans="1:8" ht="27.95" customHeight="1">
+      <c r="A150" s="117" t="s">
+        <v>299</v>
+      </c>
+      <c r="B150" s="117" t="s">
         <v>35</v>
       </c>
-      <c r="C28" s="118" t="s">
-        <v>115</v>
-      </c>
-      <c r="D28" s="119">
+      <c r="C150" s="117" t="s">
+        <v>114</v>
+      </c>
+      <c r="D150" s="118">
         <v>93</v>
       </c>
-      <c r="E28" s="119">
+      <c r="E150" s="118">
         <f>'93'!M54</f>
         <v>0</v>
       </c>
-      <c r="F28" s="118" t="s">
+      <c r="F150" s="117" t="s">
         <v>81</v>
       </c>
-      <c r="G28" s="118" t="s">
+      <c r="G150" s="117" t="s">
         <v>80</v>
       </c>
-      <c r="H28" s="118"/>
+      <c r="H150" s="117"/>
     </row>
-    <row r="29" spans="1:8" ht="27.95" customHeight="1">
-      <c r="A29" s="118" t="s">
-        <v>114</v>
-      </c>
-      <c r="B29" s="118" t="s">
+    <row r="151" spans="1:8" ht="27.95" customHeight="1">
+      <c r="A151" s="117" t="s">
+        <v>300</v>
+      </c>
+      <c r="B151" s="117" t="s">
         <v>35</v>
       </c>
-      <c r="C29" s="118" t="s">
-        <v>113</v>
-      </c>
-      <c r="D29" s="119">
+      <c r="C151" s="117" t="s">
+        <v>112</v>
+      </c>
+      <c r="D151" s="118">
         <v>93</v>
       </c>
-      <c r="E29" s="119">
+      <c r="E151" s="118">
         <f>'93'!N54</f>
         <v>0</v>
       </c>
-      <c r="F29" s="118" t="s">
+      <c r="F151" s="117" t="s">
         <v>81</v>
       </c>
-      <c r="G29" s="118" t="s">
+      <c r="G151" s="117" t="s">
         <v>80</v>
       </c>
-      <c r="H29" s="118"/>
+      <c r="H151" s="117"/>
     </row>
-    <row r="30" spans="1:8" ht="27.95" customHeight="1">
-      <c r="A30" s="118" t="s">
-        <v>112</v>
-      </c>
-      <c r="B30" s="118" t="s">
-        <v>107</v>
-      </c>
-      <c r="C30" s="118" t="s">
-        <v>111</v>
-      </c>
-      <c r="D30" s="119">
+    <row r="152" spans="1:8" ht="27.95" customHeight="1">
+      <c r="A152" s="117" t="s">
+        <v>301</v>
+      </c>
+      <c r="B152" s="117" t="s">
+        <v>106</v>
+      </c>
+      <c r="C152" s="117" t="s">
+        <v>110</v>
+      </c>
+      <c r="D152" s="118">
         <v>93</v>
       </c>
-      <c r="E30" s="119">
+      <c r="E152" s="118">
         <f>'93'!M65</f>
         <v>0</v>
       </c>
-      <c r="F30" s="118" t="s">
+      <c r="F152" s="117" t="s">
         <v>81</v>
       </c>
-      <c r="G30" s="118" t="s">
-        <v>105</v>
-      </c>
-      <c r="H30" s="118"/>
+      <c r="G152" s="117" t="s">
+        <v>104</v>
+      </c>
+      <c r="H152" s="117"/>
     </row>
-    <row r="31" spans="1:8" ht="27.95" customHeight="1">
-      <c r="A31" s="118" t="s">
-        <v>110</v>
-      </c>
-      <c r="B31" s="118" t="s">
-        <v>107</v>
-      </c>
-      <c r="C31" s="118" t="s">
-        <v>109</v>
-      </c>
-      <c r="D31" s="119">
+    <row r="153" spans="1:8" ht="27.95" customHeight="1">
+      <c r="A153" s="117" t="s">
+        <v>302</v>
+      </c>
+      <c r="B153" s="117" t="s">
+        <v>106</v>
+      </c>
+      <c r="C153" s="117" t="s">
+        <v>108</v>
+      </c>
+      <c r="D153" s="118">
         <v>93</v>
       </c>
-      <c r="E31" s="119">
+      <c r="E153" s="118">
         <f>'93'!M63</f>
         <v>0</v>
       </c>
-      <c r="F31" s="118" t="s">
+      <c r="F153" s="117" t="s">
         <v>81</v>
       </c>
-      <c r="G31" s="118" t="s">
+      <c r="G153" s="117" t="s">
+        <v>104</v>
+      </c>
+      <c r="H153" s="117"/>
+    </row>
+    <row r="154" spans="1:8" ht="27.95" customHeight="1">
+      <c r="A154" s="117" t="s">
+        <v>303</v>
+      </c>
+      <c r="B154" s="117" t="s">
+        <v>106</v>
+      </c>
+      <c r="C154" s="117" t="s">
         <v>105</v>
       </c>
-      <c r="H31" s="118"/>
-    </row>
-    <row r="32" spans="1:8" ht="27.95" customHeight="1">
-      <c r="A32" s="118" t="s">
-        <v>108</v>
-      </c>
-      <c r="B32" s="118" t="s">
-        <v>107</v>
-      </c>
-      <c r="C32" s="118" t="s">
-        <v>106</v>
-      </c>
-      <c r="D32" s="119">
+      <c r="D154" s="118">
         <v>93</v>
       </c>
-      <c r="E32" s="119">
+      <c r="E154" s="118">
         <f>'93'!Q59</f>
         <v>0</v>
       </c>
-      <c r="F32" s="118" t="s">
+      <c r="F154" s="117" t="s">
         <v>81</v>
       </c>
-      <c r="G32" s="118" t="s">
+      <c r="G154" s="117" t="s">
+        <v>80</v>
+      </c>
+      <c r="H154" s="117" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="155" spans="1:8" ht="27.95" customHeight="1">
+      <c r="A155" s="117" t="s">
+        <v>304</v>
+      </c>
+      <c r="B155" s="117" t="s">
+        <v>106</v>
+      </c>
+      <c r="C155" s="117" t="s">
         <v>105</v>
       </c>
-      <c r="H32" s="118"/>
+      <c r="D155" s="118">
+        <v>93</v>
+      </c>
+      <c r="E155" s="118">
+        <f>'93'!Q60</f>
+        <v>0</v>
+      </c>
+      <c r="F155" s="117" t="s">
+        <v>81</v>
+      </c>
+      <c r="G155" s="117" t="s">
+        <v>80</v>
+      </c>
+      <c r="H155" s="117"/>
     </row>
-    <row r="33" spans="1:8" ht="27.95" customHeight="1">
-      <c r="A33" s="118" t="s">
-        <v>104</v>
-      </c>
-      <c r="B33" s="118" t="s">
-        <v>99</v>
-      </c>
-      <c r="C33" s="118" t="s">
-        <v>103</v>
-      </c>
-      <c r="D33" s="119">
+    <row r="156" spans="1:8" ht="27.95" customHeight="1">
+      <c r="A156" s="117" t="s">
+        <v>305</v>
+      </c>
+      <c r="B156" s="117" t="s">
+        <v>106</v>
+      </c>
+      <c r="C156" s="117" t="s">
+        <v>105</v>
+      </c>
+      <c r="D156" s="118">
         <v>93</v>
       </c>
-      <c r="E33" s="119">
+      <c r="E156" s="118">
+        <f>'93'!Q61</f>
+        <v>0</v>
+      </c>
+      <c r="F156" s="117" t="s">
+        <v>81</v>
+      </c>
+      <c r="G156" s="117" t="s">
+        <v>80</v>
+      </c>
+      <c r="H156" s="117"/>
+    </row>
+    <row r="157" spans="1:8" ht="27.95" customHeight="1">
+      <c r="A157" s="117" t="s">
+        <v>306</v>
+      </c>
+      <c r="B157" s="117" t="s">
+        <v>106</v>
+      </c>
+      <c r="C157" s="117" t="s">
+        <v>105</v>
+      </c>
+      <c r="D157" s="118">
+        <v>93</v>
+      </c>
+      <c r="E157" s="118">
+        <f>'93'!S59</f>
+        <v>0</v>
+      </c>
+      <c r="F157" s="117" t="s">
+        <v>81</v>
+      </c>
+      <c r="G157" s="117" t="s">
+        <v>80</v>
+      </c>
+      <c r="H157" s="117" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="158" spans="1:8" ht="27.95" customHeight="1">
+      <c r="A158" s="117" t="s">
+        <v>307</v>
+      </c>
+      <c r="B158" s="117" t="s">
+        <v>106</v>
+      </c>
+      <c r="C158" s="117" t="s">
+        <v>105</v>
+      </c>
+      <c r="D158" s="118">
+        <v>93</v>
+      </c>
+      <c r="E158" s="118">
+        <f>'93'!S60</f>
+        <v>0</v>
+      </c>
+      <c r="F158" s="117" t="s">
+        <v>81</v>
+      </c>
+      <c r="G158" s="117" t="s">
+        <v>80</v>
+      </c>
+      <c r="H158" s="117"/>
+    </row>
+    <row r="159" spans="1:8" ht="27.95" customHeight="1">
+      <c r="A159" s="117" t="s">
+        <v>308</v>
+      </c>
+      <c r="B159" s="117" t="s">
+        <v>106</v>
+      </c>
+      <c r="C159" s="117" t="s">
+        <v>105</v>
+      </c>
+      <c r="D159" s="118">
+        <v>93</v>
+      </c>
+      <c r="E159" s="118">
+        <f>'93'!S61</f>
+        <v>0</v>
+      </c>
+      <c r="F159" s="117" t="s">
+        <v>81</v>
+      </c>
+      <c r="G159" s="117" t="s">
+        <v>80</v>
+      </c>
+      <c r="H159" s="117"/>
+    </row>
+    <row r="160" spans="1:8" ht="27.95" customHeight="1">
+      <c r="A160" s="117" t="s">
+        <v>309</v>
+      </c>
+      <c r="B160" s="117" t="s">
+        <v>98</v>
+      </c>
+      <c r="C160" s="117" t="s">
+        <v>102</v>
+      </c>
+      <c r="D160" s="118">
+        <v>93</v>
+      </c>
+      <c r="E160" s="118">
         <f>'93'!C79</f>
         <v>0</v>
       </c>
-      <c r="F33" s="118" t="s">
-        <v>97</v>
-      </c>
-      <c r="G33" s="118" t="s">
+      <c r="F160" s="117" t="s">
         <v>96</v>
       </c>
-      <c r="H33" s="118"/>
+      <c r="G160" s="117" t="s">
+        <v>95</v>
+      </c>
+      <c r="H160" s="117"/>
     </row>
-    <row r="34" spans="1:8" ht="27.95" customHeight="1">
-      <c r="A34" s="118" t="s">
-        <v>102</v>
-      </c>
-      <c r="B34" s="118" t="s">
-        <v>99</v>
-      </c>
-      <c r="C34" s="118" t="s">
-        <v>101</v>
-      </c>
-      <c r="D34" s="119">
+    <row r="161" spans="1:8" ht="27.95" customHeight="1">
+      <c r="A161" s="117" t="s">
+        <v>310</v>
+      </c>
+      <c r="B161" s="117" t="s">
+        <v>98</v>
+      </c>
+      <c r="C161" s="117" t="s">
+        <v>100</v>
+      </c>
+      <c r="D161" s="118">
         <v>93</v>
       </c>
-      <c r="E34" s="119">
+      <c r="E161" s="118">
         <f>'93'!C80</f>
         <v>0</v>
       </c>
-      <c r="F34" s="118" t="s">
+      <c r="F161" s="117" t="s">
+        <v>96</v>
+      </c>
+      <c r="G161" s="117" t="s">
+        <v>95</v>
+      </c>
+      <c r="H161" s="117"/>
+    </row>
+    <row r="162" spans="1:8" ht="27.95" customHeight="1">
+      <c r="A162" s="117" t="s">
+        <v>311</v>
+      </c>
+      <c r="B162" s="117" t="s">
+        <v>98</v>
+      </c>
+      <c r="C162" s="117" t="s">
         <v>97</v>
       </c>
-      <c r="G34" s="118" t="s">
-        <v>96</v>
-      </c>
-      <c r="H34" s="118"/>
-    </row>
-    <row r="35" spans="1:8" ht="27.95" customHeight="1">
-      <c r="A35" s="118" t="s">
-        <v>100</v>
-      </c>
-      <c r="B35" s="118" t="s">
-        <v>99</v>
-      </c>
-      <c r="C35" s="118" t="s">
-        <v>98</v>
-      </c>
-      <c r="D35" s="119">
+      <c r="D162" s="118">
         <v>93</v>
       </c>
-      <c r="E35" s="119">
+      <c r="E162" s="118">
         <f>'93'!C78</f>
         <v>0</v>
       </c>
-      <c r="F35" s="118" t="s">
-        <v>97</v>
-      </c>
-      <c r="G35" s="118" t="s">
+      <c r="F162" s="117" t="s">
         <v>96</v>
       </c>
-      <c r="H35" s="118"/>
+      <c r="G162" s="117" t="s">
+        <v>95</v>
+      </c>
+      <c r="H162" s="117"/>
     </row>
-    <row r="36" spans="1:8" ht="27.95" customHeight="1">
-      <c r="A36" s="118" t="s">
+    <row r="163" spans="1:8" ht="27.95" customHeight="1">
+      <c r="A163" s="117" t="s">
+        <v>312</v>
+      </c>
+      <c r="B163" s="117" t="s">
+        <v>98</v>
+      </c>
+      <c r="C163" s="193">
+        <v>8.3333333333333329E-2</v>
+      </c>
+      <c r="D163" s="118">
+        <v>93</v>
+      </c>
+      <c r="E163" s="118">
+        <f>'93'!F78</f>
+        <v>0</v>
+      </c>
+      <c r="F163" s="117" t="s">
+        <v>96</v>
+      </c>
+      <c r="G163" s="117" t="s">
         <v>95</v>
       </c>
-      <c r="B36" s="118" t="s">
+      <c r="H163" s="117"/>
+    </row>
+    <row r="164" spans="1:8" ht="27.95" customHeight="1">
+      <c r="A164" s="117" t="s">
+        <v>313</v>
+      </c>
+      <c r="B164" s="117" t="s">
+        <v>98</v>
+      </c>
+      <c r="C164" s="193">
+        <v>0.16666666666666666</v>
+      </c>
+      <c r="D164" s="118">
+        <v>93</v>
+      </c>
+      <c r="E164" s="118">
+        <f>'93'!G78</f>
+        <v>0</v>
+      </c>
+      <c r="F164" s="117" t="s">
+        <v>96</v>
+      </c>
+      <c r="G164" s="117" t="s">
+        <v>95</v>
+      </c>
+      <c r="H164" s="117"/>
+    </row>
+    <row r="165" spans="1:8" ht="27.95" customHeight="1">
+      <c r="A165" s="117" t="s">
+        <v>314</v>
+      </c>
+      <c r="B165" s="117" t="s">
+        <v>98</v>
+      </c>
+      <c r="C165" s="193">
+        <v>0.25</v>
+      </c>
+      <c r="D165" s="118">
+        <v>93</v>
+      </c>
+      <c r="E165" s="118">
+        <f>'93'!H78</f>
+        <v>0</v>
+      </c>
+      <c r="F165" s="117" t="s">
+        <v>96</v>
+      </c>
+      <c r="G165" s="117" t="s">
+        <v>95</v>
+      </c>
+      <c r="H165" s="117"/>
+    </row>
+    <row r="166" spans="1:8" ht="27.95" customHeight="1">
+      <c r="A166" s="117" t="s">
+        <v>315</v>
+      </c>
+      <c r="B166" s="117" t="s">
+        <v>98</v>
+      </c>
+      <c r="C166" s="193">
+        <v>0.33333333333333298</v>
+      </c>
+      <c r="D166" s="118">
+        <v>93</v>
+      </c>
+      <c r="E166" s="118">
+        <f>'93'!J78</f>
+        <v>0</v>
+      </c>
+      <c r="F166" s="117" t="s">
+        <v>96</v>
+      </c>
+      <c r="G166" s="117" t="s">
+        <v>95</v>
+      </c>
+      <c r="H166" s="117"/>
+    </row>
+    <row r="167" spans="1:8" ht="27.95" customHeight="1">
+      <c r="A167" s="117" t="s">
+        <v>316</v>
+      </c>
+      <c r="B167" s="117" t="s">
+        <v>98</v>
+      </c>
+      <c r="C167" s="193">
+        <v>0.41666666666666602</v>
+      </c>
+      <c r="D167" s="118">
+        <v>93</v>
+      </c>
+      <c r="E167" s="118">
+        <f>'93'!L78</f>
+        <v>0</v>
+      </c>
+      <c r="F167" s="117" t="s">
+        <v>96</v>
+      </c>
+      <c r="G167" s="117" t="s">
+        <v>95</v>
+      </c>
+      <c r="H167" s="117"/>
+    </row>
+    <row r="168" spans="1:8" ht="27.95" customHeight="1">
+      <c r="A168" s="117" t="s">
+        <v>317</v>
+      </c>
+      <c r="B168" s="117" t="s">
+        <v>98</v>
+      </c>
+      <c r="C168" s="193">
+        <v>0.499999999999999</v>
+      </c>
+      <c r="D168" s="118">
+        <v>93</v>
+      </c>
+      <c r="E168" s="118">
+        <f>'93'!M78</f>
+        <v>0</v>
+      </c>
+      <c r="F168" s="117" t="s">
+        <v>96</v>
+      </c>
+      <c r="G168" s="117" t="s">
+        <v>95</v>
+      </c>
+      <c r="H168" s="117"/>
+    </row>
+    <row r="169" spans="1:8" ht="27.95" customHeight="1">
+      <c r="A169" s="117" t="s">
+        <v>318</v>
+      </c>
+      <c r="B169" s="117" t="s">
+        <v>98</v>
+      </c>
+      <c r="C169" s="193">
+        <v>0.58333333333333204</v>
+      </c>
+      <c r="D169" s="118">
+        <v>93</v>
+      </c>
+      <c r="E169" s="118">
+        <f>'93'!N78</f>
+        <v>0</v>
+      </c>
+      <c r="F169" s="117" t="s">
+        <v>96</v>
+      </c>
+      <c r="G169" s="117" t="s">
+        <v>95</v>
+      </c>
+      <c r="H169" s="117"/>
+    </row>
+    <row r="170" spans="1:8" ht="27.95" customHeight="1">
+      <c r="A170" s="117" t="s">
+        <v>319</v>
+      </c>
+      <c r="B170" s="117" t="s">
+        <v>98</v>
+      </c>
+      <c r="C170" s="193">
+        <v>0.66666666666666496</v>
+      </c>
+      <c r="D170" s="118">
+        <v>93</v>
+      </c>
+      <c r="E170" s="118">
+        <f>'93'!O78</f>
+        <v>0</v>
+      </c>
+      <c r="F170" s="117" t="s">
+        <v>96</v>
+      </c>
+      <c r="G170" s="117" t="s">
+        <v>95</v>
+      </c>
+      <c r="H170" s="117"/>
+    </row>
+    <row r="171" spans="1:8" ht="27.95" customHeight="1">
+      <c r="A171" s="117" t="s">
+        <v>320</v>
+      </c>
+      <c r="B171" s="117" t="s">
+        <v>98</v>
+      </c>
+      <c r="C171" s="193">
+        <v>0.749999999999998</v>
+      </c>
+      <c r="D171" s="118">
+        <v>93</v>
+      </c>
+      <c r="E171" s="118">
+        <f>'93'!P78</f>
+        <v>0</v>
+      </c>
+      <c r="F171" s="117" t="s">
+        <v>96</v>
+      </c>
+      <c r="G171" s="117" t="s">
+        <v>95</v>
+      </c>
+      <c r="H171" s="117"/>
+    </row>
+    <row r="172" spans="1:8" ht="27.95" customHeight="1">
+      <c r="A172" s="117" t="s">
+        <v>321</v>
+      </c>
+      <c r="B172" s="117" t="s">
+        <v>98</v>
+      </c>
+      <c r="C172" s="193">
+        <v>0.83333333333333104</v>
+      </c>
+      <c r="D172" s="118">
+        <v>93</v>
+      </c>
+      <c r="E172" s="118">
+        <f>'93'!Q78</f>
+        <v>0</v>
+      </c>
+      <c r="F172" s="117" t="s">
+        <v>96</v>
+      </c>
+      <c r="G172" s="117" t="s">
+        <v>95</v>
+      </c>
+      <c r="H172" s="117"/>
+    </row>
+    <row r="173" spans="1:8" ht="27.95" customHeight="1">
+      <c r="A173" s="117" t="s">
+        <v>322</v>
+      </c>
+      <c r="B173" s="117" t="s">
+        <v>98</v>
+      </c>
+      <c r="C173" s="193">
+        <v>0.91666666666666397</v>
+      </c>
+      <c r="D173" s="118">
+        <v>93</v>
+      </c>
+      <c r="E173" s="118">
+        <f>'93'!R78</f>
+        <v>0</v>
+      </c>
+      <c r="F173" s="117" t="s">
+        <v>96</v>
+      </c>
+      <c r="G173" s="117" t="s">
+        <v>95</v>
+      </c>
+      <c r="H173" s="117"/>
+    </row>
+    <row r="174" spans="1:8" ht="27.95" customHeight="1">
+      <c r="A174" s="117" t="s">
+        <v>323</v>
+      </c>
+      <c r="B174" s="117" t="s">
+        <v>98</v>
+      </c>
+      <c r="C174" s="193">
+        <v>0.999999999999997</v>
+      </c>
+      <c r="D174" s="118">
+        <v>93</v>
+      </c>
+      <c r="E174" s="118">
+        <f>'93'!S78</f>
+        <v>0</v>
+      </c>
+      <c r="F174" s="117" t="s">
+        <v>96</v>
+      </c>
+      <c r="G174" s="117" t="s">
+        <v>95</v>
+      </c>
+      <c r="H174" s="117"/>
+    </row>
+    <row r="175" spans="1:8" ht="27.95" customHeight="1">
+      <c r="A175" s="117" t="s">
+        <v>324</v>
+      </c>
+      <c r="B175" s="117" t="s">
         <v>62</v>
       </c>
-      <c r="C36" s="118" t="s">
-        <v>94</v>
-      </c>
-      <c r="D36" s="119">
+      <c r="C175" s="117" t="s">
         <v>93</v>
       </c>
-      <c r="E36" s="119">
+      <c r="D175" s="118">
+        <v>93</v>
+      </c>
+      <c r="E175" s="118">
         <f>'93'!A82</f>
         <v>0</v>
       </c>
-      <c r="F36" s="118" t="s">
+      <c r="F175" s="117" t="s">
+        <v>92</v>
+      </c>
+      <c r="G175" s="117"/>
+      <c r="H175" s="117" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="176" spans="1:8" ht="27.95" customHeight="1">
+      <c r="A176" s="117" t="s">
+        <v>325</v>
+      </c>
+      <c r="B176" s="117" t="s">
+        <v>82</v>
+      </c>
+      <c r="C176" s="117" t="s">
+        <v>89</v>
+      </c>
+      <c r="D176" s="118">
         <v>93</v>
       </c>
-      <c r="G36" s="118"/>
-      <c r="H36" s="118" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="37" spans="1:8" ht="27.95" customHeight="1">
-      <c r="A37" s="118" t="s">
-        <v>91</v>
-      </c>
-      <c r="B37" s="118" t="s">
-        <v>83</v>
-      </c>
-      <c r="C37" s="118" t="s">
-        <v>90</v>
-      </c>
-      <c r="D37" s="119">
-        <v>93</v>
-      </c>
-      <c r="E37" s="119">
+      <c r="E176" s="118">
         <f>'93'!N82</f>
         <v>0</v>
       </c>
-      <c r="F37" s="118" t="s">
+      <c r="F176" s="117" t="s">
         <v>81</v>
       </c>
-      <c r="G37" s="118" t="s">
+      <c r="G176" s="117" t="s">
         <v>80</v>
       </c>
-      <c r="H37" s="118"/>
+      <c r="H176" s="117"/>
     </row>
-    <row r="38" spans="1:8" ht="27.95" customHeight="1">
-      <c r="A38" s="118" t="s">
-        <v>89</v>
-      </c>
-      <c r="B38" s="118" t="s">
-        <v>83</v>
-      </c>
-      <c r="C38" s="118" t="s">
-        <v>88</v>
-      </c>
-      <c r="D38" s="119">
+    <row r="177" spans="1:8" ht="27.95" customHeight="1">
+      <c r="A177" s="117" t="s">
+        <v>326</v>
+      </c>
+      <c r="B177" s="117" t="s">
+        <v>82</v>
+      </c>
+      <c r="C177" s="117" t="s">
+        <v>87</v>
+      </c>
+      <c r="D177" s="118">
         <v>93</v>
       </c>
-      <c r="E38" s="119">
+      <c r="E177" s="118">
         <f>'93'!M82</f>
         <v>0</v>
       </c>
-      <c r="F38" s="118" t="s">
-        <v>87</v>
-      </c>
-      <c r="G38" s="118" t="s">
+      <c r="F177" s="117" t="s">
+        <v>86</v>
+      </c>
+      <c r="G177" s="117" t="s">
         <v>80</v>
       </c>
-      <c r="H38" s="118"/>
+      <c r="H177" s="117"/>
     </row>
-    <row r="39" spans="1:8" ht="27.95" customHeight="1">
-      <c r="A39" s="118" t="s">
-        <v>86</v>
-      </c>
-      <c r="B39" s="118" t="s">
-        <v>83</v>
-      </c>
-      <c r="C39" s="118" t="s">
-        <v>85</v>
-      </c>
-      <c r="D39" s="119">
+    <row r="178" spans="1:8" ht="27.95" customHeight="1">
+      <c r="A178" s="117" t="s">
+        <v>327</v>
+      </c>
+      <c r="B178" s="117" t="s">
+        <v>82</v>
+      </c>
+      <c r="C178" s="117" t="s">
+        <v>84</v>
+      </c>
+      <c r="D178" s="118">
         <v>93</v>
       </c>
-      <c r="E39" s="119">
+      <c r="E178" s="118">
         <f>'93'!P82</f>
         <v>0</v>
       </c>
-      <c r="F39" s="118" t="s">
+      <c r="F178" s="117" t="s">
         <v>81</v>
       </c>
-      <c r="G39" s="118" t="s">
+      <c r="G178" s="117" t="s">
         <v>80</v>
       </c>
-      <c r="H39" s="118"/>
+      <c r="H178" s="117"/>
     </row>
-    <row r="40" spans="1:8" ht="27.95" customHeight="1">
-      <c r="A40" s="118" t="s">
-        <v>84</v>
-      </c>
-      <c r="B40" s="118" t="s">
-        <v>83</v>
-      </c>
-      <c r="C40" s="118" t="s">
-        <v>82</v>
-      </c>
-      <c r="D40" s="119">
+    <row r="179" spans="1:8" ht="24.75" customHeight="1">
+      <c r="A179" s="117" t="s">
+        <v>328</v>
+      </c>
+      <c r="B179" s="194" t="s">
+        <v>186</v>
+      </c>
+      <c r="C179" s="194" t="s">
+        <v>119</v>
+      </c>
+      <c r="D179" s="118">
         <v>93</v>
       </c>
-      <c r="E40" s="119">
-        <f>'93'!Q82</f>
+      <c r="E179" s="118">
+        <f>'93'!M76</f>
         <v>0</v>
       </c>
-      <c r="F40" s="118" t="s">
+      <c r="F179" s="117" t="s">
         <v>81</v>
       </c>
-      <c r="G40" s="118" t="s">
+      <c r="G179" s="117"/>
+      <c r="H179" s="117"/>
+    </row>
+    <row r="180" spans="1:8" ht="24.75" customHeight="1">
+      <c r="A180" s="117" t="s">
+        <v>329</v>
+      </c>
+      <c r="B180" s="194" t="s">
+        <v>186</v>
+      </c>
+      <c r="C180" s="194" t="s">
+        <v>119</v>
+      </c>
+      <c r="D180" s="118">
+        <v>93</v>
+      </c>
+      <c r="E180" s="118">
+        <f>'93'!N76</f>
+        <v>0</v>
+      </c>
+      <c r="F180" s="117" t="s">
+        <v>81</v>
+      </c>
+      <c r="G180" s="117"/>
+      <c r="H180" s="117"/>
+    </row>
+    <row r="181" spans="1:8" ht="24.75" customHeight="1">
+      <c r="A181" s="117" t="s">
+        <v>330</v>
+      </c>
+      <c r="B181" s="194" t="s">
+        <v>186</v>
+      </c>
+      <c r="C181" s="194" t="s">
+        <v>119</v>
+      </c>
+      <c r="D181" s="118">
+        <v>93</v>
+      </c>
+      <c r="E181" s="118">
+        <f>'93'!O76</f>
+        <v>0</v>
+      </c>
+      <c r="F181" s="117" t="s">
+        <v>81</v>
+      </c>
+      <c r="G181" s="117"/>
+      <c r="H181" s="117"/>
+    </row>
+    <row r="182" spans="1:8" ht="24.75" customHeight="1">
+      <c r="A182" s="117" t="s">
+        <v>331</v>
+      </c>
+      <c r="B182" s="194" t="s">
+        <v>187</v>
+      </c>
+      <c r="C182" s="194" t="s">
+        <v>119</v>
+      </c>
+      <c r="D182" s="118">
+        <v>93</v>
+      </c>
+      <c r="E182" s="118">
+        <f>'93'!P76</f>
+        <v>0</v>
+      </c>
+      <c r="F182" s="117" t="s">
+        <v>81</v>
+      </c>
+      <c r="G182" s="117"/>
+      <c r="H182" s="117"/>
+    </row>
+    <row r="183" spans="1:8" ht="24.75" customHeight="1">
+      <c r="A183" s="117" t="s">
+        <v>332</v>
+      </c>
+      <c r="B183" s="194" t="s">
+        <v>187</v>
+      </c>
+      <c r="C183" s="194" t="s">
+        <v>119</v>
+      </c>
+      <c r="D183" s="118">
+        <v>93</v>
+      </c>
+      <c r="E183" s="118">
+        <f>'93'!Q76</f>
+        <v>0</v>
+      </c>
+      <c r="F183" s="117" t="s">
+        <v>81</v>
+      </c>
+      <c r="G183" s="117"/>
+      <c r="H183" s="117"/>
+    </row>
+    <row r="184" spans="1:8" ht="24.75" customHeight="1">
+      <c r="A184" s="117" t="s">
+        <v>333</v>
+      </c>
+      <c r="B184" s="194" t="s">
+        <v>187</v>
+      </c>
+      <c r="C184" s="194" t="s">
+        <v>119</v>
+      </c>
+      <c r="D184" s="118">
+        <v>93</v>
+      </c>
+      <c r="E184" s="118">
+        <f>'93'!R76</f>
+        <v>0</v>
+      </c>
+      <c r="F184" s="117" t="s">
+        <v>81</v>
+      </c>
+      <c r="G184" s="117"/>
+      <c r="H184" s="117"/>
+    </row>
+    <row r="185" spans="1:8" ht="24.75" customHeight="1">
+      <c r="A185" s="117" t="s">
+        <v>334</v>
+      </c>
+      <c r="B185" s="194" t="s">
+        <v>187</v>
+      </c>
+      <c r="C185" s="194" t="s">
+        <v>119</v>
+      </c>
+      <c r="D185" s="118">
+        <v>93</v>
+      </c>
+      <c r="E185" s="118">
+        <f>'93'!S76</f>
+        <v>0</v>
+      </c>
+      <c r="F185" s="117" t="s">
+        <v>81</v>
+      </c>
+      <c r="G185" s="117"/>
+      <c r="H185" s="117"/>
+    </row>
+    <row r="186" spans="1:8" ht="39" customHeight="1">
+      <c r="A186" s="117" t="s">
+        <v>335</v>
+      </c>
+      <c r="B186" s="194" t="s">
+        <v>188</v>
+      </c>
+      <c r="C186" s="194" t="s">
+        <v>41</v>
+      </c>
+      <c r="D186" s="118">
+        <v>93</v>
+      </c>
+      <c r="E186" s="118">
+        <f>'93'!N71</f>
+        <v>0</v>
+      </c>
+      <c r="F186" s="194" t="s">
+        <v>96</v>
+      </c>
+      <c r="G186" s="117" t="s">
         <v>80</v>
       </c>
-      <c r="H40" s="118"/>
+      <c r="H186" s="117"/>
+    </row>
+    <row r="187" spans="1:8" ht="39" customHeight="1">
+      <c r="A187" s="117" t="s">
+        <v>336</v>
+      </c>
+      <c r="B187" s="194" t="s">
+        <v>188</v>
+      </c>
+      <c r="C187" s="194" t="s">
+        <v>42</v>
+      </c>
+      <c r="D187" s="118">
+        <v>93</v>
+      </c>
+      <c r="E187" s="118">
+        <f>'93'!O71</f>
+        <v>0</v>
+      </c>
+      <c r="F187" s="194" t="s">
+        <v>81</v>
+      </c>
+      <c r="G187" s="117" t="s">
+        <v>80</v>
+      </c>
+      <c r="H187" s="117"/>
+    </row>
+    <row r="188" spans="1:8" ht="39" customHeight="1">
+      <c r="A188" s="117" t="s">
+        <v>337</v>
+      </c>
+      <c r="B188" s="194" t="s">
+        <v>188</v>
+      </c>
+      <c r="C188" s="194" t="s">
+        <v>189</v>
+      </c>
+      <c r="D188" s="118">
+        <v>93</v>
+      </c>
+      <c r="E188" s="118">
+        <f>'93'!P71</f>
+        <v>0</v>
+      </c>
+      <c r="F188" s="194" t="s">
+        <v>96</v>
+      </c>
+      <c r="G188" s="117" t="s">
+        <v>80</v>
+      </c>
+      <c r="H188" s="117"/>
+    </row>
+    <row r="189" spans="1:8" ht="39" customHeight="1">
+      <c r="A189" s="117" t="s">
+        <v>338</v>
+      </c>
+      <c r="B189" s="194" t="s">
+        <v>188</v>
+      </c>
+      <c r="C189" s="194" t="s">
+        <v>44</v>
+      </c>
+      <c r="D189" s="118">
+        <v>93</v>
+      </c>
+      <c r="E189" s="118">
+        <f>'93'!Q71</f>
+        <v>0</v>
+      </c>
+      <c r="F189" s="194" t="s">
+        <v>96</v>
+      </c>
+      <c r="G189" s="117" t="s">
+        <v>80</v>
+      </c>
+      <c r="H189" s="117"/>
+    </row>
+    <row r="190" spans="1:8" ht="39" customHeight="1">
+      <c r="A190" s="117" t="s">
+        <v>339</v>
+      </c>
+      <c r="B190" s="194" t="s">
+        <v>188</v>
+      </c>
+      <c r="C190" s="194" t="s">
+        <v>45</v>
+      </c>
+      <c r="D190" s="118">
+        <v>93</v>
+      </c>
+      <c r="E190" s="118">
+        <f>'93'!R71</f>
+        <v>0</v>
+      </c>
+      <c r="F190" s="194" t="s">
+        <v>96</v>
+      </c>
+      <c r="G190" s="117" t="s">
+        <v>80</v>
+      </c>
+      <c r="H190" s="117"/>
+    </row>
+    <row r="191" spans="1:8" ht="39" customHeight="1">
+      <c r="A191" s="117" t="s">
+        <v>340</v>
+      </c>
+      <c r="B191" s="194" t="s">
+        <v>188</v>
+      </c>
+      <c r="C191" s="194" t="s">
+        <v>14</v>
+      </c>
+      <c r="D191" s="118">
+        <v>93</v>
+      </c>
+      <c r="E191" s="118">
+        <f>'93'!S71</f>
+        <v>0</v>
+      </c>
+      <c r="F191" s="194" t="s">
+        <v>81</v>
+      </c>
+      <c r="G191" s="117" t="s">
+        <v>80</v>
+      </c>
+      <c r="H191" s="117"/>
+    </row>
+    <row r="192" spans="1:8" ht="39" customHeight="1">
+      <c r="B192" s="194"/>
+      <c r="C192" s="194"/>
+      <c r="D192" s="118"/>
+      <c r="E192" s="118"/>
+      <c r="F192" s="117"/>
+      <c r="G192" s="117"/>
+      <c r="H192" s="117"/>
+    </row>
+    <row r="193" spans="2:8" ht="39" customHeight="1">
+      <c r="B193" s="194"/>
+      <c r="C193" s="117"/>
+      <c r="D193" s="118"/>
+      <c r="E193" s="118"/>
+      <c r="F193" s="117"/>
+      <c r="G193" s="117"/>
+      <c r="H193" s="117"/>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:H1"/>
     <mergeCell ref="A2:H2"/>
   </mergeCells>
+  <phoneticPr fontId="18" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>